--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -28816,6528 +28673,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:W42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．天第2期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>314 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>128 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>147 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>CSH A</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>CSH C</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>CSH D</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>CSV A</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>CSV C</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>CSV D</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>49&amp;50/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="16" t="inlineStr"/>
-      <c r="M6" s="16" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr"/>
-      <c r="O6" s="16" t="inlineStr"/>
-      <c r="P6" s="16" t="inlineStr"/>
-      <c r="Q6" s="17" t="inlineStr">
-        <is>
-          <t>CSH A | 4306呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t>CSH C | 2189呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="S6" s="17" t="inlineStr">
-        <is>
-          <t>CSH D | 2647呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="T6" s="16" t="inlineStr"/>
-      <c r="U6" s="16" t="inlineStr"/>
-      <c r="V6" s="16" t="inlineStr"/>
-      <c r="W6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr"/>
-      <c r="O7" s="16" t="inlineStr"/>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" s="16" t="inlineStr"/>
-      <c r="S7" s="16" t="inlineStr"/>
-      <c r="T7" s="17" t="inlineStr">
-        <is>
-          <t>CSV A | 3110呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="U7" s="17" t="inlineStr">
-        <is>
-          <t>CSV C | 1511呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="V7" s="17" t="inlineStr">
-        <is>
-          <t>CSV D | 1786呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="W7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="16" t="inlineStr"/>
-      <c r="N8" s="16" t="inlineStr"/>
-      <c r="O8" s="16" t="inlineStr"/>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q8" s="16" t="inlineStr"/>
-      <c r="R8" s="16" t="inlineStr"/>
-      <c r="S8" s="16" t="inlineStr"/>
-      <c r="T8" s="16" t="inlineStr"/>
-      <c r="U8" s="16" t="inlineStr"/>
-      <c r="V8" s="16" t="inlineStr"/>
-      <c r="W8" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$8,281万
-$45,803/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr"/>
-      <c r="M9" s="16" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr"/>
-      <c r="O9" s="16" t="inlineStr"/>
-      <c r="P9" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,435万
-$35,970/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="Q9" s="16" t="inlineStr"/>
-      <c r="R9" s="16" t="inlineStr"/>
-      <c r="S9" s="16" t="inlineStr"/>
-      <c r="T9" s="16" t="inlineStr"/>
-      <c r="U9" s="16" t="inlineStr"/>
-      <c r="V9" s="16" t="inlineStr"/>
-      <c r="W9" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="16" t="inlineStr"/>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
-      <c r="M10" s="16" t="inlineStr"/>
-      <c r="N10" s="16" t="inlineStr"/>
-      <c r="O10" s="16" t="inlineStr"/>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q10" s="16" t="inlineStr"/>
-      <c r="R10" s="16" t="inlineStr"/>
-      <c r="S10" s="16" t="inlineStr"/>
-      <c r="T10" s="16" t="inlineStr"/>
-      <c r="U10" s="16" t="inlineStr"/>
-      <c r="V10" s="16" t="inlineStr"/>
-      <c r="W10" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$8,112万
-$44,866/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
-      <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr"/>
-      <c r="O11" s="16" t="inlineStr"/>
-      <c r="P11" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,230万
-$34,613/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="Q11" s="16" t="inlineStr"/>
-      <c r="R11" s="16" t="inlineStr"/>
-      <c r="S11" s="16" t="inlineStr"/>
-      <c r="T11" s="16" t="inlineStr"/>
-      <c r="U11" s="16" t="inlineStr"/>
-      <c r="V11" s="16" t="inlineStr"/>
-      <c r="W11" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$10,510万
-$47,132/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$8,018万
-$44,345/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
-      <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="16" t="inlineStr"/>
-      <c r="O12" s="16" t="inlineStr"/>
-      <c r="P12" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,818万
-$38,504/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="Q12" s="16" t="inlineStr"/>
-      <c r="R12" s="16" t="inlineStr"/>
-      <c r="S12" s="16" t="inlineStr"/>
-      <c r="T12" s="16" t="inlineStr"/>
-      <c r="U12" s="16" t="inlineStr"/>
-      <c r="V12" s="16" t="inlineStr"/>
-      <c r="W12" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
-      <c r="M13" s="16" t="inlineStr"/>
-      <c r="N13" s="16" t="inlineStr"/>
-      <c r="O13" s="16" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="Q13" s="16" t="inlineStr"/>
-      <c r="R13" s="16" t="inlineStr"/>
-      <c r="S13" s="16" t="inlineStr"/>
-      <c r="T13" s="16" t="inlineStr"/>
-      <c r="U13" s="16" t="inlineStr"/>
-      <c r="V13" s="16" t="inlineStr"/>
-      <c r="W13" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$9,525万
-$42,713/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,512万
-$41,550/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr"/>
-      <c r="I14" s="16" t="inlineStr"/>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
-      <c r="M14" s="16" t="inlineStr"/>
-      <c r="N14" s="16" t="inlineStr"/>
-      <c r="O14" s="16" t="inlineStr"/>
-      <c r="P14" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,671万
-$37,530/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="Q14" s="16" t="inlineStr"/>
-      <c r="R14" s="16" t="inlineStr"/>
-      <c r="S14" s="16" t="inlineStr"/>
-      <c r="T14" s="16" t="inlineStr"/>
-      <c r="U14" s="16" t="inlineStr"/>
-      <c r="V14" s="16" t="inlineStr"/>
-      <c r="W14" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="16" t="inlineStr"/>
-      <c r="O15" s="16" t="inlineStr"/>
-      <c r="P15" s="17" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q15" s="16" t="inlineStr"/>
-      <c r="R15" s="16" t="inlineStr"/>
-      <c r="S15" s="16" t="inlineStr"/>
-      <c r="T15" s="16" t="inlineStr"/>
-      <c r="U15" s="16" t="inlineStr"/>
-      <c r="V15" s="16" t="inlineStr"/>
-      <c r="W15" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$9,321万
-$41,797/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,006万
-$38,750/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
-      <c r="M16" s="16" t="inlineStr"/>
-      <c r="N16" s="16" t="inlineStr"/>
-      <c r="O16" s="16" t="inlineStr"/>
-      <c r="P16" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$6,222万
-$41,176/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="Q16" s="16" t="inlineStr"/>
-      <c r="R16" s="16" t="inlineStr"/>
-      <c r="S16" s="16" t="inlineStr"/>
-      <c r="T16" s="16" t="inlineStr"/>
-      <c r="U16" s="16" t="inlineStr"/>
-      <c r="V16" s="16" t="inlineStr"/>
-      <c r="W16" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$9,332万
-$41,850/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,239万
-$40,040/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr"/>
-      <c r="N17" s="16" t="inlineStr"/>
-      <c r="O17" s="16" t="inlineStr"/>
-      <c r="P17" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,553万
-$36,749/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="Q17" s="16" t="inlineStr"/>
-      <c r="R17" s="16" t="inlineStr"/>
-      <c r="S17" s="16" t="inlineStr"/>
-      <c r="T17" s="16" t="inlineStr"/>
-      <c r="U17" s="16" t="inlineStr"/>
-      <c r="V17" s="16" t="inlineStr"/>
-      <c r="W17" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$9,228万
-$41,381/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,230万
-$39,989/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr"/>
-      <c r="O18" s="16" t="inlineStr"/>
-      <c r="P18" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,485万
-$36,299/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="Q18" s="16" t="inlineStr"/>
-      <c r="R18" s="16" t="inlineStr"/>
-      <c r="S18" s="16" t="inlineStr"/>
-      <c r="T18" s="16" t="inlineStr"/>
-      <c r="U18" s="16" t="inlineStr"/>
-      <c r="V18" s="16" t="inlineStr"/>
-      <c r="W18" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr"/>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,096万
-$39,246/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr"/>
-      <c r="O19" s="16" t="inlineStr"/>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q19" s="16" t="inlineStr"/>
-      <c r="R19" s="16" t="inlineStr"/>
-      <c r="S19" s="16" t="inlineStr"/>
-      <c r="T19" s="16" t="inlineStr"/>
-      <c r="U19" s="16" t="inlineStr"/>
-      <c r="V19" s="16" t="inlineStr"/>
-      <c r="W19" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$8,977万
-$40,257/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,060万
-$39,050/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr"/>
-      <c r="I20" s="16" t="inlineStr"/>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr"/>
-      <c r="N20" s="16" t="inlineStr"/>
-      <c r="O20" s="16" t="inlineStr"/>
-      <c r="P20" s="19" t="inlineStr">
-        <is>
-          <t>C | 1511呎 (4+房)
-$5,419万
-$35,863/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="Q20" s="16" t="inlineStr"/>
-      <c r="R20" s="16" t="inlineStr"/>
-      <c r="S20" s="16" t="inlineStr"/>
-      <c r="T20" s="16" t="inlineStr"/>
-      <c r="U20" s="16" t="inlineStr"/>
-      <c r="V20" s="16" t="inlineStr"/>
-      <c r="W20" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 2230呎 (4+房)
-$8,807万
-$39,494/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>B | 1808呎 (4+房)
-$7,380万
-$40,821/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr"/>
-      <c r="I21" s="16" t="inlineStr"/>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr"/>
-      <c r="M21" s="16" t="inlineStr"/>
-      <c r="N21" s="16" t="inlineStr"/>
-      <c r="O21" s="16" t="inlineStr"/>
-      <c r="P21" s="19" t="inlineStr">
-        <is>
-          <t>C | 1513呎 (4+房)
-$5,473万
-$36,174/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="Q21" s="16" t="inlineStr"/>
-      <c r="R21" s="16" t="inlineStr"/>
-      <c r="S21" s="16" t="inlineStr"/>
-      <c r="T21" s="16" t="inlineStr"/>
-      <c r="U21" s="16" t="inlineStr"/>
-      <c r="V21" s="16" t="inlineStr"/>
-      <c r="W21" s="17" t="inlineStr">
-        <is>
-          <t>D | 1785呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,570万
-$34,896/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$979万
-$31,783/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$827万
-$27,461/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,427万
-$29,599/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$814万
-$26,412/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$852万
-$27,747/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$938万
-$30,866/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O22" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P22" s="16" t="inlineStr"/>
-      <c r="Q22" s="16" t="inlineStr"/>
-      <c r="R22" s="16" t="inlineStr"/>
-      <c r="S22" s="16" t="inlineStr"/>
-      <c r="T22" s="16" t="inlineStr"/>
-      <c r="U22" s="16" t="inlineStr"/>
-      <c r="V22" s="16" t="inlineStr"/>
-      <c r="W22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,570万
-$34,896/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$978万
-$31,751/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$821万
-$27,276/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,421万
-$29,485/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$807万
-$26,202/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$842万
-$27,417/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$927万
-$30,499/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P23" s="16" t="inlineStr"/>
-      <c r="Q23" s="16" t="inlineStr"/>
-      <c r="R23" s="16" t="inlineStr"/>
-      <c r="S23" s="16" t="inlineStr"/>
-      <c r="T23" s="16" t="inlineStr"/>
-      <c r="U23" s="16" t="inlineStr"/>
-      <c r="V23" s="16" t="inlineStr"/>
-      <c r="W23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$869万
-$28,882/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,651万
-$34,260/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$890万
-$28,882/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$927万
-$30,197/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$918万
-$30,197/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr"/>
-      <c r="Q24" s="16" t="inlineStr"/>
-      <c r="R24" s="16" t="inlineStr"/>
-      <c r="S24" s="16" t="inlineStr"/>
-      <c r="T24" s="16" t="inlineStr"/>
-      <c r="U24" s="16" t="inlineStr"/>
-      <c r="V24" s="16" t="inlineStr"/>
-      <c r="W24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr"/>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,658万
-$36,853/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$810万
-$26,898/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,568万
-$32,529/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$796万
-$25,839/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K25" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,428万
-$31,794/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$826万
-$26,908/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$909万
-$29,898/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N25" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,404万
-$30,544/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O25" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr"/>
-      <c r="Q25" s="16" t="inlineStr"/>
-      <c r="R25" s="16" t="inlineStr"/>
-      <c r="S25" s="16" t="inlineStr"/>
-      <c r="T25" s="16" t="inlineStr"/>
-      <c r="U25" s="16" t="inlineStr"/>
-      <c r="V25" s="16" t="inlineStr"/>
-      <c r="W25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr"/>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,656万
-$36,804/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,026万
-$33,320/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$805万
-$26,737/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,427万
-$29,605/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$790万
-$25,652/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,391万
-$30,976/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$909万
-$29,602/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$900万
-$29,601/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,405万
-$30,564/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O26" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P26" s="16" t="inlineStr"/>
-      <c r="Q26" s="16" t="inlineStr"/>
-      <c r="R26" s="16" t="inlineStr"/>
-      <c r="S26" s="16" t="inlineStr"/>
-      <c r="T26" s="16" t="inlineStr"/>
-      <c r="U26" s="16" t="inlineStr"/>
-      <c r="V26" s="16" t="inlineStr"/>
-      <c r="W26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,652万
-$36,700/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$770万
-$25,581/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,550万
-$32,161/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$787万
-$25,550/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$889万
-$28,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O27" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P27" s="16" t="inlineStr"/>
-      <c r="Q27" s="16" t="inlineStr"/>
-      <c r="R27" s="16" t="inlineStr"/>
-      <c r="S27" s="16" t="inlineStr"/>
-      <c r="T27" s="16" t="inlineStr"/>
-      <c r="U27" s="16" t="inlineStr"/>
-      <c r="V27" s="16" t="inlineStr"/>
-      <c r="W27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr"/>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,646万
-$36,578/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,105万
-$35,886/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$766万
-$25,446/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,337万
-$27,732/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$785万
-$25,480/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,372万
-$30,557/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,401万
-$30,508/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O28" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P28" s="16" t="inlineStr"/>
-      <c r="Q28" s="16" t="inlineStr"/>
-      <c r="R28" s="16" t="inlineStr"/>
-      <c r="S28" s="16" t="inlineStr"/>
-      <c r="T28" s="16" t="inlineStr"/>
-      <c r="U28" s="16" t="inlineStr"/>
-      <c r="V28" s="16" t="inlineStr"/>
-      <c r="W28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,088万
-$35,308/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$849万
-$28,198/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$869万
-$28,198/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O29" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P29" s="16" t="inlineStr"/>
-      <c r="Q29" s="16" t="inlineStr"/>
-      <c r="R29" s="16" t="inlineStr"/>
-      <c r="S29" s="16" t="inlineStr"/>
-      <c r="T29" s="16" t="inlineStr"/>
-      <c r="U29" s="16" t="inlineStr"/>
-      <c r="V29" s="16" t="inlineStr"/>
-      <c r="W29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr"/>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,631万
-$36,238/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr"/>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$762万
-$25,327/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,310万
-$27,178/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$780万
-$25,328/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O30" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P30" s="16" t="inlineStr"/>
-      <c r="Q30" s="16" t="inlineStr"/>
-      <c r="R30" s="16" t="inlineStr"/>
-      <c r="S30" s="16" t="inlineStr"/>
-      <c r="T30" s="16" t="inlineStr"/>
-      <c r="U30" s="16" t="inlineStr"/>
-      <c r="V30" s="16" t="inlineStr"/>
-      <c r="W30" s="16" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,595万
-$35,440/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$947万
-$30,732/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr"/>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$761万
-$25,276/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,282万
-$26,604/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$779万
-$25,277/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,334万
-$29,711/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$825万
-$26,881/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,312万
-$29,376/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O31" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P31" s="16" t="inlineStr"/>
-      <c r="Q31" s="16" t="inlineStr"/>
-      <c r="R31" s="16" t="inlineStr"/>
-      <c r="S31" s="16" t="inlineStr"/>
-      <c r="T31" s="16" t="inlineStr"/>
-      <c r="U31" s="16" t="inlineStr"/>
-      <c r="V31" s="16" t="inlineStr"/>
-      <c r="W31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,043万
-$33,863/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr"/>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$759万
-$25,226/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$777万
-$25,226/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$825万
-$26,860/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N32" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,305万
-$29,288/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O32" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P32" s="16" t="inlineStr"/>
-      <c r="Q32" s="16" t="inlineStr"/>
-      <c r="R32" s="16" t="inlineStr"/>
-      <c r="S32" s="16" t="inlineStr"/>
-      <c r="T32" s="16" t="inlineStr"/>
-      <c r="U32" s="16" t="inlineStr"/>
-      <c r="V32" s="16" t="inlineStr"/>
-      <c r="W32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr"/>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,035万
-$33,610/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr"/>
-      <c r="H33" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$758万
-$25,175/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,278万
-$26,519/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$774万
-$25,144/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N33" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,387万
-$30,326/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="O33" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P33" s="16" t="inlineStr"/>
-      <c r="Q33" s="16" t="inlineStr"/>
-      <c r="R33" s="16" t="inlineStr"/>
-      <c r="S33" s="16" t="inlineStr"/>
-      <c r="T33" s="16" t="inlineStr"/>
-      <c r="U33" s="16" t="inlineStr"/>
-      <c r="V33" s="16" t="inlineStr"/>
-      <c r="W33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,600万
-$35,556/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$756万
-$25,125/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,256万
-$26,063/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$774万
-$25,126/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,311万
-$29,190/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L34" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N34" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,258万
-$28,689/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O34" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P34" s="16" t="inlineStr"/>
-      <c r="Q34" s="16" t="inlineStr"/>
-      <c r="R34" s="16" t="inlineStr"/>
-      <c r="S34" s="16" t="inlineStr"/>
-      <c r="T34" s="16" t="inlineStr"/>
-      <c r="U34" s="16" t="inlineStr"/>
-      <c r="V34" s="16" t="inlineStr"/>
-      <c r="W34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr"/>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,576万
-$35,026/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$753万
-$25,024/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$771万
-$25,025/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K35" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$823万
-$26,816/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N35" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O35" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P35" s="16" t="inlineStr"/>
-      <c r="Q35" s="16" t="inlineStr"/>
-      <c r="R35" s="16" t="inlineStr"/>
-      <c r="S35" s="16" t="inlineStr"/>
-      <c r="T35" s="16" t="inlineStr"/>
-      <c r="U35" s="16" t="inlineStr"/>
-      <c r="V35" s="16" t="inlineStr"/>
-      <c r="W35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,526万
-$33,900/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="H36" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$750万
-$24,924/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,239万
-$25,705/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$768万
-$24,925/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K36" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,305万
-$29,062/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="L36" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$820万
-$26,708/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,296万
-$29,180/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="O36" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P36" s="16" t="inlineStr"/>
-      <c r="Q36" s="16" t="inlineStr"/>
-      <c r="R36" s="16" t="inlineStr"/>
-      <c r="S36" s="16" t="inlineStr"/>
-      <c r="T36" s="16" t="inlineStr"/>
-      <c r="U36" s="16" t="inlineStr"/>
-      <c r="V36" s="16" t="inlineStr"/>
-      <c r="W36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$829万
-$27,527/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$848万
-$27,528/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N37" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O37" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P37" s="16" t="inlineStr"/>
-      <c r="Q37" s="16" t="inlineStr"/>
-      <c r="R37" s="16" t="inlineStr"/>
-      <c r="S37" s="16" t="inlineStr"/>
-      <c r="T37" s="16" t="inlineStr"/>
-      <c r="U37" s="16" t="inlineStr"/>
-      <c r="V37" s="16" t="inlineStr"/>
-      <c r="W37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr"/>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,011万
-$32,811/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$772万
-$25,635/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,417万
-$29,400/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$758万
-$24,626/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K38" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L38" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N38" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O38" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P38" s="16" t="inlineStr"/>
-      <c r="Q38" s="16" t="inlineStr"/>
-      <c r="R38" s="16" t="inlineStr"/>
-      <c r="S38" s="16" t="inlineStr"/>
-      <c r="T38" s="16" t="inlineStr"/>
-      <c r="U38" s="16" t="inlineStr"/>
-      <c r="V38" s="16" t="inlineStr"/>
-      <c r="W38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$1,003万
-$32,578/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr"/>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$765万
-$25,430/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,220万
-$25,315/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$752万
-$24,429/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K39" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L39" s="17" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N39" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,184万
-$27,750/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O39" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P39" s="16" t="inlineStr"/>
-      <c r="Q39" s="16" t="inlineStr"/>
-      <c r="R39" s="16" t="inlineStr"/>
-      <c r="S39" s="16" t="inlineStr"/>
-      <c r="T39" s="16" t="inlineStr"/>
-      <c r="U39" s="16" t="inlineStr"/>
-      <c r="V39" s="16" t="inlineStr"/>
-      <c r="W39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr"/>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$899万
-$29,181/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$758万
-$25,193/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,212万
-$25,145/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$746万
-$24,233/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,240万
-$27,627/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$793万
-$25,819/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M40" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$785万
-$25,818/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,169万
-$27,555/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O40" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P40" s="16" t="inlineStr"/>
-      <c r="Q40" s="16" t="inlineStr"/>
-      <c r="R40" s="16" t="inlineStr"/>
-      <c r="S40" s="16" t="inlineStr"/>
-      <c r="T40" s="16" t="inlineStr"/>
-      <c r="U40" s="16" t="inlineStr"/>
-      <c r="V40" s="16" t="inlineStr"/>
-      <c r="W40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr"/>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,380万
-$30,671/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$861万
-$27,963/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr"/>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$721万
-$23,946/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,210万
-$25,104/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$738万
-$23,946/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-$1,260万
-$28,062/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$785万
-$25,560/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M41" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$776万
-$25,527/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="N41" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,130万
-$27,062/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="O41" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P41" s="16" t="inlineStr"/>
-      <c r="Q41" s="16" t="inlineStr"/>
-      <c r="R41" s="16" t="inlineStr"/>
-      <c r="S41" s="16" t="inlineStr"/>
-      <c r="T41" s="16" t="inlineStr"/>
-      <c r="U41" s="16" t="inlineStr"/>
-      <c r="V41" s="16" t="inlineStr"/>
-      <c r="W41" s="16" t="inlineStr"/>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr"/>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>A2 | 450呎 (2房)
-$1,214万
-$26,979/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>A3 | 308呎 (1房)
-$845万
-$27,432/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 612呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr"/>
-      <c r="H42" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 301呎 (1房)
-$681万
-$22,617/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>B10 | 482呎 (2房)
-$1,198万
-$24,861/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 308呎 (1房)
-$697万
-$22,618/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K42" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 307呎 (1房)
-$777万
-$25,304/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 304呎 (1房)
-$769万
-$25,304/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="N42" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 787呎 (3房)
-$2,157万
-$27,409/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="O42" s="19" t="inlineStr">
-        <is>
-          <t>B9 | 296呎 (1房)
-$730万
-$24,675/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P42" s="16" t="inlineStr"/>
-      <c r="Q42" s="16" t="inlineStr"/>
-      <c r="R42" s="16" t="inlineStr"/>
-      <c r="S42" s="16" t="inlineStr"/>
-      <c r="T42" s="16" t="inlineStr"/>
-      <c r="U42" s="16" t="inlineStr"/>
-      <c r="V42" s="16" t="inlineStr"/>
-      <c r="W42" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:W1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天玺．天第2期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>270 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>84 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>145 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>PSH A</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>PSH B</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>PSV A</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>PSV B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>49&amp;50/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
-      <c r="L6" s="16" t="inlineStr"/>
-      <c r="M6" s="16" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr"/>
-      <c r="O6" s="16" t="inlineStr"/>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t>PSH A | 3936呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="Q6" s="20" t="inlineStr">
-        <is>
-          <t>PSH B | 3553呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R6" s="16" t="inlineStr"/>
-      <c r="S6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
-      <c r="L7" s="16" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr"/>
-      <c r="O7" s="16" t="inlineStr"/>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" s="17" t="inlineStr">
-        <is>
-          <t>PSV A | 2989呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr">
-        <is>
-          <t>PSV B | 2765呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="16" t="inlineStr"/>
-      <c r="N8" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$5,225万
-$42,586/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr"/>
-      <c r="Q8" s="16" t="inlineStr"/>
-      <c r="R8" s="16" t="inlineStr"/>
-      <c r="S8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr"/>
-      <c r="M9" s="16" t="inlineStr"/>
-      <c r="N9" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,824万
-$39,314/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O9" s="18" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr"/>
-      <c r="Q9" s="16" t="inlineStr"/>
-      <c r="R9" s="16" t="inlineStr"/>
-      <c r="S9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="16" t="inlineStr"/>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
-      <c r="M10" s="16" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr"/>
-      <c r="Q10" s="16" t="inlineStr"/>
-      <c r="R10" s="16" t="inlineStr"/>
-      <c r="S10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-$8,348万
-$42,055/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
-      <c r="M11" s="16" t="inlineStr"/>
-      <c r="N11" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,330万
-$35,289/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O11" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$5,191万
-$38,028/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr"/>
-      <c r="Q11" s="16" t="inlineStr"/>
-      <c r="R11" s="16" t="inlineStr"/>
-      <c r="S11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
-      <c r="M12" s="16" t="inlineStr"/>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr"/>
-      <c r="Q12" s="16" t="inlineStr"/>
-      <c r="R12" s="16" t="inlineStr"/>
-      <c r="S12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
-      <c r="M13" s="16" t="inlineStr"/>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,668万
-$38,044/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$5,020万
-$36,777/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr"/>
-      <c r="R13" s="16" t="inlineStr"/>
-      <c r="S13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr"/>
-      <c r="I14" s="16" t="inlineStr"/>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
-      <c r="M14" s="16" t="inlineStr"/>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$4,934万
-$36,147/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr"/>
-      <c r="Q14" s="16" t="inlineStr"/>
-      <c r="R14" s="16" t="inlineStr"/>
-      <c r="S14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$4,908万
-$35,956/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr"/>
-      <c r="Q15" s="16" t="inlineStr"/>
-      <c r="R15" s="16" t="inlineStr"/>
-      <c r="S15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
-      <c r="M16" s="16" t="inlineStr"/>
-      <c r="N16" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,470万
-$36,430/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr"/>
-      <c r="R16" s="16" t="inlineStr"/>
-      <c r="S16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr"/>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O17" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$4,808万
-$35,223/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P17" s="16" t="inlineStr"/>
-      <c r="Q17" s="16" t="inlineStr"/>
-      <c r="R17" s="16" t="inlineStr"/>
-      <c r="S17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr"/>
-      <c r="N18" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,450万
-$36,267/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="O18" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$4,800万
-$35,165/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="P18" s="16" t="inlineStr"/>
-      <c r="Q18" s="16" t="inlineStr"/>
-      <c r="R18" s="16" t="inlineStr"/>
-      <c r="S18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr"/>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr"/>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O19" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr"/>
-      <c r="Q19" s="16" t="inlineStr"/>
-      <c r="R19" s="16" t="inlineStr"/>
-      <c r="S19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr"/>
-      <c r="I20" s="16" t="inlineStr"/>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr"/>
-      <c r="N20" s="19" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-$4,448万
-$36,251/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="O20" s="19" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-$4,789万
-$35,084/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr"/>
-      <c r="Q20" s="16" t="inlineStr"/>
-      <c r="R20" s="16" t="inlineStr"/>
-      <c r="S20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1985呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>B | 1993呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr"/>
-      <c r="I21" s="16" t="inlineStr"/>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr"/>
-      <c r="M21" s="16" t="inlineStr"/>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>C | 1227呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>D | 1365呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="P21" s="16" t="inlineStr"/>
-      <c r="Q21" s="16" t="inlineStr"/>
-      <c r="R21" s="16" t="inlineStr"/>
-      <c r="S21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,572万
-$32,888/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$930万
-$30,809/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$958万
-$32,043/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$828万
-$27,695/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$826万
-$27,810/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="inlineStr"/>
-      <c r="O22" s="16" t="inlineStr"/>
-      <c r="P22" s="16" t="inlineStr"/>
-      <c r="Q22" s="16" t="inlineStr"/>
-      <c r="R22" s="16" t="inlineStr"/>
-      <c r="S22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr"/>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,710万
-$40,859/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,566万
-$32,761/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$927万
-$30,686/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$954万
-$31,915/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$859万
-$28,723/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$824万
-$27,732/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N23" s="16" t="inlineStr"/>
-      <c r="O23" s="16" t="inlineStr"/>
-      <c r="P23" s="16" t="inlineStr"/>
-      <c r="Q23" s="16" t="inlineStr"/>
-      <c r="R23" s="16" t="inlineStr"/>
-      <c r="S23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,560万
-$32,644/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$919万
-$30,443/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$910万
-$30,442/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$910万
-$30,442/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$908万
-$30,569/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr"/>
-      <c r="O24" s="16" t="inlineStr"/>
-      <c r="P24" s="16" t="inlineStr"/>
-      <c r="Q24" s="16" t="inlineStr"/>
-      <c r="R24" s="16" t="inlineStr"/>
-      <c r="S24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr"/>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,657万
-$40,279/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,555万
-$32,529/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$915万
-$30,312/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$906万
-$30,312/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K25" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$816万
-$27,280/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$814万
-$27,394/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr"/>
-      <c r="O25" s="16" t="inlineStr"/>
-      <c r="P25" s="16" t="inlineStr"/>
-      <c r="Q25" s="16" t="inlineStr"/>
-      <c r="R25" s="16" t="inlineStr"/>
-      <c r="S25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr"/>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,545万
-$39,040/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,540万
-$32,226/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$913万
-$30,228/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$812万
-$27,172/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$812万
-$27,172/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$810万
-$27,285/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr"/>
-      <c r="O26" s="16" t="inlineStr"/>
-      <c r="P26" s="16" t="inlineStr"/>
-      <c r="Q26" s="16" t="inlineStr"/>
-      <c r="R26" s="16" t="inlineStr"/>
-      <c r="S26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr"/>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,626万
-$39,932/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,537万
-$32,161/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$899万
-$29,784/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$800万
-$26,772/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$800万
-$26,772/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$798万
-$26,884/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N27" s="16" t="inlineStr"/>
-      <c r="O27" s="16" t="inlineStr"/>
-      <c r="P27" s="16" t="inlineStr"/>
-      <c r="Q27" s="16" t="inlineStr"/>
-      <c r="R27" s="16" t="inlineStr"/>
-      <c r="S27" s="16" t="inlineStr"/>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr"/>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,605万
-$39,705/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$790万
-$26,428/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$818万
-$27,551/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr"/>
-      <c r="O28" s="16" t="inlineStr"/>
-      <c r="P28" s="16" t="inlineStr"/>
-      <c r="Q28" s="16" t="inlineStr"/>
-      <c r="R28" s="16" t="inlineStr"/>
-      <c r="S28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$868万
-$29,016/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$898万
-$30,248/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N29" s="16" t="inlineStr"/>
-      <c r="O29" s="16" t="inlineStr"/>
-      <c r="P29" s="16" t="inlineStr"/>
-      <c r="Q29" s="16" t="inlineStr"/>
-      <c r="R29" s="16" t="inlineStr"/>
-      <c r="S29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr"/>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,501万
-$38,558/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K30" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$768万
-$25,670/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$795万
-$26,760/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="inlineStr"/>
-      <c r="O30" s="16" t="inlineStr"/>
-      <c r="P30" s="16" t="inlineStr"/>
-      <c r="Q30" s="16" t="inlineStr"/>
-      <c r="R30" s="16" t="inlineStr"/>
-      <c r="S30" s="16" t="inlineStr"/>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr"/>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,335万
-$36,730/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr"/>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$766万
-$25,618/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$793万
-$26,706/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="inlineStr"/>
-      <c r="O31" s="16" t="inlineStr"/>
-      <c r="P31" s="16" t="inlineStr"/>
-      <c r="Q31" s="16" t="inlineStr"/>
-      <c r="R31" s="16" t="inlineStr"/>
-      <c r="S31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr"/>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$764万
-$25,567/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$791万
-$26,620/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N32" s="16" t="inlineStr"/>
-      <c r="O32" s="16" t="inlineStr"/>
-      <c r="P32" s="16" t="inlineStr"/>
-      <c r="Q32" s="16" t="inlineStr"/>
-      <c r="R32" s="16" t="inlineStr"/>
-      <c r="S32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr"/>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,557万
-$39,172/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr"/>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$890万
-$29,470/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$792万
-$26,489/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K33" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$763万
-$25,516/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$789万
-$26,566/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N33" s="16" t="inlineStr"/>
-      <c r="O33" s="16" t="inlineStr"/>
-      <c r="P33" s="16" t="inlineStr"/>
-      <c r="Q33" s="16" t="inlineStr"/>
-      <c r="R33" s="16" t="inlineStr"/>
-      <c r="S33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr"/>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr"/>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$799万
-$26,470/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$789万
-$26,403/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$790万
-$26,436/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$787万
-$26,513/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N34" s="16" t="inlineStr"/>
-      <c r="O34" s="16" t="inlineStr"/>
-      <c r="P34" s="16" t="inlineStr"/>
-      <c r="Q34" s="16" t="inlineStr"/>
-      <c r="R34" s="16" t="inlineStr"/>
-      <c r="S34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr"/>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,610万
-$39,758/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$796万
-$26,364/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$787万
-$26,330/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K35" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$787万
-$26,330/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$785万
-$26,440/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N35" s="16" t="inlineStr"/>
-      <c r="O35" s="16" t="inlineStr"/>
-      <c r="P35" s="16" t="inlineStr"/>
-      <c r="Q35" s="16" t="inlineStr"/>
-      <c r="R35" s="16" t="inlineStr"/>
-      <c r="S35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr"/>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,366万
-$37,070/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr"/>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$792万
-$26,225/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$784万
-$26,225/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K36" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$783万
-$26,192/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L36" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$782万
-$26,334/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N36" s="16" t="inlineStr"/>
-      <c r="O36" s="16" t="inlineStr"/>
-      <c r="P36" s="16" t="inlineStr"/>
-      <c r="Q36" s="16" t="inlineStr"/>
-      <c r="R36" s="16" t="inlineStr"/>
-      <c r="S36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr"/>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$875万
-$28,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$866万
-$28,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$866万
-$28,964/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$864万
-$29,085/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N37" s="16" t="inlineStr"/>
-      <c r="O37" s="16" t="inlineStr"/>
-      <c r="P37" s="16" t="inlineStr"/>
-      <c r="Q37" s="16" t="inlineStr"/>
-      <c r="R37" s="16" t="inlineStr"/>
-      <c r="S37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr"/>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,136万
-$34,543/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr"/>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,405万
-$29,400/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$782万
-$25,878/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$775万
-$25,911/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$775万
-$25,911/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$773万
-$26,019/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N38" s="16" t="inlineStr"/>
-      <c r="O38" s="16" t="inlineStr"/>
-      <c r="P38" s="16" t="inlineStr"/>
-      <c r="Q38" s="16" t="inlineStr"/>
-      <c r="R38" s="16" t="inlineStr"/>
-      <c r="S38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr"/>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,033万
-$33,401/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr"/>
-      <c r="H39" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,386万
-$28,989/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$776万
-$25,704/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$769万
-$25,703/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K39" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$769万
-$25,703/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$767万
-$25,810/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N39" s="16" t="inlineStr"/>
-      <c r="O39" s="16" t="inlineStr"/>
-      <c r="P39" s="16" t="inlineStr"/>
-      <c r="Q39" s="16" t="inlineStr"/>
-      <c r="R39" s="16" t="inlineStr"/>
-      <c r="S39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr"/>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,064万
-$33,745/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr"/>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,367万
-$28,588/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$837万
-$27,706/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$745万
-$24,902/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$718万
-$23,998/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$716万
-$24,098/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M40" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="inlineStr"/>
-      <c r="O40" s="16" t="inlineStr"/>
-      <c r="P40" s="16" t="inlineStr"/>
-      <c r="Q40" s="16" t="inlineStr"/>
-      <c r="R40" s="16" t="inlineStr"/>
-      <c r="S40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr"/>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 908呎 (4+房)
-$3,012万
-$33,172/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr"/>
-      <c r="H41" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,350万
-$28,242/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$746万
-$24,686/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$738万
-$24,685/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$710万
-$23,758/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$709万
-$23,857/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N41" s="16" t="inlineStr"/>
-      <c r="O41" s="16" t="inlineStr"/>
-      <c r="P41" s="16" t="inlineStr"/>
-      <c r="Q41" s="16" t="inlineStr"/>
-      <c r="R41" s="16" t="inlineStr"/>
-      <c r="S41" s="16" t="inlineStr"/>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr"/>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>A1 | 874呎 (4+房)
-$2,659万
-$30,427/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr"/>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
-$1,320万
-$27,623/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>B2 | 302呎 (1房)
-$719万
-$23,809/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 299呎 (1房)
-$712万
-$23,808/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="inlineStr">
-        <is>
-          <t>B5 | 299呎 (1房)
-$685万
-$22,923/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>B6 | 297呎 (1房)
-$683万
-$22,985/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M42" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 455呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="inlineStr"/>
-      <c r="O42" s="16" t="inlineStr"/>
-      <c r="P42" s="16" t="inlineStr"/>
-      <c r="Q42" s="16" t="inlineStr"/>
-      <c r="R42" s="16" t="inlineStr"/>
-      <c r="S42" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -28673,4 +28870,6528 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:W41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>CSH A</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>CSH C</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>CSH D</t>
+        </is>
+      </c>
+      <c r="T4" s="19" t="inlineStr">
+        <is>
+          <t>CSV A</t>
+        </is>
+      </c>
+      <c r="U4" s="19" t="inlineStr">
+        <is>
+          <t>CSV C</t>
+        </is>
+      </c>
+      <c r="V4" s="19" t="inlineStr">
+        <is>
+          <t>CSV D</t>
+        </is>
+      </c>
+      <c r="W4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>49&amp;50</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+      <c r="K5" s="20" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr"/>
+      <c r="M5" s="20" t="inlineStr"/>
+      <c r="N5" s="20" t="inlineStr"/>
+      <c r="O5" s="20" t="inlineStr"/>
+      <c r="P5" s="20" t="inlineStr"/>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>CSH A | 4306呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t>CSH C | 2189呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S5" s="21" t="inlineStr">
+        <is>
+          <t>CSH D | 2647呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="T5" s="20" t="inlineStr"/>
+      <c r="U5" s="20" t="inlineStr"/>
+      <c r="V5" s="20" t="inlineStr"/>
+      <c r="W5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t>CSV A | 3110呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="U6" s="21" t="inlineStr">
+        <is>
+          <t>CSV C | 1511呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="V6" s="21" t="inlineStr">
+        <is>
+          <t>CSV D | 1786呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="W6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="20" t="inlineStr"/>
+      <c r="W7" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$8281万
+$45,803/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5435万
+$35,970/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="20" t="inlineStr"/>
+      <c r="W8" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
+      <c r="W9" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$8112万
+$44,866/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5230万
+$34,613/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="20" t="inlineStr"/>
+      <c r="W10" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$10510万
+$47,132/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$8018万
+$44,345/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5818万
+$38,504/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
+      <c r="W11" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="24" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+      <c r="W12" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$9525万
+$42,713/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7512万
+$41,550/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5671万
+$37,530/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="20" t="inlineStr"/>
+      <c r="W13" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr"/>
+      <c r="N14" s="20" t="inlineStr"/>
+      <c r="O14" s="20" t="inlineStr"/>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="20" t="inlineStr"/>
+      <c r="T14" s="20" t="inlineStr"/>
+      <c r="U14" s="20" t="inlineStr"/>
+      <c r="V14" s="20" t="inlineStr"/>
+      <c r="W14" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$9321万
+$41,797/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7006万
+$38,750/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+      <c r="K15" s="20" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr"/>
+      <c r="M15" s="20" t="inlineStr"/>
+      <c r="N15" s="20" t="inlineStr"/>
+      <c r="O15" s="20" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$6222万
+$41,176/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="20" t="inlineStr"/>
+      <c r="T15" s="20" t="inlineStr"/>
+      <c r="U15" s="20" t="inlineStr"/>
+      <c r="V15" s="20" t="inlineStr"/>
+      <c r="W15" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$9332万
+$41,850/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7239万
+$40,040/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
+      <c r="K16" s="20" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr"/>
+      <c r="M16" s="20" t="inlineStr"/>
+      <c r="N16" s="20" t="inlineStr"/>
+      <c r="O16" s="20" t="inlineStr"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5553万
+$36,749/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="20" t="inlineStr"/>
+      <c r="T16" s="20" t="inlineStr"/>
+      <c r="U16" s="20" t="inlineStr"/>
+      <c r="V16" s="20" t="inlineStr"/>
+      <c r="W16" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$9228万
+$41,381/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7230万
+$39,989/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
+      <c r="K17" s="20" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr"/>
+      <c r="M17" s="20" t="inlineStr"/>
+      <c r="N17" s="20" t="inlineStr"/>
+      <c r="O17" s="20" t="inlineStr"/>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5485万
+$36,299/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="Q17" s="20" t="inlineStr"/>
+      <c r="R17" s="20" t="inlineStr"/>
+      <c r="S17" s="20" t="inlineStr"/>
+      <c r="T17" s="20" t="inlineStr"/>
+      <c r="U17" s="20" t="inlineStr"/>
+      <c r="V17" s="20" t="inlineStr"/>
+      <c r="W17" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7096万
+$39,246/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+      <c r="K18" s="20" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr"/>
+      <c r="M18" s="20" t="inlineStr"/>
+      <c r="N18" s="20" t="inlineStr"/>
+      <c r="O18" s="20" t="inlineStr"/>
+      <c r="P18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q18" s="20" t="inlineStr"/>
+      <c r="R18" s="20" t="inlineStr"/>
+      <c r="S18" s="20" t="inlineStr"/>
+      <c r="T18" s="20" t="inlineStr"/>
+      <c r="U18" s="20" t="inlineStr"/>
+      <c r="V18" s="20" t="inlineStr"/>
+      <c r="W18" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$8977万
+$40,257/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7060万
+$39,050/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
+      <c r="K19" s="20" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr"/>
+      <c r="M19" s="20" t="inlineStr"/>
+      <c r="N19" s="20" t="inlineStr"/>
+      <c r="O19" s="20" t="inlineStr"/>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>C | 1511呎 (4+房)
+$5419万
+$35,863/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr"/>
+      <c r="R19" s="20" t="inlineStr"/>
+      <c r="S19" s="20" t="inlineStr"/>
+      <c r="T19" s="20" t="inlineStr"/>
+      <c r="U19" s="20" t="inlineStr"/>
+      <c r="V19" s="20" t="inlineStr"/>
+      <c r="W19" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 2230呎 (4+房)
+$8807万
+$39,494/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1808呎 (4+房)
+$7380万
+$40,821/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
+      <c r="K20" s="20" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr"/>
+      <c r="M20" s="20" t="inlineStr"/>
+      <c r="N20" s="20" t="inlineStr"/>
+      <c r="O20" s="20" t="inlineStr"/>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>C | 1513呎 (4+房)
+$5473万
+$36,174/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="Q20" s="20" t="inlineStr"/>
+      <c r="R20" s="20" t="inlineStr"/>
+      <c r="S20" s="20" t="inlineStr"/>
+      <c r="T20" s="20" t="inlineStr"/>
+      <c r="U20" s="20" t="inlineStr"/>
+      <c r="V20" s="20" t="inlineStr"/>
+      <c r="W20" s="21" t="inlineStr">
+        <is>
+          <t>D | 1785呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1570万
+$34,896/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$979万
+$31,783/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$827万
+$27,461/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1427万
+$29,599/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$814万
+$26,412/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$852万
+$27,747/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M21" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$938万
+$30,866/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P21" s="20" t="inlineStr"/>
+      <c r="Q21" s="20" t="inlineStr"/>
+      <c r="R21" s="20" t="inlineStr"/>
+      <c r="S21" s="20" t="inlineStr"/>
+      <c r="T21" s="20" t="inlineStr"/>
+      <c r="U21" s="20" t="inlineStr"/>
+      <c r="V21" s="20" t="inlineStr"/>
+      <c r="W21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1570万
+$34,896/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$978万
+$31,751/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$821万
+$27,276/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1421万
+$29,485/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$807万
+$26,202/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$842万
+$27,417/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$927万
+$30,499/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P22" s="20" t="inlineStr"/>
+      <c r="Q22" s="20" t="inlineStr"/>
+      <c r="R22" s="20" t="inlineStr"/>
+      <c r="S22" s="20" t="inlineStr"/>
+      <c r="T22" s="20" t="inlineStr"/>
+      <c r="U22" s="20" t="inlineStr"/>
+      <c r="V22" s="20" t="inlineStr"/>
+      <c r="W22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$869万
+$28,882/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1651万
+$34,260/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$890万
+$28,882/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L23" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$927万
+$30,197/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M23" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$918万
+$30,197/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P23" s="20" t="inlineStr"/>
+      <c r="Q23" s="20" t="inlineStr"/>
+      <c r="R23" s="20" t="inlineStr"/>
+      <c r="S23" s="20" t="inlineStr"/>
+      <c r="T23" s="20" t="inlineStr"/>
+      <c r="U23" s="20" t="inlineStr"/>
+      <c r="V23" s="20" t="inlineStr"/>
+      <c r="W23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1658万
+$36,853/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$810万
+$26,898/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1568万
+$32,529/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$796万
+$25,839/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1428万
+$31,794/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$826万
+$26,908/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$909万
+$29,898/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N24" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2404万
+$30,544/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P24" s="20" t="inlineStr"/>
+      <c r="Q24" s="20" t="inlineStr"/>
+      <c r="R24" s="20" t="inlineStr"/>
+      <c r="S24" s="20" t="inlineStr"/>
+      <c r="T24" s="20" t="inlineStr"/>
+      <c r="U24" s="20" t="inlineStr"/>
+      <c r="V24" s="20" t="inlineStr"/>
+      <c r="W24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1656万
+$36,804/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1026万
+$33,320/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$805万
+$26,737/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1427万
+$29,605/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$790万
+$25,652/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1391万
+$30,976/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L25" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$909万
+$29,602/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M25" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$900万
+$29,601/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="N25" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2405万
+$30,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P25" s="20" t="inlineStr"/>
+      <c r="Q25" s="20" t="inlineStr"/>
+      <c r="R25" s="20" t="inlineStr"/>
+      <c r="S25" s="20" t="inlineStr"/>
+      <c r="T25" s="20" t="inlineStr"/>
+      <c r="U25" s="20" t="inlineStr"/>
+      <c r="V25" s="20" t="inlineStr"/>
+      <c r="W25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1652万
+$36,700/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr"/>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$770万
+$25,581/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1550万
+$32,161/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$787万
+$25,550/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$889万
+$28,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P26" s="20" t="inlineStr"/>
+      <c r="Q26" s="20" t="inlineStr"/>
+      <c r="R26" s="20" t="inlineStr"/>
+      <c r="S26" s="20" t="inlineStr"/>
+      <c r="T26" s="20" t="inlineStr"/>
+      <c r="U26" s="20" t="inlineStr"/>
+      <c r="V26" s="20" t="inlineStr"/>
+      <c r="W26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1646万
+$36,578/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1105万
+$35,886/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$766万
+$25,446/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1337万
+$27,732/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$785万
+$25,480/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1372万
+$30,557/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2401万
+$30,508/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P27" s="20" t="inlineStr"/>
+      <c r="Q27" s="20" t="inlineStr"/>
+      <c r="R27" s="20" t="inlineStr"/>
+      <c r="S27" s="20" t="inlineStr"/>
+      <c r="T27" s="20" t="inlineStr"/>
+      <c r="U27" s="20" t="inlineStr"/>
+      <c r="V27" s="20" t="inlineStr"/>
+      <c r="W27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1088万
+$35,308/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$849万
+$28,198/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$869万
+$28,198/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P28" s="20" t="inlineStr"/>
+      <c r="Q28" s="20" t="inlineStr"/>
+      <c r="R28" s="20" t="inlineStr"/>
+      <c r="S28" s="20" t="inlineStr"/>
+      <c r="T28" s="20" t="inlineStr"/>
+      <c r="U28" s="20" t="inlineStr"/>
+      <c r="V28" s="20" t="inlineStr"/>
+      <c r="W28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1631万
+$36,238/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr"/>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$762万
+$25,327/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1310万
+$27,178/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$780万
+$25,328/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P29" s="20" t="inlineStr"/>
+      <c r="Q29" s="20" t="inlineStr"/>
+      <c r="R29" s="20" t="inlineStr"/>
+      <c r="S29" s="20" t="inlineStr"/>
+      <c r="T29" s="20" t="inlineStr"/>
+      <c r="U29" s="20" t="inlineStr"/>
+      <c r="V29" s="20" t="inlineStr"/>
+      <c r="W29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1595万
+$35,440/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$947万
+$30,732/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$761万
+$25,276/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1282万
+$26,604/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$779万
+$25,277/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1334万
+$29,711/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$825万
+$26,881/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2312万
+$29,376/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P30" s="20" t="inlineStr"/>
+      <c r="Q30" s="20" t="inlineStr"/>
+      <c r="R30" s="20" t="inlineStr"/>
+      <c r="S30" s="20" t="inlineStr"/>
+      <c r="T30" s="20" t="inlineStr"/>
+      <c r="U30" s="20" t="inlineStr"/>
+      <c r="V30" s="20" t="inlineStr"/>
+      <c r="W30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1043万
+$33,863/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$759万
+$25,226/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$777万
+$25,226/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$825万
+$26,860/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2305万
+$29,288/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P31" s="20" t="inlineStr"/>
+      <c r="Q31" s="20" t="inlineStr"/>
+      <c r="R31" s="20" t="inlineStr"/>
+      <c r="S31" s="20" t="inlineStr"/>
+      <c r="T31" s="20" t="inlineStr"/>
+      <c r="U31" s="20" t="inlineStr"/>
+      <c r="V31" s="20" t="inlineStr"/>
+      <c r="W31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1035万
+$33,610/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$758万
+$25,175/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1278万
+$26,519/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$774万
+$25,144/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2387万
+$30,326/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P32" s="20" t="inlineStr"/>
+      <c r="Q32" s="20" t="inlineStr"/>
+      <c r="R32" s="20" t="inlineStr"/>
+      <c r="S32" s="20" t="inlineStr"/>
+      <c r="T32" s="20" t="inlineStr"/>
+      <c r="U32" s="20" t="inlineStr"/>
+      <c r="V32" s="20" t="inlineStr"/>
+      <c r="W32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1600万
+$35,556/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$756万
+$25,125/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1256万
+$26,063/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$774万
+$25,126/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1311万
+$29,190/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2258万
+$28,689/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O33" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P33" s="20" t="inlineStr"/>
+      <c r="Q33" s="20" t="inlineStr"/>
+      <c r="R33" s="20" t="inlineStr"/>
+      <c r="S33" s="20" t="inlineStr"/>
+      <c r="T33" s="20" t="inlineStr"/>
+      <c r="U33" s="20" t="inlineStr"/>
+      <c r="V33" s="20" t="inlineStr"/>
+      <c r="W33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1576万
+$35,026/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$753万
+$25,024/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$771万
+$25,025/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$823万
+$26,816/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P34" s="20" t="inlineStr"/>
+      <c r="Q34" s="20" t="inlineStr"/>
+      <c r="R34" s="20" t="inlineStr"/>
+      <c r="S34" s="20" t="inlineStr"/>
+      <c r="T34" s="20" t="inlineStr"/>
+      <c r="U34" s="20" t="inlineStr"/>
+      <c r="V34" s="20" t="inlineStr"/>
+      <c r="W34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1526万
+$33,900/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$750万
+$24,924/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1239万
+$25,705/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$768万
+$24,925/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1305万
+$29,062/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="L35" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$820万
+$26,708/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N35" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2296万
+$29,180/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P35" s="20" t="inlineStr"/>
+      <c r="Q35" s="20" t="inlineStr"/>
+      <c r="R35" s="20" t="inlineStr"/>
+      <c r="S35" s="20" t="inlineStr"/>
+      <c r="T35" s="20" t="inlineStr"/>
+      <c r="U35" s="20" t="inlineStr"/>
+      <c r="V35" s="20" t="inlineStr"/>
+      <c r="W35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$829万
+$27,527/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$848万
+$27,528/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N36" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P36" s="20" t="inlineStr"/>
+      <c r="Q36" s="20" t="inlineStr"/>
+      <c r="R36" s="20" t="inlineStr"/>
+      <c r="S36" s="20" t="inlineStr"/>
+      <c r="T36" s="20" t="inlineStr"/>
+      <c r="U36" s="20" t="inlineStr"/>
+      <c r="V36" s="20" t="inlineStr"/>
+      <c r="W36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1011万
+$32,811/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$772万
+$25,635/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I37" s="25" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1417万
+$29,400/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$758万
+$24,626/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K37" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M37" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N37" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O37" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P37" s="20" t="inlineStr"/>
+      <c r="Q37" s="20" t="inlineStr"/>
+      <c r="R37" s="20" t="inlineStr"/>
+      <c r="S37" s="20" t="inlineStr"/>
+      <c r="T37" s="20" t="inlineStr"/>
+      <c r="U37" s="20" t="inlineStr"/>
+      <c r="V37" s="20" t="inlineStr"/>
+      <c r="W37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$1003万
+$32,578/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$765万
+$25,430/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1220万
+$25,315/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$752万
+$24,429/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M38" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N38" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2184万
+$27,750/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P38" s="20" t="inlineStr"/>
+      <c r="Q38" s="20" t="inlineStr"/>
+      <c r="R38" s="20" t="inlineStr"/>
+      <c r="S38" s="20" t="inlineStr"/>
+      <c r="T38" s="20" t="inlineStr"/>
+      <c r="U38" s="20" t="inlineStr"/>
+      <c r="V38" s="20" t="inlineStr"/>
+      <c r="W38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$899万
+$29,181/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$758万
+$25,193/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1212万
+$25,145/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$746万
+$24,233/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1240万
+$27,627/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$793万
+$25,819/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M39" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$785万
+$25,818/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2169万
+$27,555/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P39" s="20" t="inlineStr"/>
+      <c r="Q39" s="20" t="inlineStr"/>
+      <c r="R39" s="20" t="inlineStr"/>
+      <c r="S39" s="20" t="inlineStr"/>
+      <c r="T39" s="20" t="inlineStr"/>
+      <c r="U39" s="20" t="inlineStr"/>
+      <c r="V39" s="20" t="inlineStr"/>
+      <c r="W39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1380万
+$30,671/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$861万
+$27,963/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$721万
+$23,946/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1210万
+$25,104/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$738万
+$23,946/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+$1260万
+$28,062/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$785万
+$25,560/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$776万
+$25,527/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N40" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2130万
+$27,062/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P40" s="20" t="inlineStr"/>
+      <c r="Q40" s="20" t="inlineStr"/>
+      <c r="R40" s="20" t="inlineStr"/>
+      <c r="S40" s="20" t="inlineStr"/>
+      <c r="T40" s="20" t="inlineStr"/>
+      <c r="U40" s="20" t="inlineStr"/>
+      <c r="V40" s="20" t="inlineStr"/>
+      <c r="W40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 450呎 (2房)
+$1214万
+$26,979/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>A3 | 308呎 (1房)
+$845万
+$27,432/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 612呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 301呎 (1房)
+$681万
+$22,617/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>B10 | 482呎 (2房)
+$1198万
+$24,861/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 308呎 (1房)
+$697万
+$22,618/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K41" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 307呎 (1房)
+$777万
+$25,304/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M41" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 304呎 (1房)
+$769万
+$25,304/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 787呎 (3房)
+$2157万
+$27,409/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="O41" s="23" t="inlineStr">
+        <is>
+          <t>B9 | 296呎 (1房)
+$730万
+$24,675/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P41" s="20" t="inlineStr"/>
+      <c r="Q41" s="20" t="inlineStr"/>
+      <c r="R41" s="20" t="inlineStr"/>
+      <c r="S41" s="20" t="inlineStr"/>
+      <c r="T41" s="20" t="inlineStr"/>
+      <c r="U41" s="20" t="inlineStr"/>
+      <c r="V41" s="20" t="inlineStr"/>
+      <c r="W41" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>PSH A</t>
+        </is>
+      </c>
+      <c r="Q4" s="19" t="inlineStr">
+        <is>
+          <t>PSH B</t>
+        </is>
+      </c>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>PSV A</t>
+        </is>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
+        <is>
+          <t>PSV B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>49&amp;50</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+      <c r="K5" s="20" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr"/>
+      <c r="M5" s="20" t="inlineStr"/>
+      <c r="N5" s="20" t="inlineStr"/>
+      <c r="O5" s="20" t="inlineStr"/>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t>PSH A | 3936呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="Q5" s="24" t="inlineStr">
+        <is>
+          <t>PSH B | 3553呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R5" s="20" t="inlineStr"/>
+      <c r="S5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>PSV A | 2989呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="inlineStr">
+        <is>
+          <t>PSV B | 2765呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$5225万
+$42,586/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4824万
+$39,314/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O8" s="22" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+$8348万
+$42,055/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4330万
+$35,289/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$5191万
+$38,028/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4668万
+$38,044/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O12" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$5020万
+$36,777/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="24" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O13" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$4934万
+$36,147/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O14" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$4908万
+$35,956/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+      <c r="K15" s="20" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr"/>
+      <c r="M15" s="20" t="inlineStr"/>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4470万
+$36,430/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
+      <c r="K16" s="20" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr"/>
+      <c r="M16" s="20" t="inlineStr"/>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O16" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$4808万
+$35,223/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
+      <c r="K17" s="20" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr"/>
+      <c r="M17" s="20" t="inlineStr"/>
+      <c r="N17" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4450万
+$36,267/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="O17" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$4800万
+$35,165/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="P17" s="20" t="inlineStr"/>
+      <c r="Q17" s="20" t="inlineStr"/>
+      <c r="R17" s="20" t="inlineStr"/>
+      <c r="S17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+      <c r="K18" s="20" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr"/>
+      <c r="M18" s="20" t="inlineStr"/>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P18" s="20" t="inlineStr"/>
+      <c r="Q18" s="20" t="inlineStr"/>
+      <c r="R18" s="20" t="inlineStr"/>
+      <c r="S18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
+      <c r="K19" s="20" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr"/>
+      <c r="M19" s="20" t="inlineStr"/>
+      <c r="N19" s="23" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+$4448万
+$36,251/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+$4789万
+$35,084/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="P19" s="20" t="inlineStr"/>
+      <c r="Q19" s="20" t="inlineStr"/>
+      <c r="R19" s="20" t="inlineStr"/>
+      <c r="S19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1985呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr"/>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>B | 1993呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
+      <c r="K20" s="20" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr"/>
+      <c r="M20" s="20" t="inlineStr"/>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1227呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>D | 1365呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="P20" s="20" t="inlineStr"/>
+      <c r="Q20" s="20" t="inlineStr"/>
+      <c r="R20" s="20" t="inlineStr"/>
+      <c r="S20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1572万
+$32,888/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$930万
+$30,809/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$958万
+$32,043/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$828万
+$27,695/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$826万
+$27,810/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N21" s="20" t="inlineStr"/>
+      <c r="O21" s="20" t="inlineStr"/>
+      <c r="P21" s="20" t="inlineStr"/>
+      <c r="Q21" s="20" t="inlineStr"/>
+      <c r="R21" s="20" t="inlineStr"/>
+      <c r="S21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3710万
+$40,859/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1566万
+$32,761/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$927万
+$30,686/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$954万
+$31,915/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$859万
+$28,723/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$824万
+$27,732/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N22" s="20" t="inlineStr"/>
+      <c r="O22" s="20" t="inlineStr"/>
+      <c r="P22" s="20" t="inlineStr"/>
+      <c r="Q22" s="20" t="inlineStr"/>
+      <c r="R22" s="20" t="inlineStr"/>
+      <c r="S22" s="20" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr"/>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1560万
+$32,644/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$919万
+$30,443/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$910万
+$30,442/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$910万
+$30,442/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L23" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$908万
+$30,569/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N23" s="20" t="inlineStr"/>
+      <c r="O23" s="20" t="inlineStr"/>
+      <c r="P23" s="20" t="inlineStr"/>
+      <c r="Q23" s="20" t="inlineStr"/>
+      <c r="R23" s="20" t="inlineStr"/>
+      <c r="S23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3657万
+$40,279/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1555万
+$32,529/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$915万
+$30,312/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$906万
+$30,312/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$816万
+$27,280/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$814万
+$27,394/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr"/>
+      <c r="O24" s="20" t="inlineStr"/>
+      <c r="P24" s="20" t="inlineStr"/>
+      <c r="Q24" s="20" t="inlineStr"/>
+      <c r="R24" s="20" t="inlineStr"/>
+      <c r="S24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3545万
+$39,040/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1540万
+$32,226/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$913万
+$30,228/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$812万
+$27,172/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$812万
+$27,172/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$810万
+$27,285/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr"/>
+      <c r="O25" s="20" t="inlineStr"/>
+      <c r="P25" s="20" t="inlineStr"/>
+      <c r="Q25" s="20" t="inlineStr"/>
+      <c r="R25" s="20" t="inlineStr"/>
+      <c r="S25" s="20" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3626万
+$39,932/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr"/>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1537万
+$32,161/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$899万
+$29,784/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$800万
+$26,772/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$800万
+$26,772/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$798万
+$26,884/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr"/>
+      <c r="O26" s="20" t="inlineStr"/>
+      <c r="P26" s="20" t="inlineStr"/>
+      <c r="Q26" s="20" t="inlineStr"/>
+      <c r="R26" s="20" t="inlineStr"/>
+      <c r="S26" s="20" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3605万
+$39,705/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$790万
+$26,428/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$818万
+$27,551/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N27" s="20" t="inlineStr"/>
+      <c r="O27" s="20" t="inlineStr"/>
+      <c r="P27" s="20" t="inlineStr"/>
+      <c r="Q27" s="20" t="inlineStr"/>
+      <c r="R27" s="20" t="inlineStr"/>
+      <c r="S27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$868万
+$29,016/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$898万
+$30,248/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N28" s="20" t="inlineStr"/>
+      <c r="O28" s="20" t="inlineStr"/>
+      <c r="P28" s="20" t="inlineStr"/>
+      <c r="Q28" s="20" t="inlineStr"/>
+      <c r="R28" s="20" t="inlineStr"/>
+      <c r="S28" s="20" t="inlineStr"/>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3501万
+$38,558/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr"/>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$768万
+$25,670/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$795万
+$26,760/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N29" s="20" t="inlineStr"/>
+      <c r="O29" s="20" t="inlineStr"/>
+      <c r="P29" s="20" t="inlineStr"/>
+      <c r="Q29" s="20" t="inlineStr"/>
+      <c r="R29" s="20" t="inlineStr"/>
+      <c r="S29" s="20" t="inlineStr"/>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3335万
+$36,730/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$766万
+$25,618/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$793万
+$26,706/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N30" s="20" t="inlineStr"/>
+      <c r="O30" s="20" t="inlineStr"/>
+      <c r="P30" s="20" t="inlineStr"/>
+      <c r="Q30" s="20" t="inlineStr"/>
+      <c r="R30" s="20" t="inlineStr"/>
+      <c r="S30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$764万
+$25,567/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$791万
+$26,620/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N31" s="20" t="inlineStr"/>
+      <c r="O31" s="20" t="inlineStr"/>
+      <c r="P31" s="20" t="inlineStr"/>
+      <c r="Q31" s="20" t="inlineStr"/>
+      <c r="R31" s="20" t="inlineStr"/>
+      <c r="S31" s="20" t="inlineStr"/>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3557万
+$39,172/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr"/>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I32" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$890万
+$29,470/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$792万
+$26,489/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$763万
+$25,516/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$789万
+$26,566/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr"/>
+      <c r="O32" s="20" t="inlineStr"/>
+      <c r="P32" s="20" t="inlineStr"/>
+      <c r="Q32" s="20" t="inlineStr"/>
+      <c r="R32" s="20" t="inlineStr"/>
+      <c r="S32" s="20" t="inlineStr"/>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$799万
+$26,470/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$789万
+$26,403/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$790万
+$26,436/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$787万
+$26,513/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="inlineStr"/>
+      <c r="O33" s="20" t="inlineStr"/>
+      <c r="P33" s="20" t="inlineStr"/>
+      <c r="Q33" s="20" t="inlineStr"/>
+      <c r="R33" s="20" t="inlineStr"/>
+      <c r="S33" s="20" t="inlineStr"/>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3610万
+$39,758/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$796万
+$26,364/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$787万
+$26,330/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$787万
+$26,330/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$785万
+$26,440/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N34" s="20" t="inlineStr"/>
+      <c r="O34" s="20" t="inlineStr"/>
+      <c r="P34" s="20" t="inlineStr"/>
+      <c r="Q34" s="20" t="inlineStr"/>
+      <c r="R34" s="20" t="inlineStr"/>
+      <c r="S34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3366万
+$37,070/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$792万
+$26,225/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$784万
+$26,225/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$783万
+$26,192/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L35" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$782万
+$26,334/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N35" s="20" t="inlineStr"/>
+      <c r="O35" s="20" t="inlineStr"/>
+      <c r="P35" s="20" t="inlineStr"/>
+      <c r="Q35" s="20" t="inlineStr"/>
+      <c r="R35" s="20" t="inlineStr"/>
+      <c r="S35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I36" s="25" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$875万
+$28,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$866万
+$28,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K36" s="25" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$866万
+$28,964/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L36" s="25" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$864万
+$29,085/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N36" s="20" t="inlineStr"/>
+      <c r="O36" s="20" t="inlineStr"/>
+      <c r="P36" s="20" t="inlineStr"/>
+      <c r="Q36" s="20" t="inlineStr"/>
+      <c r="R36" s="20" t="inlineStr"/>
+      <c r="S36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3136万
+$34,543/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1405万
+$29,400/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$782万
+$25,878/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$775万
+$25,911/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$775万
+$25,911/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L37" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$773万
+$26,019/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M37" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N37" s="20" t="inlineStr"/>
+      <c r="O37" s="20" t="inlineStr"/>
+      <c r="P37" s="20" t="inlineStr"/>
+      <c r="Q37" s="20" t="inlineStr"/>
+      <c r="R37" s="20" t="inlineStr"/>
+      <c r="S37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3033万
+$33,401/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1386万
+$28,989/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$776万
+$25,704/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$769万
+$25,703/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$769万
+$25,703/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$767万
+$25,810/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M38" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N38" s="20" t="inlineStr"/>
+      <c r="O38" s="20" t="inlineStr"/>
+      <c r="P38" s="20" t="inlineStr"/>
+      <c r="Q38" s="20" t="inlineStr"/>
+      <c r="R38" s="20" t="inlineStr"/>
+      <c r="S38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3064万
+$33,745/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1367万
+$28,588/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$837万
+$27,706/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$745万
+$24,902/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$718万
+$23,998/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$716万
+$24,098/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M39" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N39" s="20" t="inlineStr"/>
+      <c r="O39" s="20" t="inlineStr"/>
+      <c r="P39" s="20" t="inlineStr"/>
+      <c r="Q39" s="20" t="inlineStr"/>
+      <c r="R39" s="20" t="inlineStr"/>
+      <c r="S39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 908呎 (4+房)
+$3012万
+$33,172/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1350万
+$28,242/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$746万
+$24,686/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$738万
+$24,685/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$710万
+$23,758/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$709万
+$23,857/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N40" s="20" t="inlineStr"/>
+      <c r="O40" s="20" t="inlineStr"/>
+      <c r="P40" s="20" t="inlineStr"/>
+      <c r="Q40" s="20" t="inlineStr"/>
+      <c r="R40" s="20" t="inlineStr"/>
+      <c r="S40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>A1 | 874呎 (4+房)
+$2659万
+$30,427/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+$1320万
+$27,623/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>B2 | 302呎 (1房)
+$719万
+$23,809/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 299呎 (1房)
+$712万
+$23,808/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>B5 | 299呎 (1房)
+$685万
+$22,923/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>B6 | 297呎 (1房)
+$683万
+$22,985/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M41" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 455呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="N41" s="20" t="inlineStr"/>
+      <c r="O41" s="20" t="inlineStr"/>
+      <c r="P41" s="20" t="inlineStr"/>
+      <c r="Q41" s="20" t="inlineStr"/>
+      <c r="R41" s="20" t="inlineStr"/>
+      <c r="S41" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -671,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -5073,14 +5073,14 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>8069552</v>
+        <v>8444880</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>26545</v>
+        <v>27779</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5857,14 +5857,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>7973748</v>
+        <v>8344620</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>26229</v>
+        <v>27449</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6641,14 +6641,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>7894714</v>
+        <v>8261910</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>25969</v>
+        <v>27177</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>7972716</v>
+        <v>8343540</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>25970</v>
+        <v>27178</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6835,14 +6835,14 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>7650388</v>
+        <v>8006220</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>24839</v>
+        <v>25994</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6897,14 +6897,14 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>14201610</v>
+        <v>16018095</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>29464</v>
+        <v>33233</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6959,14 +6959,14 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>7476324</v>
+        <v>7824060</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>24838</v>
+        <v>25994</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -7433,14 +7433,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>7816454</v>
+        <v>8180010</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>25712</v>
+        <v>26908</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7681,14 +7681,14 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>13483768</v>
+        <v>15208436</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>27975</v>
+        <v>31553</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -8209,14 +8209,14 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K115" s="5" t="n">
-        <v>7738968</v>
+        <v>8098920</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>25457</v>
+        <v>26641</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>7815422</v>
+        <v>8178930</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>25457</v>
+        <v>26641</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -9055,14 +9055,14 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K128" s="5" t="n">
-        <v>7646948</v>
+        <v>8002620</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>24909</v>
+        <v>26067</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
@@ -9249,14 +9249,14 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K131" s="5" t="n">
-        <v>13331548</v>
+        <v>15036746</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>27659</v>
+        <v>31197</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -10235,14 +10235,14 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>9505494</v>
+        <v>10721313</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>30862</v>
+        <v>34809</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10779,14 +10779,14 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K154" s="5" t="n">
-        <v>7469186</v>
+        <v>7816590</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>24251</v>
+        <v>25379</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
@@ -10911,14 +10911,14 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>7299250</v>
+        <v>7638750</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>24250</v>
+        <v>25378</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -11043,14 +11043,14 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>9352500</v>
+        <v>10548750</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>30365</v>
+        <v>34249</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -13427,14 +13427,14 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>8969542</v>
+        <v>10116809</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>29122</v>
+        <v>32847</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -14227,14 +14227,14 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
-        <v>8902634</v>
+        <v>10041343</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>28905</v>
+        <v>32602</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -17163,14 +17163,14 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>7291596</v>
+        <v>7630740</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>23674</v>
+        <v>24775</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -17295,14 +17295,14 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K252" s="5" t="n">
-        <v>7125702</v>
+        <v>7457130</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>23673</v>
+        <v>24775</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -18049,14 +18049,14 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>12186974</v>
+        <v>12753810</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>25284</v>
+        <v>26460</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -18243,14 +18243,14 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>8690902</v>
+        <v>9802529</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>28217</v>
+        <v>31826</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -19043,14 +19043,14 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>8629240</v>
+        <v>9732980</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>28017</v>
+        <v>31601</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -20657,14 +20657,14 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K303" s="5" t="n">
-        <v>11869806</v>
+        <v>12421890</v>
       </c>
       <c r="L303" s="5" t="n">
-        <v>26377</v>
+        <v>27604</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
@@ -25831,14 +25831,14 @@
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>8239488</v>
+        <v>8622720</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>27557</v>
+        <v>28839</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
@@ -25893,14 +25893,14 @@
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K381" s="5" t="n">
-        <v>8001784</v>
+        <v>8373960</v>
       </c>
       <c r="L381" s="5" t="n">
-        <v>26496</v>
+        <v>27728</v>
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
@@ -25955,14 +25955,14 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>13519458</v>
+        <v>14148270</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>28283</v>
+        <v>29599</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -26491,14 +26491,14 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>8206636</v>
+        <v>8588340</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>27447</v>
+        <v>28724</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
@@ -26553,14 +26553,14 @@
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K391" s="5" t="n">
-        <v>7969878</v>
+        <v>8340570</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>26390</v>
+        <v>27618</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
@@ -26615,14 +26615,14 @@
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>13467514</v>
+        <v>14093910</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>28175</v>
+        <v>29485</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -27019,14 +27019,14 @@
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>7807940</v>
+        <v>8171100</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>26289</v>
+        <v>27512</v>
       </c>
       <c r="M398" s="3" t="inlineStr">
         <is>
@@ -27081,14 +27081,14 @@
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>7827892</v>
+        <v>8191980</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>26180</v>
+        <v>27398</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -27143,14 +27143,14 @@
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>7827892</v>
+        <v>8191980</v>
       </c>
       <c r="L400" s="5" t="n">
-        <v>26180</v>
+        <v>27398</v>
       </c>
       <c r="M400" s="3" t="inlineStr">
         <is>
@@ -27205,14 +27205,14 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>7906582</v>
+        <v>8274330</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>26181</v>
+        <v>27398</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
@@ -27267,14 +27267,14 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>13419182</v>
+        <v>15135589</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>28074</v>
+        <v>31664</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -27803,14 +27803,14 @@
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K410" s="5" t="n">
-        <v>7794352</v>
+        <v>8156880</v>
       </c>
       <c r="L410" s="5" t="n">
-        <v>26068</v>
+        <v>27281</v>
       </c>
       <c r="M410" s="3" t="inlineStr">
         <is>
@@ -27865,14 +27865,14 @@
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>7872698</v>
+        <v>8238870</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>26069</v>
+        <v>27281</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -28525,14 +28525,14 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K421" s="5" t="n">
-        <v>7850768</v>
+        <v>8215920</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>25996</v>
+        <v>27205</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -28587,14 +28587,14 @@
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K422" s="5" t="n">
-        <v>13247354</v>
+        <v>14941783</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>27714</v>
+        <v>31259</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -29177,14 +29177,14 @@
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K431" s="5" t="n">
-        <v>7735528</v>
+        <v>8095320</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>25614</v>
+        <v>26806</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -29239,14 +29239,14 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K432" s="5" t="n">
-        <v>13220866</v>
+        <v>14911907</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>27659</v>
+        <v>31196</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -30319,14 +30319,14 @@
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K448" s="5" t="n">
-        <v>7726068</v>
+        <v>8714286</v>
       </c>
       <c r="L448" s="5" t="n">
-        <v>26014</v>
+        <v>29341</v>
       </c>
       <c r="M448" s="3" t="inlineStr">
         <is>
@@ -30381,14 +30381,14 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K449" s="5" t="n">
-        <v>7461188</v>
+        <v>7808220</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>24954</v>
+        <v>26114</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -33225,14 +33225,14 @@
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>7653914</v>
+        <v>8632903</v>
       </c>
       <c r="L491" s="5" t="n">
-        <v>25344</v>
+        <v>28586</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -35687,14 +35687,14 @@
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K528" s="5" t="n">
-        <v>7428766</v>
+        <v>8378957</v>
       </c>
       <c r="L528" s="5" t="n">
-        <v>25013</v>
+        <v>28212</v>
       </c>
       <c r="M528" s="3" t="inlineStr">
         <is>
@@ -35749,14 +35749,14 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K529" s="5" t="n">
-        <v>7447772</v>
+        <v>8400394</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>24909</v>
+        <v>28095</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
@@ -35811,14 +35811,14 @@
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K530" s="5" t="n">
-        <v>7447772</v>
+        <v>8400394</v>
       </c>
       <c r="L530" s="5" t="n">
-        <v>24909</v>
+        <v>28095</v>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
@@ -35873,14 +35873,14 @@
       </c>
       <c r="J531" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="K531" s="5" t="n">
-        <v>7522592</v>
+        <v>8484784</v>
       </c>
       <c r="L531" s="5" t="n">
-        <v>24909</v>
+        <v>28095</v>
       </c>
       <c r="M531" s="3" t="inlineStr">
         <is>
@@ -37263,14 +37263,14 @@
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K552" s="5" t="n">
-        <v>11916676</v>
+        <v>12470940</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>24930</v>
+        <v>26090</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -37853,14 +37853,14 @@
       </c>
       <c r="J561" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K561" s="5" t="n">
-        <v>7195878</v>
+        <v>7530570</v>
       </c>
       <c r="L561" s="5" t="n">
-        <v>23827</v>
+        <v>24936</v>
       </c>
       <c r="M561" s="3" t="inlineStr">
         <is>
@@ -37915,14 +37915,14 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K562" s="5" t="n">
-        <v>11752158</v>
+        <v>12298770</v>
       </c>
       <c r="L562" s="5" t="n">
-        <v>24586</v>
+        <v>25730</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
@@ -39227,14 +39227,14 @@
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K582" s="5" t="n">
-        <v>11355354</v>
+        <v>11883510</v>
       </c>
       <c r="L582" s="5" t="n">
-        <v>23756</v>
+        <v>24861</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N586"/>
+  <dimension ref="A1:P586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -753,7 +753,12 @@
           <t>付款办法</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>额外回赠/补贴</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>是否招标</t>
         </is>
@@ -825,6 +830,11 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -895,6 +905,11 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -965,6 +980,11 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1035,6 +1055,11 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1105,6 +1130,11 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1175,6 +1205,11 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1245,6 +1280,11 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1315,6 +1355,11 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1385,6 +1430,11 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1455,6 +1505,11 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1525,6 +1580,11 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1587,6 +1647,11 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1649,6 +1714,11 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1719,6 +1789,11 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1789,6 +1864,11 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1859,6 +1939,11 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1929,6 +2014,11 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1999,6 +2089,11 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2069,6 +2164,11 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2131,6 +2231,11 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2193,6 +2298,11 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2263,6 +2373,11 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2333,6 +2448,11 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2395,6 +2515,11 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2457,6 +2582,11 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2519,6 +2649,11 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2589,6 +2724,11 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2659,6 +2799,11 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2729,6 +2874,11 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2799,6 +2949,11 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2869,6 +3024,11 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2931,6 +3091,11 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2993,6 +3158,11 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3055,6 +3225,11 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3125,6 +3300,11 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3195,6 +3375,11 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3265,6 +3450,11 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3335,6 +3525,11 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3405,6 +3600,11 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3467,6 +3667,11 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3529,6 +3734,11 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3591,6 +3801,11 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3661,6 +3876,11 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3723,6 +3943,11 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3785,6 +4010,11 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3847,6 +4077,11 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3917,6 +4152,11 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3979,6 +4219,11 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4041,6 +4286,11 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4103,6 +4353,11 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4173,6 +4428,11 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4243,6 +4503,11 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4305,6 +4570,11 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4375,6 +4645,11 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4445,6 +4720,11 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4507,6 +4787,11 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4569,6 +4854,11 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4631,6 +4921,11 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4701,6 +4996,11 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4763,6 +5063,11 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4825,6 +5130,11 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4887,6 +5197,11 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4957,6 +5272,11 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5027,6 +5347,11 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5089,6 +5414,11 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5151,6 +5481,11 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5221,6 +5556,11 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5283,6 +5623,11 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5345,6 +5690,11 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5407,6 +5757,11 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5477,6 +5832,11 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5539,6 +5899,11 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5601,6 +5966,11 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5671,6 +6041,11 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5741,6 +6116,11 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5811,6 +6191,11 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5873,6 +6258,11 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5935,6 +6325,11 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6005,6 +6400,11 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6067,6 +6467,11 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6129,6 +6534,11 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6191,6 +6601,11 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6261,6 +6676,11 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6323,6 +6743,11 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6385,6 +6810,11 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6455,6 +6885,11 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6525,6 +6960,11 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6595,6 +7035,11 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6657,6 +7102,11 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6719,6 +7169,11 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6789,6 +7244,11 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6851,6 +7311,11 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6913,6 +7378,11 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6975,6 +7445,11 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7045,6 +7520,11 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7115,6 +7595,11 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7185,6 +7670,11 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7255,6 +7745,11 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7325,6 +7820,11 @@
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7387,6 +7887,11 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7449,6 +7954,11 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7511,6 +8021,11 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7573,6 +8088,11 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7635,6 +8155,11 @@
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7697,6 +8222,11 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7759,6 +8289,11 @@
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7829,6 +8364,11 @@
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7899,6 +8439,11 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7961,6 +8506,11 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8031,6 +8581,11 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8101,6 +8656,11 @@
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8163,6 +8723,11 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8225,6 +8790,11 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8287,6 +8857,11 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8349,6 +8924,11 @@
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8411,6 +8991,11 @@
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8473,6 +9058,11 @@
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8535,6 +9125,11 @@
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8605,6 +9200,11 @@
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8667,6 +9267,11 @@
       </c>
       <c r="N122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8729,6 +9334,11 @@
       </c>
       <c r="N123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8799,6 +9409,11 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8869,6 +9484,11 @@
       </c>
       <c r="N125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8939,6 +9559,11 @@
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9009,6 +9634,11 @@
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9071,6 +9701,11 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9141,6 +9776,11 @@
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9203,6 +9843,11 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9265,6 +9910,11 @@
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9327,6 +9977,11 @@
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9397,6 +10052,11 @@
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9467,6 +10127,11 @@
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9529,6 +10194,11 @@
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9599,6 +10269,11 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9669,6 +10344,11 @@
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9731,6 +10411,11 @@
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9801,6 +10486,11 @@
       </c>
       <c r="N139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9871,6 +10561,11 @@
       </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9933,6 +10628,11 @@
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9995,6 +10695,11 @@
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10057,6 +10762,11 @@
       </c>
       <c r="N143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10119,6 +10829,11 @@
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10189,6 +10904,11 @@
       </c>
       <c r="N145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10251,6 +10971,11 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10313,6 +11038,11 @@
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10383,6 +11113,11 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -10453,6 +11188,11 @@
       </c>
       <c r="N149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10523,6 +11263,11 @@
       </c>
       <c r="N150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10593,6 +11338,11 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10663,6 +11413,11 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10733,6 +11488,11 @@
       </c>
       <c r="N153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10795,6 +11555,11 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10865,6 +11630,11 @@
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10927,6 +11697,11 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10997,6 +11772,11 @@
       </c>
       <c r="N157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11059,6 +11839,11 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11129,6 +11914,11 @@
       </c>
       <c r="N159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11199,6 +11989,11 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11269,6 +12064,11 @@
       </c>
       <c r="N161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11339,6 +12139,11 @@
       </c>
       <c r="N162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11409,6 +12214,11 @@
       </c>
       <c r="N163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11479,6 +12289,11 @@
       </c>
       <c r="N164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11549,6 +12364,11 @@
       </c>
       <c r="N165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11611,6 +12431,11 @@
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11673,6 +12498,11 @@
       </c>
       <c r="N167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11735,6 +12565,11 @@
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11805,6 +12640,11 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11875,6 +12715,11 @@
       </c>
       <c r="N170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11937,6 +12782,11 @@
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12007,6 +12857,11 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12077,6 +12932,11 @@
       </c>
       <c r="N173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12139,6 +12999,11 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12209,6 +13074,11 @@
       </c>
       <c r="N175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12271,6 +13141,11 @@
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12333,6 +13208,11 @@
       </c>
       <c r="N177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12395,6 +13275,11 @@
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12457,6 +13342,11 @@
       </c>
       <c r="N179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12519,6 +13409,11 @@
       </c>
       <c r="N180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12589,6 +13484,11 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12651,6 +13551,11 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12713,6 +13618,11 @@
       </c>
       <c r="N183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12783,6 +13693,11 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -12853,6 +13768,11 @@
       </c>
       <c r="N185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12915,6 +13835,11 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12985,6 +13910,11 @@
       </c>
       <c r="N187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13047,6 +13977,11 @@
       </c>
       <c r="N188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13117,6 +14052,11 @@
       </c>
       <c r="N189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13179,6 +14119,11 @@
       </c>
       <c r="N190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13249,6 +14194,11 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13311,6 +14261,11 @@
       </c>
       <c r="N192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13381,6 +14336,11 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13443,6 +14403,11 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13513,6 +14478,11 @@
       </c>
       <c r="N195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13583,6 +14553,11 @@
       </c>
       <c r="N196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13653,6 +14628,11 @@
       </c>
       <c r="N197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13715,6 +14695,11 @@
       </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13785,6 +14770,11 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13855,6 +14845,11 @@
       </c>
       <c r="N200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13925,6 +14920,11 @@
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13987,6 +14987,11 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14049,6 +15054,11 @@
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14111,6 +15121,11 @@
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14181,6 +15196,11 @@
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14243,6 +15263,11 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14313,6 +15338,11 @@
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14383,6 +15413,11 @@
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14453,6 +15488,11 @@
       </c>
       <c r="N209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14515,6 +15555,11 @@
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14585,6 +15630,11 @@
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14655,6 +15705,11 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14717,6 +15772,11 @@
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14779,6 +15839,11 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14841,6 +15906,11 @@
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14903,6 +15973,11 @@
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14973,6 +16048,11 @@
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15043,6 +16123,11 @@
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15105,6 +16190,11 @@
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15175,6 +16265,11 @@
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15245,6 +16340,11 @@
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15315,6 +16415,11 @@
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15385,6 +16490,11 @@
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15447,6 +16557,11 @@
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15517,6 +16632,11 @@
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15579,6 +16699,11 @@
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15649,6 +16774,11 @@
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15711,6 +16841,11 @@
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15781,6 +16916,11 @@
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15851,6 +16991,11 @@
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15913,6 +17058,11 @@
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15983,6 +17133,11 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -16053,6 +17208,11 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16115,6 +17275,11 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16185,6 +17350,11 @@
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16247,6 +17417,11 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16309,6 +17484,11 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16371,6 +17551,11 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16433,6 +17618,11 @@
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16495,6 +17685,11 @@
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16565,6 +17760,11 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16635,6 +17835,11 @@
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16697,6 +17902,11 @@
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16767,6 +17977,11 @@
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16837,6 +18052,11 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16907,6 +18127,11 @@
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -16977,6 +18202,11 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17047,6 +18277,11 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17117,6 +18352,11 @@
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17179,6 +18419,11 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17249,6 +18494,11 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17311,6 +18561,11 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17381,6 +18636,11 @@
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17451,6 +18711,11 @@
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17521,6 +18786,11 @@
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17591,6 +18861,11 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17661,6 +18936,11 @@
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17731,6 +19011,11 @@
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17801,6 +19086,11 @@
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17871,6 +19161,11 @@
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -17941,6 +19236,11 @@
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18003,6 +19303,11 @@
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18065,6 +19370,11 @@
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18127,6 +19437,11 @@
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18197,6 +19512,11 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18259,6 +19579,11 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18329,6 +19654,11 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18399,6 +19729,11 @@
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -18469,6 +19804,11 @@
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18531,6 +19871,11 @@
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18601,6 +19946,11 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18671,6 +20021,11 @@
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18741,6 +20096,11 @@
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18803,6 +20163,11 @@
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18865,6 +20230,11 @@
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18927,6 +20297,11 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -18997,6 +20372,11 @@
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19059,6 +20439,11 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
+          <t>3% 印花税补贴</t>
+        </is>
+      </c>
+      <c r="O278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19129,6 +20514,11 @@
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19199,6 +20589,11 @@
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19269,6 +20664,11 @@
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19331,6 +20731,11 @@
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19393,6 +20798,11 @@
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19455,6 +20865,11 @@
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19517,6 +20932,11 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19579,6 +20999,11 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19641,6 +21066,11 @@
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19703,6 +21133,11 @@
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19773,6 +21208,11 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19835,6 +21275,11 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19905,6 +21350,11 @@
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -19975,6 +21425,11 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20045,6 +21500,11 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20107,6 +21567,11 @@
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20169,6 +21634,11 @@
       </c>
       <c r="N295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20231,6 +21701,11 @@
       </c>
       <c r="N296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20293,6 +21768,11 @@
       </c>
       <c r="N297" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20355,6 +21835,11 @@
       </c>
       <c r="N298" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20417,6 +21902,11 @@
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20479,6 +21969,11 @@
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20549,6 +22044,11 @@
       </c>
       <c r="N301" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20611,6 +22111,11 @@
       </c>
       <c r="N302" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20673,6 +22178,11 @@
       </c>
       <c r="N303" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20743,6 +22253,11 @@
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -20805,6 +22320,11 @@
       </c>
       <c r="N305" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20867,6 +22387,11 @@
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20929,6 +22454,11 @@
       </c>
       <c r="N307" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -20991,6 +22521,11 @@
       </c>
       <c r="N308" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21061,6 +22596,11 @@
       </c>
       <c r="N309" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21123,6 +22663,11 @@
       </c>
       <c r="N310" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21185,6 +22730,11 @@
       </c>
       <c r="N311" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21247,6 +22797,11 @@
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21317,6 +22872,11 @@
       </c>
       <c r="N313" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21379,6 +22939,11 @@
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21441,6 +23006,11 @@
       </c>
       <c r="N315" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21511,6 +23081,11 @@
       </c>
       <c r="N316" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21581,6 +23156,11 @@
       </c>
       <c r="N317" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O317" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -21651,6 +23231,11 @@
       </c>
       <c r="N318" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21721,6 +23306,11 @@
       </c>
       <c r="N319" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -21791,6 +23381,11 @@
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O320" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21861,6 +23456,11 @@
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O321" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21923,6 +23523,11 @@
       </c>
       <c r="N322" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O322" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -21993,6 +23598,11 @@
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O323" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22063,6 +23673,11 @@
       </c>
       <c r="N324" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O324" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22133,6 +23748,11 @@
       </c>
       <c r="N325" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O325" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -22195,6 +23815,11 @@
       </c>
       <c r="N326" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O326" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22265,6 +23890,11 @@
       </c>
       <c r="N327" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O327" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22335,6 +23965,11 @@
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O328" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -22405,6 +24040,11 @@
       </c>
       <c r="N329" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O329" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22475,6 +24115,11 @@
       </c>
       <c r="N330" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O330" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22545,6 +24190,11 @@
       </c>
       <c r="N331" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22615,6 +24265,11 @@
       </c>
       <c r="N332" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22677,6 +24332,11 @@
       </c>
       <c r="N333" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22739,6 +24399,11 @@
       </c>
       <c r="N334" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O334" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22809,6 +24474,11 @@
       </c>
       <c r="N335" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22871,6 +24541,11 @@
       </c>
       <c r="N336" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -22941,6 +24616,11 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23011,6 +24691,11 @@
       </c>
       <c r="N338" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O338" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23081,6 +24766,11 @@
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O339" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23151,6 +24841,11 @@
       </c>
       <c r="N340" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O340" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -23213,6 +24908,11 @@
       </c>
       <c r="N341" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23275,6 +24975,11 @@
       </c>
       <c r="N342" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O342" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23345,6 +25050,11 @@
       </c>
       <c r="N343" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23415,6 +25125,11 @@
       </c>
       <c r="N344" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -23477,6 +25192,11 @@
       </c>
       <c r="N345" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23547,6 +25267,11 @@
       </c>
       <c r="N346" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -23617,6 +25342,11 @@
       </c>
       <c r="N347" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O347" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23687,6 +25417,11 @@
       </c>
       <c r="N348" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23749,6 +25484,11 @@
       </c>
       <c r="N349" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O349" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23819,6 +25559,11 @@
       </c>
       <c r="N350" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O350" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23889,6 +25634,11 @@
       </c>
       <c r="N351" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O351" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -23959,6 +25709,11 @@
       </c>
       <c r="N352" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O352" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24029,6 +25784,11 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O353" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24091,6 +25851,11 @@
       </c>
       <c r="N354" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O354" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24161,6 +25926,11 @@
       </c>
       <c r="N355" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O355" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24231,6 +26001,11 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O356" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24293,6 +26068,11 @@
       </c>
       <c r="N357" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O357" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24363,6 +26143,11 @@
       </c>
       <c r="N358" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O358" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24433,6 +26218,11 @@
       </c>
       <c r="N359" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24503,6 +26293,11 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24565,6 +26360,11 @@
       </c>
       <c r="N361" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24627,6 +26427,11 @@
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24697,6 +26502,11 @@
       </c>
       <c r="N363" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24767,6 +26577,11 @@
       </c>
       <c r="N364" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O364" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24837,6 +26652,11 @@
       </c>
       <c r="N365" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O365" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24907,6 +26727,11 @@
       </c>
       <c r="N366" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O366" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -24977,6 +26802,11 @@
       </c>
       <c r="N367" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O367" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25047,6 +26877,11 @@
       </c>
       <c r="N368" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O368" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25109,6 +26944,11 @@
       </c>
       <c r="N369" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O369" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25171,6 +27011,11 @@
       </c>
       <c r="N370" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O370" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25241,6 +27086,11 @@
       </c>
       <c r="N371" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O371" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25311,6 +27161,11 @@
       </c>
       <c r="N372" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O372" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25381,6 +27236,11 @@
       </c>
       <c r="N373" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O373" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25451,6 +27311,11 @@
       </c>
       <c r="N374" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O374" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25521,6 +27386,11 @@
       </c>
       <c r="N375" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O375" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25591,6 +27461,11 @@
       </c>
       <c r="N376" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O376" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25661,6 +27536,11 @@
       </c>
       <c r="N377" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O377" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25723,6 +27603,11 @@
       </c>
       <c r="N378" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O378" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25785,6 +27670,11 @@
       </c>
       <c r="N379" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O379" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25847,6 +27737,11 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O380" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25909,6 +27804,11 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O381" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -25971,6 +27871,11 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O382" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26041,6 +27946,11 @@
       </c>
       <c r="N383" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O383" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26111,6 +28021,11 @@
       </c>
       <c r="N384" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O384" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26181,6 +28096,11 @@
       </c>
       <c r="N385" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O385" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26251,6 +28171,11 @@
       </c>
       <c r="N386" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O386" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26321,6 +28246,11 @@
       </c>
       <c r="N387" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O387" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26383,6 +28313,11 @@
       </c>
       <c r="N388" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O388" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26445,6 +28380,11 @@
       </c>
       <c r="N389" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O389" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26507,6 +28447,11 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O390" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26569,6 +28514,11 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O391" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26631,6 +28581,11 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O392" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26701,6 +28656,11 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O393" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26771,6 +28731,11 @@
       </c>
       <c r="N394" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O394" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26841,6 +28806,11 @@
       </c>
       <c r="N395" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O395" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26903,6 +28873,11 @@
       </c>
       <c r="N396" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O396" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -26973,6 +28948,11 @@
       </c>
       <c r="N397" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O397" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27035,6 +29015,11 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O398" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27097,6 +29082,11 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O399" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27159,6 +29149,11 @@
       </c>
       <c r="N400" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O400" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27221,6 +29216,11 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O401" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27283,6 +29283,11 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O402" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27353,6 +29358,11 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O403" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27423,6 +29433,11 @@
       </c>
       <c r="N404" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O404" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27493,6 +29508,11 @@
       </c>
       <c r="N405" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27563,6 +29583,11 @@
       </c>
       <c r="N406" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O406" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27633,6 +29658,11 @@
       </c>
       <c r="N407" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O407" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27695,6 +29725,11 @@
       </c>
       <c r="N408" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O408" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27757,6 +29792,11 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O409" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27819,6 +29859,11 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O410" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27881,6 +29926,11 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O411" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -27951,6 +30001,11 @@
       </c>
       <c r="N412" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -28021,6 +30076,11 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -28091,6 +30151,11 @@
       </c>
       <c r="N414" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28161,6 +30226,11 @@
       </c>
       <c r="N415" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -28223,6 +30293,11 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28293,6 +30368,11 @@
       </c>
       <c r="N417" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28355,6 +30435,11 @@
       </c>
       <c r="N418" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28417,6 +30502,11 @@
       </c>
       <c r="N419" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28479,6 +30569,11 @@
       </c>
       <c r="N420" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O420" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28541,6 +30636,11 @@
       </c>
       <c r="N421" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O421" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28603,6 +30703,11 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O422" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28673,6 +30778,11 @@
       </c>
       <c r="N423" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O423" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28743,6 +30853,11 @@
       </c>
       <c r="N424" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O424" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28813,6 +30928,11 @@
       </c>
       <c r="N425" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O425" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28875,6 +30995,11 @@
       </c>
       <c r="N426" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O426" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -28945,6 +31070,11 @@
       </c>
       <c r="N427" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O427" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29007,6 +31137,11 @@
       </c>
       <c r="N428" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O428" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29069,6 +31204,11 @@
       </c>
       <c r="N429" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O429" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29131,6 +31271,11 @@
       </c>
       <c r="N430" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O430" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29193,6 +31338,11 @@
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O431" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29255,6 +31405,11 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O432" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29325,6 +31480,11 @@
       </c>
       <c r="N433" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O433" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29395,6 +31555,11 @@
       </c>
       <c r="N434" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O434" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29465,6 +31630,11 @@
       </c>
       <c r="N435" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O435" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29527,6 +31697,11 @@
       </c>
       <c r="N436" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O436" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29597,6 +31772,11 @@
       </c>
       <c r="N437" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O437" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29659,6 +31839,11 @@
       </c>
       <c r="N438" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O438" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29721,6 +31906,11 @@
       </c>
       <c r="N439" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O439" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29791,6 +31981,11 @@
       </c>
       <c r="N440" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O440" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29861,6 +32056,11 @@
       </c>
       <c r="N441" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O441" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -29931,6 +32131,11 @@
       </c>
       <c r="N442" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O442" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -30001,6 +32206,11 @@
       </c>
       <c r="N443" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O443" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -30071,6 +32281,11 @@
       </c>
       <c r="N444" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30141,6 +32356,11 @@
       </c>
       <c r="N445" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -30203,6 +32423,11 @@
       </c>
       <c r="N446" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30273,6 +32498,11 @@
       </c>
       <c r="N447" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O447" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30335,6 +32565,11 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O448" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30397,6 +32632,11 @@
       </c>
       <c r="N449" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O449" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30467,6 +32707,11 @@
       </c>
       <c r="N450" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O450" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30537,6 +32782,11 @@
       </c>
       <c r="N451" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O451" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30607,6 +32857,11 @@
       </c>
       <c r="N452" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O452" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30677,6 +32932,11 @@
       </c>
       <c r="N453" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O453" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30747,6 +33007,11 @@
       </c>
       <c r="N454" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O454" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30817,6 +33082,11 @@
       </c>
       <c r="N455" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O455" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30887,6 +33157,11 @@
       </c>
       <c r="N456" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O456" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -30957,6 +33232,11 @@
       </c>
       <c r="N457" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O457" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31019,6 +33299,11 @@
       </c>
       <c r="N458" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O458" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31081,6 +33366,11 @@
       </c>
       <c r="N459" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O459" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31151,6 +33441,11 @@
       </c>
       <c r="N460" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O460" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31221,6 +33516,11 @@
       </c>
       <c r="N461" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O461" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31291,6 +33591,11 @@
       </c>
       <c r="N462" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O462" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31361,6 +33666,11 @@
       </c>
       <c r="N463" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O463" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31431,6 +33741,11 @@
       </c>
       <c r="N464" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O464" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31501,6 +33816,11 @@
       </c>
       <c r="N465" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O465" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31563,6 +33883,11 @@
       </c>
       <c r="N466" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O466" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31633,6 +33958,11 @@
       </c>
       <c r="N467" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O467" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31695,6 +34025,11 @@
       </c>
       <c r="N468" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O468" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31757,6 +34092,11 @@
       </c>
       <c r="N469" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O469" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31827,6 +34167,11 @@
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O470" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31897,6 +34242,11 @@
       </c>
       <c r="N471" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O471" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -31967,6 +34317,11 @@
       </c>
       <c r="N472" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O472" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -32037,6 +34392,11 @@
       </c>
       <c r="N473" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O473" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -32107,6 +34467,11 @@
       </c>
       <c r="N474" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O474" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32177,6 +34542,11 @@
       </c>
       <c r="N475" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O475" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -32239,6 +34609,11 @@
       </c>
       <c r="N476" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O476" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32309,6 +34684,11 @@
       </c>
       <c r="N477" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O477" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32371,6 +34751,11 @@
       </c>
       <c r="N478" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O478" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32433,6 +34818,11 @@
       </c>
       <c r="N479" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O479" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32503,6 +34893,11 @@
       </c>
       <c r="N480" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O480" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32573,6 +34968,11 @@
       </c>
       <c r="N481" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O481" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32643,6 +35043,11 @@
       </c>
       <c r="N482" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O482" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32713,6 +35118,11 @@
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O483" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32783,6 +35193,11 @@
       </c>
       <c r="N484" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O484" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32853,6 +35268,11 @@
       </c>
       <c r="N485" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O485" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -32923,6 +35343,11 @@
       </c>
       <c r="N486" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O486" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -32993,6 +35418,11 @@
       </c>
       <c r="N487" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O487" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33055,6 +35485,11 @@
       </c>
       <c r="N488" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O488" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33117,6 +35552,11 @@
       </c>
       <c r="N489" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O489" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33179,6 +35619,11 @@
       </c>
       <c r="N490" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O490" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33241,6 +35686,11 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O491" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33311,6 +35761,11 @@
       </c>
       <c r="N492" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O492" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33381,6 +35836,11 @@
       </c>
       <c r="N493" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O493" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33451,6 +35911,11 @@
       </c>
       <c r="N494" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O494" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33521,6 +35986,11 @@
       </c>
       <c r="N495" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O495" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33583,6 +36053,11 @@
       </c>
       <c r="N496" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O496" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33653,6 +36128,11 @@
       </c>
       <c r="N497" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O497" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33715,6 +36195,11 @@
       </c>
       <c r="N498" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O498" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33777,6 +36262,11 @@
       </c>
       <c r="N499" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O499" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33839,6 +36329,11 @@
       </c>
       <c r="N500" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O500" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33901,6 +36396,11 @@
       </c>
       <c r="N501" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O501" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -33971,6 +36471,11 @@
       </c>
       <c r="N502" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O502" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34041,6 +36546,11 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O503" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34111,6 +36621,11 @@
       </c>
       <c r="N504" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O504" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34181,6 +36696,11 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O505" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34251,6 +36771,11 @@
       </c>
       <c r="N506" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O506" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34321,6 +36846,11 @@
       </c>
       <c r="N507" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O507" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34383,6 +36913,11 @@
       </c>
       <c r="N508" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O508" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34445,6 +36980,11 @@
       </c>
       <c r="N509" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O509" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34507,6 +37047,11 @@
       </c>
       <c r="N510" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O510" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34569,6 +37114,11 @@
       </c>
       <c r="N511" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O511" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34639,6 +37189,11 @@
       </c>
       <c r="N512" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O512" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -34709,6 +37264,11 @@
       </c>
       <c r="N513" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O513" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -34779,6 +37339,11 @@
       </c>
       <c r="N514" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O514" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34849,6 +37414,11 @@
       </c>
       <c r="N515" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O515" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -34911,6 +37481,11 @@
       </c>
       <c r="N516" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O516" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -34981,6 +37556,11 @@
       </c>
       <c r="N517" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O517" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35043,6 +37623,11 @@
       </c>
       <c r="N518" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O518" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35105,6 +37690,11 @@
       </c>
       <c r="N519" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O519" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35167,6 +37757,11 @@
       </c>
       <c r="N520" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O520" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35229,6 +37824,11 @@
       </c>
       <c r="N521" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O521" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35299,6 +37899,11 @@
       </c>
       <c r="N522" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O522" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35369,6 +37974,11 @@
       </c>
       <c r="N523" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O523" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35439,6 +38049,11 @@
       </c>
       <c r="N524" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O524" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35509,6 +38124,11 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O525" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35571,6 +38191,11 @@
       </c>
       <c r="N526" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O526" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35641,6 +38266,11 @@
       </c>
       <c r="N527" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O527" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35703,6 +38333,11 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O528" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35765,6 +38400,11 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O529" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35827,6 +38467,11 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O530" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35889,6 +38534,11 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O531" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -35959,6 +38609,11 @@
       </c>
       <c r="N532" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O532" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36029,6 +38684,11 @@
       </c>
       <c r="N533" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O533" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36099,6 +38759,11 @@
       </c>
       <c r="N534" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O534" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36169,6 +38834,11 @@
       </c>
       <c r="N535" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O535" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36239,6 +38909,11 @@
       </c>
       <c r="N536" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O536" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -36309,6 +38984,11 @@
       </c>
       <c r="N537" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O537" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36371,6 +39051,11 @@
       </c>
       <c r="N538" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O538" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36433,6 +39118,11 @@
       </c>
       <c r="N539" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O539" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36495,6 +39185,11 @@
       </c>
       <c r="N540" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O540" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36557,6 +39252,11 @@
       </c>
       <c r="N541" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36627,6 +39327,11 @@
       </c>
       <c r="N542" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O542" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -36697,6 +39402,11 @@
       </c>
       <c r="N543" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O543" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -36767,6 +39477,11 @@
       </c>
       <c r="N544" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O544" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36837,6 +39552,11 @@
       </c>
       <c r="N545" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O545" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -36899,6 +39619,11 @@
       </c>
       <c r="N546" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O546" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -36969,6 +39694,11 @@
       </c>
       <c r="N547" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O547" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37031,6 +39761,11 @@
       </c>
       <c r="N548" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O548" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37093,6 +39828,11 @@
       </c>
       <c r="N549" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O549" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37155,6 +39895,11 @@
       </c>
       <c r="N550" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O550" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37217,6 +39962,11 @@
       </c>
       <c r="N551" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O551" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37279,6 +40029,11 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O552" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37349,6 +40104,11 @@
       </c>
       <c r="N553" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O553" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37419,6 +40179,11 @@
       </c>
       <c r="N554" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O554" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37489,6 +40254,11 @@
       </c>
       <c r="N555" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O555" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37551,6 +40321,11 @@
       </c>
       <c r="N556" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O556" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37621,6 +40396,11 @@
       </c>
       <c r="N557" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O557" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37683,6 +40463,11 @@
       </c>
       <c r="N558" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O558" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37745,6 +40530,11 @@
       </c>
       <c r="N559" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O559" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37807,6 +40597,11 @@
       </c>
       <c r="N560" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O560" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37869,6 +40664,11 @@
       </c>
       <c r="N561" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O561" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -37931,6 +40731,11 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O562" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38001,6 +40806,11 @@
       </c>
       <c r="N563" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O563" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38071,6 +40881,11 @@
       </c>
       <c r="N564" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O564" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38141,6 +40956,11 @@
       </c>
       <c r="N565" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O565" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38203,6 +41023,11 @@
       </c>
       <c r="N566" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O566" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38273,6 +41098,11 @@
       </c>
       <c r="N567" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O567" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38335,6 +41165,11 @@
       </c>
       <c r="N568" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O568" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38397,6 +41232,11 @@
       </c>
       <c r="N569" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O569" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38459,6 +41299,11 @@
       </c>
       <c r="N570" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O570" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38521,6 +41366,11 @@
       </c>
       <c r="N571" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O571" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38591,6 +41441,11 @@
       </c>
       <c r="N572" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O572" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -38661,6 +41516,11 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O573" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -38731,6 +41591,11 @@
       </c>
       <c r="N574" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O574" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38801,6 +41666,11 @@
       </c>
       <c r="N575" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O575" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -38863,6 +41733,11 @@
       </c>
       <c r="N576" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O576" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38933,6 +41808,11 @@
       </c>
       <c r="N577" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O577" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -38995,6 +41875,11 @@
       </c>
       <c r="N578" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O578" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39057,6 +41942,11 @@
       </c>
       <c r="N579" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O579" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39119,6 +42009,11 @@
       </c>
       <c r="N580" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O580" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39181,6 +42076,11 @@
       </c>
       <c r="N581" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O581" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39243,6 +42143,11 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
+          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+        </is>
+      </c>
+      <c r="O582" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39313,6 +42218,11 @@
       </c>
       <c r="N583" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O583" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39383,6 +42293,11 @@
       </c>
       <c r="N584" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O584" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39453,6 +42368,11 @@
       </c>
       <c r="N585" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O585" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -39515,12 +42435,18 @@
       </c>
       <c r="N586" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O586" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P586"/>
+  <dimension ref="A1:O586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O250" s="3" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O252" s="3" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税补贴</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O380" s="3" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O381" s="3" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O382" s="3" t="inlineStr">
@@ -28447,7 +28447,7 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O390" s="3" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O391" s="3" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O392" s="3" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O398" s="3" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O399" s="3" t="inlineStr">
@@ -29149,7 +29149,7 @@
       </c>
       <c r="N400" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O400" s="3" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O401" s="3" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O410" s="3" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O411" s="3" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="N421" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O421" s="3" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O431" s="3" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="N449" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O449" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr">
@@ -38400,7 +38400,7 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O552" s="3" t="inlineStr">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O562" s="3" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 无二按2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O582" s="3" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -7378,7 +7378,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr">
@@ -38400,7 +38400,7 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -7378,7 +7378,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr">
@@ -38400,7 +38400,7 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>3% 现金回赠 (提前成交2% + 现金回赠1%)</t>
+          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O250" s="3" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O252" s="3" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O380" s="3" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O381" s="3" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O382" s="3" t="inlineStr">
@@ -28447,7 +28447,7 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O390" s="3" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O391" s="3" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O392" s="3" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O398" s="3" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O399" s="3" t="inlineStr">
@@ -29149,7 +29149,7 @@
       </c>
       <c r="N400" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O400" s="3" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O401" s="3" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O410" s="3" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O411" s="3" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="N421" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O421" s="3" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O431" s="3" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="N449" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
         </is>
       </c>
       <c r="O449" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr">
@@ -38400,7 +38400,7 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O552" s="3" t="inlineStr">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O562" s="3" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 现金回赠2%)</t>
+          <t>3% 印花税直送 (代缴从价印花税)</t>
         </is>
       </c>
       <c r="O582" s="3" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -5414,7 +5414,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O250" s="3" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O252" s="3" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O266" s="3" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O278" s="3" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O380" s="3" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O381" s="3" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O382" s="3" t="inlineStr">
@@ -28447,7 +28447,7 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O390" s="3" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O391" s="3" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O392" s="3" t="inlineStr">
@@ -29015,7 +29015,7 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O398" s="3" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O399" s="3" t="inlineStr">
@@ -29149,7 +29149,7 @@
       </c>
       <c r="N400" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O400" s="3" t="inlineStr">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O401" s="3" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O402" s="3" t="inlineStr">
@@ -29859,7 +29859,7 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O410" s="3" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O411" s="3" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="N421" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O421" s="3" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O422" s="3" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O431" s="3" t="inlineStr">
@@ -31405,7 +31405,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O432" s="3" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O448" s="3" t="inlineStr">
@@ -32632,7 +32632,7 @@
       </c>
       <c r="N449" s="3" t="inlineStr">
         <is>
-          <t>4% 现金回赠 (提前成交2% + 特别现金2%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O449" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O491" s="3" t="inlineStr">
@@ -38333,7 +38333,7 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O528" s="3" t="inlineStr">
@@ -38400,7 +38400,7 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O529" s="3" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O530" s="3" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O531" s="3" t="inlineStr">
@@ -40029,7 +40029,7 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O552" s="3" t="inlineStr">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O562" s="3" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>3% 印花税直送 (代缴从价印花税)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O582" s="3" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O586"/>
+  <dimension ref="A1:N586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -753,12 +753,7 @@
           <t>付款办法</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>额外回赠/补贴</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>是否招标</t>
         </is>
@@ -830,11 +825,6 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -905,11 +895,6 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -980,11 +965,6 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1055,11 +1035,6 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1130,11 +1105,6 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1205,11 +1175,6 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1280,11 +1245,6 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1355,11 +1315,6 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1430,11 +1385,6 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -1505,11 +1455,6 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -1580,11 +1525,6 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1647,11 +1587,6 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1714,11 +1649,6 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1789,11 +1719,6 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1864,11 +1789,6 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1939,11 +1859,6 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2014,11 +1929,6 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2089,11 +1999,6 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2164,11 +2069,6 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2231,11 +2131,6 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2298,11 +2193,6 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2373,11 +2263,6 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -2448,11 +2333,6 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2515,11 +2395,6 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2582,11 +2457,6 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2649,11 +2519,6 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2724,11 +2589,6 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2799,11 +2659,6 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -2874,11 +2729,6 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -2949,11 +2799,6 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3024,11 +2869,6 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3091,11 +2931,6 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3158,11 +2993,6 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3225,11 +3055,6 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3300,11 +3125,6 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3375,11 +3195,6 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3450,11 +3265,6 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3525,11 +3335,6 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3600,11 +3405,6 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3667,11 +3467,6 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3734,11 +3529,6 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3801,11 +3591,6 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3876,11 +3661,6 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3943,11 +3723,6 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4010,11 +3785,6 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4077,11 +3847,6 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4152,11 +3917,6 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4219,11 +3979,6 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4286,11 +4041,6 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4353,11 +4103,6 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4428,11 +4173,6 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4503,11 +4243,6 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4570,11 +4305,6 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4645,11 +4375,6 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4720,11 +4445,6 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4787,11 +4507,6 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4854,11 +4569,6 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4921,11 +4631,6 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4996,11 +4701,6 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5063,11 +4763,6 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5130,11 +4825,6 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5197,11 +4887,6 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5272,11 +4957,6 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5347,11 +5027,6 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5414,11 +5089,6 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5481,11 +5151,6 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5556,11 +5221,6 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5623,11 +5283,6 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5690,11 +5345,6 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5757,11 +5407,6 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5832,11 +5477,6 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5899,11 +5539,6 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5966,11 +5601,6 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6041,11 +5671,6 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6116,11 +5741,6 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6191,11 +5811,6 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6258,11 +5873,6 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6325,11 +5935,6 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6400,11 +6005,6 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6467,11 +6067,6 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6534,11 +6129,6 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6601,11 +6191,6 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6676,11 +6261,6 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6743,11 +6323,6 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6810,11 +6385,6 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6885,11 +6455,6 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6960,11 +6525,6 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7035,11 +6595,6 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O90" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7102,11 +6657,6 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7169,11 +6719,6 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7244,11 +6789,6 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7311,11 +6851,6 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7378,11 +6913,6 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O95" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7445,11 +6975,6 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O96" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7520,11 +7045,6 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7595,11 +7115,6 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7670,11 +7185,6 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7745,11 +7255,6 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7820,11 +7325,6 @@
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7887,11 +7387,6 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -7954,11 +7449,6 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8021,11 +7511,6 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O104" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8088,11 +7573,6 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O105" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8155,11 +7635,6 @@
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O106" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8222,11 +7697,6 @@
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8289,11 +7759,6 @@
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O108" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8364,11 +7829,6 @@
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O109" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8439,11 +7899,6 @@
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8506,11 +7961,6 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O111" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8581,11 +8031,6 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O112" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -8656,11 +8101,6 @@
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O113" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8723,11 +8163,6 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O114" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8790,11 +8225,6 @@
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O115" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8857,11 +8287,6 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O116" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8924,11 +8349,6 @@
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O117" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -8991,11 +8411,6 @@
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O118" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9058,11 +8473,6 @@
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O119" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9125,11 +8535,6 @@
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O120" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9200,11 +8605,6 @@
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O121" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9267,11 +8667,6 @@
       </c>
       <c r="N122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O122" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9334,11 +8729,6 @@
       </c>
       <c r="N123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O123" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9409,11 +8799,6 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O124" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9484,11 +8869,6 @@
       </c>
       <c r="N125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O125" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9559,11 +8939,6 @@
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O126" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9634,11 +9009,6 @@
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9701,11 +9071,6 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O128" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9776,11 +9141,6 @@
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9843,11 +9203,6 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9910,11 +9265,6 @@
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O131" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -9977,11 +9327,6 @@
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O132" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10052,11 +9397,6 @@
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10127,11 +9467,6 @@
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O134" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10194,11 +9529,6 @@
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10269,11 +9599,6 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O136" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10344,11 +9669,6 @@
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O137" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10411,11 +9731,6 @@
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10486,11 +9801,6 @@
       </c>
       <c r="N139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O139" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10561,11 +9871,6 @@
       </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O140" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10628,11 +9933,6 @@
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O141" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10695,11 +9995,6 @@
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O142" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10762,11 +10057,6 @@
       </c>
       <c r="N143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O143" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10829,11 +10119,6 @@
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O144" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10904,11 +10189,6 @@
       </c>
       <c r="N145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O145" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -10971,11 +10251,6 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O146" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11038,11 +10313,6 @@
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O147" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11113,11 +10383,6 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O148" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -11188,11 +10453,6 @@
       </c>
       <c r="N149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O149" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11263,11 +10523,6 @@
       </c>
       <c r="N150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O150" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11338,11 +10593,6 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O151" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11413,11 +10663,6 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O152" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11488,11 +10733,6 @@
       </c>
       <c r="N153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O153" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11555,11 +10795,6 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O154" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11630,11 +10865,6 @@
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O155" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11697,11 +10927,6 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O156" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11772,11 +10997,6 @@
       </c>
       <c r="N157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O157" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11839,11 +11059,6 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O158" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11914,11 +11129,6 @@
       </c>
       <c r="N159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O159" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -11989,11 +11199,6 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O160" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12064,11 +11269,6 @@
       </c>
       <c r="N161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O161" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12139,11 +11339,6 @@
       </c>
       <c r="N162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O162" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12214,11 +11409,6 @@
       </c>
       <c r="N163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O163" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12289,11 +11479,6 @@
       </c>
       <c r="N164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O164" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12364,11 +11549,6 @@
       </c>
       <c r="N165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O165" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12431,11 +11611,6 @@
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O166" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12498,11 +11673,6 @@
       </c>
       <c r="N167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O167" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12565,11 +11735,6 @@
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O168" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12640,11 +11805,6 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12715,11 +11875,6 @@
       </c>
       <c r="N170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O170" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12782,11 +11937,6 @@
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12857,11 +12007,6 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O172" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12932,11 +12077,6 @@
       </c>
       <c r="N173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -12999,11 +12139,6 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O174" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13074,11 +12209,6 @@
       </c>
       <c r="N175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13141,11 +12271,6 @@
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O176" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13208,11 +12333,6 @@
       </c>
       <c r="N177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O177" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13275,11 +12395,6 @@
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O178" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13342,11 +12457,6 @@
       </c>
       <c r="N179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O179" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13409,11 +12519,6 @@
       </c>
       <c r="N180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O180" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13484,11 +12589,6 @@
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O181" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13551,11 +12651,6 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O182" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13618,11 +12713,6 @@
       </c>
       <c r="N183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O183" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13693,11 +12783,6 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O184" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -13768,11 +12853,6 @@
       </c>
       <c r="N185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O185" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13835,11 +12915,6 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O186" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13910,11 +12985,6 @@
       </c>
       <c r="N187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O187" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -13977,11 +13047,6 @@
       </c>
       <c r="N188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O188" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14052,11 +13117,6 @@
       </c>
       <c r="N189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O189" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14119,11 +13179,6 @@
       </c>
       <c r="N190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O190" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14194,11 +13249,6 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O191" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14261,11 +13311,6 @@
       </c>
       <c r="N192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O192" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14336,11 +13381,6 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O193" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14403,11 +13443,6 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O194" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14478,11 +13513,6 @@
       </c>
       <c r="N195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O195" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14553,11 +13583,6 @@
       </c>
       <c r="N196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O196" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14628,11 +13653,6 @@
       </c>
       <c r="N197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O197" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14695,11 +13715,6 @@
       </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O198" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14770,11 +13785,6 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O199" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14845,11 +13855,6 @@
       </c>
       <c r="N200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O200" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14920,11 +13925,6 @@
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O201" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -14987,11 +13987,6 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O202" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15054,11 +14049,6 @@
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O203" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15121,11 +14111,6 @@
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O204" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15196,11 +14181,6 @@
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O205" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15263,11 +14243,6 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O206" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15338,11 +14313,6 @@
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O207" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15413,11 +14383,6 @@
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O208" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15488,11 +14453,6 @@
       </c>
       <c r="N209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O209" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15555,11 +14515,6 @@
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O210" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15630,11 +14585,6 @@
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O211" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15705,11 +14655,6 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O212" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15772,11 +14717,6 @@
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O213" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15839,11 +14779,6 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O214" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15906,11 +14841,6 @@
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O215" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -15973,11 +14903,6 @@
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O216" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16048,11 +14973,6 @@
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O217" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16123,11 +15043,6 @@
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O218" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16190,11 +15105,6 @@
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O219" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16265,11 +15175,6 @@
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O220" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16340,11 +15245,6 @@
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O221" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16415,11 +15315,6 @@
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O222" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16490,11 +15385,6 @@
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O223" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16557,11 +15447,6 @@
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O224" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16632,11 +15517,6 @@
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O225" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16699,11 +15579,6 @@
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O226" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16774,11 +15649,6 @@
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O227" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16841,11 +15711,6 @@
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O228" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16916,11 +15781,6 @@
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O229" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -16991,11 +15851,6 @@
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O230" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17058,11 +15913,6 @@
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O231" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17133,11 +15983,6 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O232" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -17208,11 +16053,6 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O233" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17275,11 +16115,6 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O234" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17350,11 +16185,6 @@
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O235" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17417,11 +16247,6 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O236" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17484,11 +16309,6 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O237" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17551,11 +16371,6 @@
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O238" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17618,11 +16433,6 @@
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O239" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17685,11 +16495,6 @@
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O240" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17760,11 +16565,6 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O241" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17835,11 +16635,6 @@
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O242" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17902,11 +16697,6 @@
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O243" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -17977,11 +16767,6 @@
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O244" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18052,11 +16837,6 @@
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O245" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18127,11 +16907,6 @@
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O246" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18202,11 +16977,6 @@
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O247" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18277,11 +17047,6 @@
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O248" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18352,11 +17117,6 @@
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O249" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18419,11 +17179,6 @@
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O250" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18494,11 +17249,6 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O251" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18561,11 +17311,6 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O252" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18636,11 +17381,6 @@
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O253" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18711,11 +17451,6 @@
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O254" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18786,11 +17521,6 @@
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O255" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18861,11 +17591,6 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O256" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -18936,11 +17661,6 @@
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O257" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19011,11 +17731,6 @@
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O258" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19086,11 +17801,6 @@
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O259" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19161,11 +17871,6 @@
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O260" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19236,11 +17941,6 @@
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O261" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19303,11 +18003,6 @@
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O262" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19370,11 +18065,6 @@
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O263" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19437,11 +18127,6 @@
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O264" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19512,11 +18197,6 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O265" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19579,11 +18259,6 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O266" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19654,11 +18329,6 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O267" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19729,11 +18399,6 @@
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O268" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -19804,11 +18469,6 @@
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O269" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19871,11 +18531,6 @@
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O270" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -19946,11 +18601,6 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O271" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20021,11 +18671,6 @@
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O272" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20096,11 +18741,6 @@
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O273" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20163,11 +18803,6 @@
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O274" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20230,11 +18865,6 @@
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O275" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20297,11 +18927,6 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O276" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20372,11 +18997,6 @@
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O277" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20439,11 +19059,6 @@
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O278" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20514,11 +19129,6 @@
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O279" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20589,11 +19199,6 @@
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O280" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20664,11 +19269,6 @@
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O281" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20731,11 +19331,6 @@
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O282" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20798,11 +19393,6 @@
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O283" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20865,11 +19455,6 @@
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O284" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20932,11 +19517,6 @@
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O285" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -20999,11 +19579,6 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O286" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21066,11 +19641,6 @@
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O287" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21133,11 +19703,6 @@
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O288" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21208,11 +19773,6 @@
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O289" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21275,11 +19835,6 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O290" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21350,11 +19905,6 @@
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O291" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21425,11 +19975,6 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O292" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21500,11 +20045,6 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O293" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21567,11 +20107,6 @@
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O294" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21634,11 +20169,6 @@
       </c>
       <c r="N295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O295" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21701,11 +20231,6 @@
       </c>
       <c r="N296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O296" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21768,11 +20293,6 @@
       </c>
       <c r="N297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O297" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21835,11 +20355,6 @@
       </c>
       <c r="N298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O298" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21902,11 +20417,6 @@
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O299" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -21969,11 +20479,6 @@
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O300" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22044,11 +20549,6 @@
       </c>
       <c r="N301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O301" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22111,11 +20611,6 @@
       </c>
       <c r="N302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O302" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22178,11 +20673,6 @@
       </c>
       <c r="N303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O303" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22253,11 +20743,6 @@
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O304" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -22320,11 +20805,6 @@
       </c>
       <c r="N305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O305" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22387,11 +20867,6 @@
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O306" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22454,11 +20929,6 @@
       </c>
       <c r="N307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O307" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22521,11 +20991,6 @@
       </c>
       <c r="N308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O308" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22596,11 +21061,6 @@
       </c>
       <c r="N309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O309" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22663,11 +21123,6 @@
       </c>
       <c r="N310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O310" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22730,11 +21185,6 @@
       </c>
       <c r="N311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O311" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22797,11 +21247,6 @@
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O312" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22872,11 +21317,6 @@
       </c>
       <c r="N313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O313" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -22939,11 +21379,6 @@
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O314" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23006,11 +21441,6 @@
       </c>
       <c r="N315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O315" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23081,11 +21511,6 @@
       </c>
       <c r="N316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O316" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23156,11 +21581,6 @@
       </c>
       <c r="N317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O317" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -23231,11 +21651,6 @@
       </c>
       <c r="N318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O318" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23306,11 +21721,6 @@
       </c>
       <c r="N319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O319" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -23381,11 +21791,6 @@
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O320" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23456,11 +21861,6 @@
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O321" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23523,11 +21923,6 @@
       </c>
       <c r="N322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O322" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23598,11 +21993,6 @@
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O323" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23673,11 +22063,6 @@
       </c>
       <c r="N324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O324" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23748,11 +22133,6 @@
       </c>
       <c r="N325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O325" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -23815,11 +22195,6 @@
       </c>
       <c r="N326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O326" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23890,11 +22265,6 @@
       </c>
       <c r="N327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O327" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -23965,11 +22335,6 @@
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O328" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -24040,11 +22405,6 @@
       </c>
       <c r="N329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O329" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24115,11 +22475,6 @@
       </c>
       <c r="N330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O330" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24190,11 +22545,6 @@
       </c>
       <c r="N331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O331" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24265,11 +22615,6 @@
       </c>
       <c r="N332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O332" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24332,11 +22677,6 @@
       </c>
       <c r="N333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O333" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24399,11 +22739,6 @@
       </c>
       <c r="N334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O334" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24474,11 +22809,6 @@
       </c>
       <c r="N335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O335" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24541,11 +22871,6 @@
       </c>
       <c r="N336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O336" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24616,11 +22941,6 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O337" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24691,11 +23011,6 @@
       </c>
       <c r="N338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O338" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24766,11 +23081,6 @@
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O339" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24841,11 +23151,6 @@
       </c>
       <c r="N340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O340" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -24908,11 +23213,6 @@
       </c>
       <c r="N341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O341" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -24975,11 +23275,6 @@
       </c>
       <c r="N342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O342" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25050,11 +23345,6 @@
       </c>
       <c r="N343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O343" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25125,11 +23415,6 @@
       </c>
       <c r="N344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O344" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -25192,11 +23477,6 @@
       </c>
       <c r="N345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O345" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25267,11 +23547,6 @@
       </c>
       <c r="N346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O346" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -25342,11 +23617,6 @@
       </c>
       <c r="N347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O347" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25417,11 +23687,6 @@
       </c>
       <c r="N348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O348" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25484,11 +23749,6 @@
       </c>
       <c r="N349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O349" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25559,11 +23819,6 @@
       </c>
       <c r="N350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O350" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25634,11 +23889,6 @@
       </c>
       <c r="N351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O351" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25709,11 +23959,6 @@
       </c>
       <c r="N352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O352" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25784,11 +24029,6 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O353" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25851,11 +24091,6 @@
       </c>
       <c r="N354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O354" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -25926,11 +24161,6 @@
       </c>
       <c r="N355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O355" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26001,11 +24231,6 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O356" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26068,11 +24293,6 @@
       </c>
       <c r="N357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O357" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26143,11 +24363,6 @@
       </c>
       <c r="N358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O358" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26218,11 +24433,6 @@
       </c>
       <c r="N359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O359" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26293,11 +24503,6 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O360" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26360,11 +24565,6 @@
       </c>
       <c r="N361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O361" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26427,11 +24627,6 @@
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O362" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26502,11 +24697,6 @@
       </c>
       <c r="N363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O363" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26577,11 +24767,6 @@
       </c>
       <c r="N364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O364" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26652,11 +24837,6 @@
       </c>
       <c r="N365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O365" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26727,11 +24907,6 @@
       </c>
       <c r="N366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O366" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26802,11 +24977,6 @@
       </c>
       <c r="N367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O367" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26877,11 +25047,6 @@
       </c>
       <c r="N368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O368" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -26944,11 +25109,6 @@
       </c>
       <c r="N369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O369" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27011,11 +25171,6 @@
       </c>
       <c r="N370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O370" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27086,11 +25241,6 @@
       </c>
       <c r="N371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O371" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27161,11 +25311,6 @@
       </c>
       <c r="N372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O372" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27236,11 +25381,6 @@
       </c>
       <c r="N373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O373" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27311,11 +25451,6 @@
       </c>
       <c r="N374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O374" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27386,11 +25521,6 @@
       </c>
       <c r="N375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O375" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27461,11 +25591,6 @@
       </c>
       <c r="N376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O376" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27536,11 +25661,6 @@
       </c>
       <c r="N377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O377" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27603,11 +25723,6 @@
       </c>
       <c r="N378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O378" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27670,11 +25785,6 @@
       </c>
       <c r="N379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O379" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27737,11 +25847,6 @@
       </c>
       <c r="N380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O380" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27804,11 +25909,6 @@
       </c>
       <c r="N381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O381" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27871,11 +25971,6 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O382" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -27946,11 +26041,6 @@
       </c>
       <c r="N383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O383" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28021,11 +26111,6 @@
       </c>
       <c r="N384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O384" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28096,11 +26181,6 @@
       </c>
       <c r="N385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O385" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28171,11 +26251,6 @@
       </c>
       <c r="N386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O386" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28246,11 +26321,6 @@
       </c>
       <c r="N387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O387" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28313,11 +26383,6 @@
       </c>
       <c r="N388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O388" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28380,11 +26445,6 @@
       </c>
       <c r="N389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O389" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28447,11 +26507,6 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O390" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28514,11 +26569,6 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O391" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28581,11 +26631,6 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O392" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28656,11 +26701,6 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O393" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28731,11 +26771,6 @@
       </c>
       <c r="N394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O394" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28806,11 +26841,6 @@
       </c>
       <c r="N395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O395" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28873,11 +26903,6 @@
       </c>
       <c r="N396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O396" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -28948,11 +26973,6 @@
       </c>
       <c r="N397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O397" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29015,11 +27035,6 @@
       </c>
       <c r="N398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O398" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29082,11 +27097,6 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O399" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29149,11 +27159,6 @@
       </c>
       <c r="N400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O400" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29216,11 +27221,6 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O401" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29283,11 +27283,6 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O402" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29358,11 +27353,6 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O403" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29433,11 +27423,6 @@
       </c>
       <c r="N404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O404" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29508,11 +27493,6 @@
       </c>
       <c r="N405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O405" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29583,11 +27563,6 @@
       </c>
       <c r="N406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O406" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29658,11 +27633,6 @@
       </c>
       <c r="N407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O407" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29725,11 +27695,6 @@
       </c>
       <c r="N408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O408" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29792,11 +27757,6 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O409" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29859,11 +27819,6 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O410" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -29926,11 +27881,6 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O411" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30001,11 +27951,6 @@
       </c>
       <c r="N412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O412" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -30076,11 +28021,6 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O413" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -30151,11 +28091,6 @@
       </c>
       <c r="N414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O414" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30226,11 +28161,6 @@
       </c>
       <c r="N415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O415" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -30293,11 +28223,6 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O416" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30368,11 +28293,6 @@
       </c>
       <c r="N417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O417" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30435,11 +28355,6 @@
       </c>
       <c r="N418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O418" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30502,11 +28417,6 @@
       </c>
       <c r="N419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O419" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30569,11 +28479,6 @@
       </c>
       <c r="N420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O420" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30636,11 +28541,6 @@
       </c>
       <c r="N421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O421" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30703,11 +28603,6 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O422" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30778,11 +28673,6 @@
       </c>
       <c r="N423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O423" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30853,11 +28743,6 @@
       </c>
       <c r="N424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O424" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30928,11 +28813,6 @@
       </c>
       <c r="N425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O425" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -30995,11 +28875,6 @@
       </c>
       <c r="N426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O426" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31070,11 +28945,6 @@
       </c>
       <c r="N427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O427" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31137,11 +29007,6 @@
       </c>
       <c r="N428" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O428" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31204,11 +29069,6 @@
       </c>
       <c r="N429" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O429" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31271,11 +29131,6 @@
       </c>
       <c r="N430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O430" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31338,11 +29193,6 @@
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O431" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31405,11 +29255,6 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O432" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31480,11 +29325,6 @@
       </c>
       <c r="N433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O433" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31555,11 +29395,6 @@
       </c>
       <c r="N434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O434" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31630,11 +29465,6 @@
       </c>
       <c r="N435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O435" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31697,11 +29527,6 @@
       </c>
       <c r="N436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O436" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31772,11 +29597,6 @@
       </c>
       <c r="N437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O437" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31839,11 +29659,6 @@
       </c>
       <c r="N438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O438" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31906,11 +29721,6 @@
       </c>
       <c r="N439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O439" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -31981,11 +29791,6 @@
       </c>
       <c r="N440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O440" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32056,11 +29861,6 @@
       </c>
       <c r="N441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O441" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32131,11 +29931,6 @@
       </c>
       <c r="N442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O442" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -32206,11 +30001,6 @@
       </c>
       <c r="N443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O443" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -32281,11 +30071,6 @@
       </c>
       <c r="N444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O444" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32356,11 +30141,6 @@
       </c>
       <c r="N445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O445" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -32423,11 +30203,6 @@
       </c>
       <c r="N446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O446" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32498,11 +30273,6 @@
       </c>
       <c r="N447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O447" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32565,11 +30335,6 @@
       </c>
       <c r="N448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O448" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32632,11 +30397,6 @@
       </c>
       <c r="N449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O449" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32707,11 +30467,6 @@
       </c>
       <c r="N450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O450" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32782,11 +30537,6 @@
       </c>
       <c r="N451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O451" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32857,11 +30607,6 @@
       </c>
       <c r="N452" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O452" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -32932,11 +30677,6 @@
       </c>
       <c r="N453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O453" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33007,11 +30747,6 @@
       </c>
       <c r="N454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O454" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33082,11 +30817,6 @@
       </c>
       <c r="N455" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O455" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33157,11 +30887,6 @@
       </c>
       <c r="N456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O456" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33232,11 +30957,6 @@
       </c>
       <c r="N457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O457" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33299,11 +31019,6 @@
       </c>
       <c r="N458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O458" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33366,11 +31081,6 @@
       </c>
       <c r="N459" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O459" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33441,11 +31151,6 @@
       </c>
       <c r="N460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O460" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33516,11 +31221,6 @@
       </c>
       <c r="N461" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O461" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33591,11 +31291,6 @@
       </c>
       <c r="N462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O462" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33666,11 +31361,6 @@
       </c>
       <c r="N463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O463" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33741,11 +31431,6 @@
       </c>
       <c r="N464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O464" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33816,11 +31501,6 @@
       </c>
       <c r="N465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O465" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33883,11 +31563,6 @@
       </c>
       <c r="N466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O466" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -33958,11 +31633,6 @@
       </c>
       <c r="N467" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O467" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34025,11 +31695,6 @@
       </c>
       <c r="N468" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O468" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34092,11 +31757,6 @@
       </c>
       <c r="N469" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O469" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34167,11 +31827,6 @@
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O470" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34242,11 +31897,6 @@
       </c>
       <c r="N471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O471" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34317,11 +31967,6 @@
       </c>
       <c r="N472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O472" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -34392,11 +32037,6 @@
       </c>
       <c r="N473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O473" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -34467,11 +32107,6 @@
       </c>
       <c r="N474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O474" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34542,11 +32177,6 @@
       </c>
       <c r="N475" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O475" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -34609,11 +32239,6 @@
       </c>
       <c r="N476" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O476" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34684,11 +32309,6 @@
       </c>
       <c r="N477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O477" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34751,11 +32371,6 @@
       </c>
       <c r="N478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O478" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34818,11 +32433,6 @@
       </c>
       <c r="N479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O479" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34893,11 +32503,6 @@
       </c>
       <c r="N480" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O480" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -34968,11 +32573,6 @@
       </c>
       <c r="N481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O481" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35043,11 +32643,6 @@
       </c>
       <c r="N482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O482" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35118,11 +32713,6 @@
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O483" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35193,11 +32783,6 @@
       </c>
       <c r="N484" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O484" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35268,11 +32853,6 @@
       </c>
       <c r="N485" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O485" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35343,11 +32923,6 @@
       </c>
       <c r="N486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O486" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -35418,11 +32993,6 @@
       </c>
       <c r="N487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O487" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35485,11 +33055,6 @@
       </c>
       <c r="N488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O488" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35552,11 +33117,6 @@
       </c>
       <c r="N489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O489" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35619,11 +33179,6 @@
       </c>
       <c r="N490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O490" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35686,11 +33241,6 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O491" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35761,11 +33311,6 @@
       </c>
       <c r="N492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O492" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35836,11 +33381,6 @@
       </c>
       <c r="N493" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O493" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35911,11 +33451,6 @@
       </c>
       <c r="N494" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O494" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -35986,11 +33521,6 @@
       </c>
       <c r="N495" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O495" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36053,11 +33583,6 @@
       </c>
       <c r="N496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O496" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36128,11 +33653,6 @@
       </c>
       <c r="N497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O497" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36195,11 +33715,6 @@
       </c>
       <c r="N498" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O498" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36262,11 +33777,6 @@
       </c>
       <c r="N499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O499" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36329,11 +33839,6 @@
       </c>
       <c r="N500" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O500" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36396,11 +33901,6 @@
       </c>
       <c r="N501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O501" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36471,11 +33971,6 @@
       </c>
       <c r="N502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O502" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36546,11 +34041,6 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O503" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36621,11 +34111,6 @@
       </c>
       <c r="N504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O504" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36696,11 +34181,6 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O505" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36771,11 +34251,6 @@
       </c>
       <c r="N506" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O506" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36846,11 +34321,6 @@
       </c>
       <c r="N507" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O507" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36913,11 +34383,6 @@
       </c>
       <c r="N508" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O508" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -36980,11 +34445,6 @@
       </c>
       <c r="N509" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O509" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37047,11 +34507,6 @@
       </c>
       <c r="N510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O510" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37114,11 +34569,6 @@
       </c>
       <c r="N511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O511" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37189,11 +34639,6 @@
       </c>
       <c r="N512" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O512" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -37264,11 +34709,6 @@
       </c>
       <c r="N513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O513" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -37339,11 +34779,6 @@
       </c>
       <c r="N514" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O514" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37414,11 +34849,6 @@
       </c>
       <c r="N515" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O515" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -37481,11 +34911,6 @@
       </c>
       <c r="N516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O516" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37556,11 +34981,6 @@
       </c>
       <c r="N517" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O517" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37623,11 +35043,6 @@
       </c>
       <c r="N518" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O518" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37690,11 +35105,6 @@
       </c>
       <c r="N519" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O519" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37757,11 +35167,6 @@
       </c>
       <c r="N520" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O520" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37824,11 +35229,6 @@
       </c>
       <c r="N521" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O521" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37899,11 +35299,6 @@
       </c>
       <c r="N522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O522" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -37974,11 +35369,6 @@
       </c>
       <c r="N523" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O523" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38049,11 +35439,6 @@
       </c>
       <c r="N524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O524" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38124,11 +35509,6 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O525" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38191,11 +35571,6 @@
       </c>
       <c r="N526" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O526" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38266,11 +35641,6 @@
       </c>
       <c r="N527" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O527" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38333,11 +35703,6 @@
       </c>
       <c r="N528" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O528" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38400,11 +35765,6 @@
       </c>
       <c r="N529" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O529" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38467,11 +35827,6 @@
       </c>
       <c r="N530" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O530" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38534,11 +35889,6 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O531" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38609,11 +35959,6 @@
       </c>
       <c r="N532" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O532" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38684,11 +36029,6 @@
       </c>
       <c r="N533" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O533" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38759,11 +36099,6 @@
       </c>
       <c r="N534" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O534" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38834,11 +36169,6 @@
       </c>
       <c r="N535" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O535" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -38909,11 +36239,6 @@
       </c>
       <c r="N536" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O536" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -38984,11 +36309,6 @@
       </c>
       <c r="N537" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O537" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39051,11 +36371,6 @@
       </c>
       <c r="N538" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O538" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39118,11 +36433,6 @@
       </c>
       <c r="N539" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O539" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39185,11 +36495,6 @@
       </c>
       <c r="N540" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O540" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39252,11 +36557,6 @@
       </c>
       <c r="N541" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O541" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39327,11 +36627,6 @@
       </c>
       <c r="N542" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O542" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -39402,11 +36697,6 @@
       </c>
       <c r="N543" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O543" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -39477,11 +36767,6 @@
       </c>
       <c r="N544" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O544" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39552,11 +36837,6 @@
       </c>
       <c r="N545" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O545" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -39619,11 +36899,6 @@
       </c>
       <c r="N546" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O546" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39694,11 +36969,6 @@
       </c>
       <c r="N547" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O547" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39761,11 +37031,6 @@
       </c>
       <c r="N548" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O548" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39828,11 +37093,6 @@
       </c>
       <c r="N549" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O549" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39895,11 +37155,6 @@
       </c>
       <c r="N550" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O550" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -39962,11 +37217,6 @@
       </c>
       <c r="N551" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O551" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40029,11 +37279,6 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O552" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40104,11 +37349,6 @@
       </c>
       <c r="N553" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O553" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40179,11 +37419,6 @@
       </c>
       <c r="N554" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O554" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40254,11 +37489,6 @@
       </c>
       <c r="N555" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O555" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40321,11 +37551,6 @@
       </c>
       <c r="N556" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O556" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40396,11 +37621,6 @@
       </c>
       <c r="N557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O557" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40463,11 +37683,6 @@
       </c>
       <c r="N558" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O558" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40530,11 +37745,6 @@
       </c>
       <c r="N559" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O559" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40597,11 +37807,6 @@
       </c>
       <c r="N560" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O560" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40664,11 +37869,6 @@
       </c>
       <c r="N561" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O561" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40731,11 +37931,6 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O562" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40806,11 +38001,6 @@
       </c>
       <c r="N563" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O563" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40881,11 +38071,6 @@
       </c>
       <c r="N564" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O564" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -40956,11 +38141,6 @@
       </c>
       <c r="N565" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O565" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41023,11 +38203,6 @@
       </c>
       <c r="N566" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O566" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41098,11 +38273,6 @@
       </c>
       <c r="N567" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O567" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41165,11 +38335,6 @@
       </c>
       <c r="N568" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O568" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41232,11 +38397,6 @@
       </c>
       <c r="N569" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O569" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41299,11 +38459,6 @@
       </c>
       <c r="N570" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O570" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41366,11 +38521,6 @@
       </c>
       <c r="N571" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O571" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41441,11 +38591,6 @@
       </c>
       <c r="N572" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O572" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -41516,11 +38661,6 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O573" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -41591,11 +38731,6 @@
       </c>
       <c r="N574" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O574" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41666,11 +38801,6 @@
       </c>
       <c r="N575" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O575" s="3" t="inlineStr">
-        <is>
           <t>是</t>
         </is>
       </c>
@@ -41733,11 +38863,6 @@
       </c>
       <c r="N576" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O576" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41808,11 +38933,6 @@
       </c>
       <c r="N577" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O577" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41875,11 +38995,6 @@
       </c>
       <c r="N578" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O578" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -41942,11 +39057,6 @@
       </c>
       <c r="N579" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O579" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42009,11 +39119,6 @@
       </c>
       <c r="N580" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O580" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42076,11 +39181,6 @@
       </c>
       <c r="N581" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O581" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42143,11 +39243,6 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O582" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42218,11 +39313,6 @@
       </c>
       <c r="N583" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O583" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42293,11 +39383,6 @@
       </c>
       <c r="N584" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O584" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42368,11 +39453,6 @@
       </c>
       <c r="N585" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O585" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -42434,11 +39514,6 @@
         </is>
       </c>
       <c r="N586" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O586" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M136" s="3" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -12743,38 +12743,30 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>34588000</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>38093</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L184" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K184" s="5" t="n">
+        <v>34588000</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>38093</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
@@ -12783,7 +12775,7 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13543,7 +13535,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -13553,12 +13545,12 @@
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J196" s="3" t="inlineStr">
@@ -13568,12 +13560,12 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
@@ -13583,7 +13575,7 @@
       </c>
       <c r="N196" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15943,7 +15935,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -17551,7 +17543,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -17561,12 +17553,12 @@
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J256" s="3" t="inlineStr">
@@ -17576,12 +17568,12 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
@@ -17591,7 +17583,7 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18351,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -19935,7 +19927,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -19945,12 +19937,12 @@
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J292" s="3" t="inlineStr">
@@ -19960,12 +19952,12 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
@@ -19975,7 +19967,7 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20703,38 +20695,30 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H304" s="5" t="n">
+        <v>33542000</v>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>36941</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L304" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K304" s="5" t="n">
+        <v>33542000</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>36941</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -20743,7 +20727,7 @@
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21471,7 +21455,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -21481,12 +21465,12 @@
       </c>
       <c r="H316" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I316" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J316" s="3" t="inlineStr">
@@ -21496,12 +21480,12 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M316" s="3" t="inlineStr">
@@ -21511,7 +21495,7 @@
       </c>
       <c r="N316" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27911,7 +27895,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -27981,38 +27965,30 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H413" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I413" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>20710000</v>
+      </c>
+      <c r="I413" s="5" t="n">
+        <v>38000</v>
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K413" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L413" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K413" s="5" t="n">
+        <v>20710000</v>
+      </c>
+      <c r="L413" s="5" t="n">
+        <v>38000</v>
       </c>
       <c r="M413" s="3" t="inlineStr">
         <is>
@@ -28021,7 +27997,7 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28121,38 +28097,30 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H415" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I415" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>18185000</v>
+      </c>
+      <c r="I415" s="5" t="n">
+        <v>40774</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K415" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L415" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K415" s="5" t="n">
+        <v>18185000</v>
+      </c>
+      <c r="L415" s="5" t="n">
+        <v>40774</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
@@ -28161,7 +28129,7 @@
       </c>
       <c r="N415" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28633,7 +28601,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -28643,12 +28611,12 @@
       </c>
       <c r="H423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J423" s="3" t="inlineStr">
@@ -28658,12 +28626,12 @@
       </c>
       <c r="K423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L423" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M423" s="3" t="inlineStr">
@@ -28673,7 +28641,7 @@
       </c>
       <c r="N423" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28773,7 +28741,7 @@
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G425" s="3" t="inlineStr">
@@ -28783,12 +28751,12 @@
       </c>
       <c r="H425" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I425" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J425" s="3" t="inlineStr">
@@ -28798,12 +28766,12 @@
       </c>
       <c r="K425" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L425" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M425" s="3" t="inlineStr">
@@ -28813,7 +28781,7 @@
       </c>
       <c r="N425" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29891,38 +29859,30 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H442" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I442" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>12532400</v>
+      </c>
+      <c r="I442" s="5" t="n">
+        <v>26218</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K442" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L442" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K442" s="5" t="n">
+        <v>12532400</v>
+      </c>
+      <c r="L442" s="5" t="n">
+        <v>26218</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
@@ -29931,7 +29891,7 @@
       </c>
       <c r="N442" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29961,7 +29921,7 @@
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr">
@@ -30101,7 +30061,7 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
@@ -31321,7 +31281,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -31331,12 +31291,12 @@
       </c>
       <c r="H463" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I463" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J463" s="3" t="inlineStr">
@@ -31346,12 +31306,12 @@
       </c>
       <c r="K463" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L463" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M463" s="3" t="inlineStr">
@@ -31361,7 +31321,7 @@
       </c>
       <c r="N463" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31461,7 +31421,7 @@
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -31471,12 +31431,12 @@
       </c>
       <c r="H465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J465" s="3" t="inlineStr">
@@ -31486,12 +31446,12 @@
       </c>
       <c r="K465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L465" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M465" s="3" t="inlineStr">
@@ -31501,7 +31461,7 @@
       </c>
       <c r="N465" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31887,7 @@
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -31997,7 +31957,7 @@
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr">
@@ -32137,7 +32097,7 @@
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
@@ -33481,7 +33441,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -33491,12 +33451,12 @@
       </c>
       <c r="H495" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I495" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J495" s="3" t="inlineStr">
@@ -33506,12 +33466,12 @@
       </c>
       <c r="K495" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L495" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M495" s="3" t="inlineStr">
@@ -33521,7 +33481,7 @@
       </c>
       <c r="N495" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34001,7 +33961,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -34011,12 +33971,12 @@
       </c>
       <c r="H503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J503" s="3" t="inlineStr">
@@ -34026,12 +33986,12 @@
       </c>
       <c r="K503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L503" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M503" s="3" t="inlineStr">
@@ -34041,7 +34001,7 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34559,7 @@
       </c>
       <c r="F512" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G512" s="3" t="inlineStr">
@@ -34669,7 +34629,7 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -34809,7 +34769,7 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
@@ -35259,7 +35219,7 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -35269,12 +35229,12 @@
       </c>
       <c r="H522" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I522" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J522" s="3" t="inlineStr">
@@ -35284,12 +35244,12 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M522" s="3" t="inlineStr">
@@ -35299,7 +35259,7 @@
       </c>
       <c r="N522" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36129,7 +36089,7 @@
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
@@ -36139,12 +36099,12 @@
       </c>
       <c r="H535" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I535" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J535" s="3" t="inlineStr">
@@ -36154,12 +36114,12 @@
       </c>
       <c r="K535" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L535" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M535" s="3" t="inlineStr">
@@ -36169,7 +36129,7 @@
       </c>
       <c r="N535" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36587,7 +36547,7 @@
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
@@ -36657,7 +36617,7 @@
       </c>
       <c r="F543" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
@@ -36797,7 +36757,7 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -37247,7 +37207,7 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
@@ -37255,31 +37215,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H552" s="5" t="n">
-        <v>13856600</v>
-      </c>
-      <c r="I552" s="5" t="n">
-        <v>28989</v>
+      <c r="H552" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I552" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K552" s="5" t="n">
-        <v>12470940</v>
-      </c>
-      <c r="L552" s="5" t="n">
-        <v>26090</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K552" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L552" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37277,7 @@
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
@@ -37319,12 +37287,12 @@
       </c>
       <c r="H553" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I553" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J553" s="3" t="inlineStr">
@@ -37334,12 +37302,12 @@
       </c>
       <c r="K553" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L553" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M553" s="3" t="inlineStr">
@@ -37349,7 +37317,7 @@
       </c>
       <c r="N553" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37449,7 +37417,7 @@
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
@@ -37459,12 +37427,12 @@
       </c>
       <c r="H555" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I555" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J555" s="3" t="inlineStr">
@@ -37474,12 +37442,12 @@
       </c>
       <c r="K555" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L555" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M555" s="3" t="inlineStr">
@@ -37489,7 +37457,7 @@
       </c>
       <c r="N555" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37899,7 +37867,7 @@
       </c>
       <c r="F562" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G562" s="3" t="inlineStr">
@@ -37907,31 +37875,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H562" s="5" t="n">
-        <v>13665300</v>
-      </c>
-      <c r="I562" s="5" t="n">
-        <v>28588</v>
+      <c r="H562" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I562" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K562" s="5" t="n">
-        <v>12298770</v>
-      </c>
-      <c r="L562" s="5" t="n">
-        <v>25730</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K562" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L562" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37937,7 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
@@ -37971,12 +37947,12 @@
       </c>
       <c r="H563" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I563" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J563" s="3" t="inlineStr">
@@ -37986,12 +37962,12 @@
       </c>
       <c r="K563" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L563" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M563" s="3" t="inlineStr">
@@ -38001,7 +37977,7 @@
       </c>
       <c r="N563" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38101,7 +38077,7 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
@@ -38111,12 +38087,12 @@
       </c>
       <c r="H565" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I565" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J565" s="3" t="inlineStr">
@@ -38126,12 +38102,12 @@
       </c>
       <c r="K565" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L565" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M565" s="3" t="inlineStr">
@@ -38141,7 +38117,7 @@
       </c>
       <c r="N565" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38551,38 +38527,30 @@
       </c>
       <c r="F572" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H572" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I572" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="H572" s="5" t="n">
+        <v>11780000</v>
+      </c>
+      <c r="I572" s="5" t="n">
+        <v>24644</v>
       </c>
       <c r="J572" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K572" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L572" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K572" s="5" t="n">
+        <v>11780000</v>
+      </c>
+      <c r="L572" s="5" t="n">
+        <v>24644</v>
       </c>
       <c r="M572" s="3" t="inlineStr">
         <is>
@@ -38591,7 +38559,7 @@
       </c>
       <c r="N572" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38621,38 +38589,30 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H573" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I573" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="n">
+        <v>16598000</v>
+      </c>
+      <c r="I573" s="5" t="n">
+        <v>30455</v>
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K573" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L573" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K573" s="5" t="n">
+        <v>16598000</v>
+      </c>
+      <c r="L573" s="5" t="n">
+        <v>30455</v>
       </c>
       <c r="M573" s="3" t="inlineStr">
         <is>
@@ -38661,7 +38621,7 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38761,38 +38721,30 @@
       </c>
       <c r="F575" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H575" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I575" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H575" s="5" t="n">
+        <v>14228000</v>
+      </c>
+      <c r="I575" s="5" t="n">
+        <v>31901</v>
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K575" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L575" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K575" s="5" t="n">
+        <v>14228000</v>
+      </c>
+      <c r="L575" s="5" t="n">
+        <v>31901</v>
       </c>
       <c r="M575" s="3" t="inlineStr">
         <is>
@@ -38801,7 +38753,7 @@
       </c>
       <c r="N575" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39211,7 +39163,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -39219,31 +39171,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H582" s="5" t="n">
-        <v>13203900</v>
-      </c>
-      <c r="I582" s="5" t="n">
-        <v>27623</v>
+      <c r="H582" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I582" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K582" s="5" t="n">
-        <v>11883510</v>
-      </c>
-      <c r="L582" s="5" t="n">
-        <v>24861</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K582" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L582" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39273,7 +39233,7 @@
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr">
@@ -39283,12 +39243,12 @@
       </c>
       <c r="H583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J583" s="3" t="inlineStr">
@@ -39298,12 +39258,12 @@
       </c>
       <c r="K583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L583" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M583" s="3" t="inlineStr">
@@ -39313,7 +39273,7 @@
       </c>
       <c r="N583" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39413,7 +39373,7 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
@@ -39423,12 +39383,12 @@
       </c>
       <c r="H585" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I585" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J585" s="3" t="inlineStr">
@@ -39438,12 +39398,12 @@
       </c>
       <c r="K585" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L585" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M585" s="3" t="inlineStr">
@@ -39453,7 +39413,7 @@
       </c>
       <c r="N585" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39520,8 +39480,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
@@ -39610,27 +39569,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -40995,12 +40954,12 @@
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -41221,12 +41180,12 @@
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr"/>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -41334,12 +41293,12 @@
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -41673,12 +41632,12 @@
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(已定价未售)</t>
+$3459万
+$38,093/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -41786,12 +41745,12 @@
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42125,12 +42084,12 @@
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr"/>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -42351,12 +42310,12 @@
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -42464,12 +42423,12 @@
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -42690,12 +42649,12 @@
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -42803,12 +42762,12 @@
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(已定价未售)</t>
+$3354万
+$36,941/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -42916,12 +42875,12 @@
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -43108,27 +43067,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -44349,12 +44308,12 @@
 (25年-11月-23日)</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1818万
+$40,774/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -44365,21 +44324,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$2071万
+$38,000/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -44444,28 +44403,28 @@
 (25年-11月-18日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
@@ -44634,12 +44593,12 @@
 (25年-11月-23日)</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -44650,21 +44609,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1253万
+$26,218/呎
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -44824,28 +44783,28 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -44919,12 +44878,12 @@
 (25年-11月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -44935,21 +44894,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="25" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -45109,12 +45068,12 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -45220,12 +45179,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr"/>
@@ -45299,12 +45258,12 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -45315,21 +45274,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="25" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="25" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -45419,12 +45378,12 @@
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -45489,12 +45448,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -45584,12 +45543,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -45600,21 +45559,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="25" t="inlineStr">
+      <c r="H37" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -45679,37 +45638,37 @@
 (25年-11月-05日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="25" t="inlineStr">
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1386万
-$28,989/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -45774,37 +45733,37 @@
 (25年-11月-13日)</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="F39" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="25" t="inlineStr">
+      <c r="H39" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1367万
-$28,588/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -45869,12 +45828,12 @@
 (25年-11月-10日)</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1423万
+$31,901/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -45885,21 +45844,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1660万
+$30,455/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
-      <c r="H40" s="25" t="inlineStr">
+      <c r="H40" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(已定价未售)</t>
+$1178万
+$24,644/呎
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -45964,37 +45923,37 @@
 (25年-12月-17日)</t>
         </is>
       </c>
-      <c r="D41" s="21" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="25" t="inlineStr">
+      <c r="H41" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1320万
-$27,623/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -26591,31 +26591,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H392" s="5" t="n">
-        <v>15659900</v>
-      </c>
-      <c r="I392" s="5" t="n">
-        <v>32761</v>
+      <c r="H392" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I392" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K392" s="5" t="n">
-        <v>14093910</v>
-      </c>
-      <c r="L392" s="5" t="n">
-        <v>29485</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K392" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L392" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27903,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -29199,31 +29207,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H432" s="5" t="n">
-        <v>15373100</v>
-      </c>
-      <c r="I432" s="5" t="n">
-        <v>32161</v>
+      <c r="H432" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I432" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K432" s="5" t="n">
-        <v>14911907</v>
-      </c>
-      <c r="L432" s="5" t="n">
-        <v>31196</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L432" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31211,7 +31227,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -31221,12 +31237,12 @@
       </c>
       <c r="H462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J462" s="3" t="inlineStr">
@@ -31236,12 +31252,12 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M462" s="3" t="inlineStr">
@@ -31251,7 +31267,7 @@
       </c>
       <c r="N462" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31887,7 +31903,7 @@
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G472" s="3" t="inlineStr">
@@ -34629,7 +34645,7 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
@@ -39890,7 +39906,7 @@
           <t>B | 1808呎 (4+房)
 $8281万
 $45,803/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
@@ -39906,7 +39922,7 @@
           <t>C | 1511呎 (4+房)
 $5435万
 $35,970/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="Q8" s="20" t="inlineStr"/>
@@ -40004,7 +40020,7 @@
           <t>B | 1808呎 (4+房)
 $8112万
 $44,866/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -40020,7 +40036,7 @@
           <t>C | 1511呎 (4+房)
 $5230万
 $34,613/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="Q10" s="20" t="inlineStr"/>
@@ -40049,7 +40065,7 @@
           <t>A | 2230呎 (4+房)
 $10510万
 $47,132/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -40061,7 +40077,7 @@
           <t>B | 1808呎 (4+房)
 $8018万
 $44,345/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
@@ -40077,7 +40093,7 @@
           <t>C | 1511呎 (4+房)
 $5818万
 $38,504/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr"/>
@@ -40163,7 +40179,7 @@
           <t>A | 2230呎 (4+房)
 $9525万
 $42,713/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -40175,7 +40191,7 @@
           <t>B | 1808呎 (4+房)
 $7512万
 $41,550/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
@@ -40191,7 +40207,7 @@
           <t>C | 1511呎 (4+房)
 $5671万
 $37,530/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr"/>
@@ -40277,7 +40293,7 @@
           <t>A | 2230呎 (4+房)
 $9321万
 $41,797/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -40289,7 +40305,7 @@
           <t>B | 1808呎 (4+房)
 $7006万
 $38,750/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -40305,7 +40321,7 @@
           <t>C | 1511呎 (4+房)
 $6222万
 $41,176/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
@@ -40334,7 +40350,7 @@
           <t>A | 2230呎 (4+房)
 $9332万
 $41,850/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -40346,7 +40362,7 @@
           <t>B | 1808呎 (4+房)
 $7239万
 $40,040/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -40362,7 +40378,7 @@
           <t>C | 1511呎 (4+房)
 $5553万
 $36,749/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr"/>
@@ -40391,7 +40407,7 @@
           <t>A | 2230呎 (4+房)
 $9228万
 $41,381/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -40403,7 +40419,7 @@
           <t>B | 1808呎 (4+房)
 $7230万
 $39,989/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -40419,7 +40435,7 @@
           <t>C | 1511呎 (4+房)
 $5485万
 $36,299/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
@@ -40460,7 +40476,7 @@
           <t>B | 1808呎 (4+房)
 $7096万
 $39,246/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -40505,7 +40521,7 @@
           <t>A | 2230呎 (4+房)
 $8977万
 $40,257/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -40517,7 +40533,7 @@
           <t>B | 1808呎 (4+房)
 $7060万
 $39,050/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -40533,7 +40549,7 @@
           <t>C | 1511呎 (4+房)
 $5419万
 $35,863/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="Q19" s="20" t="inlineStr"/>
@@ -40562,7 +40578,7 @@
           <t>A | 2230呎 (4+房)
 $8807万
 $39,494/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -40574,7 +40590,7 @@
           <t>B | 1808呎 (4+房)
 $7380万
 $40,821/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -40590,7 +40606,7 @@
           <t>C | 1513呎 (4+房)
 $5473万
 $36,174/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="Q20" s="20" t="inlineStr"/>
@@ -40628,7 +40644,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -40636,7 +40652,7 @@
           <t>A3 | 308呎 (1房)
 $979万
 $31,783/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40653,7 +40669,7 @@
           <t>B1 | 301呎 (1房)
 $827万
 $27,461/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -40661,7 +40677,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,599/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -40669,7 +40685,7 @@
           <t>B2 | 308呎 (1房)
 $814万
 $26,412/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -40685,7 +40701,7 @@
           <t>B5 | 307呎 (1房)
 $852万
 $27,747/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -40741,7 +40757,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -40749,7 +40765,7 @@
           <t>A3 | 308呎 (1房)
 $978万
 $31,751/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40766,7 +40782,7 @@
           <t>B1 | 301呎 (1房)
 $821万
 $27,276/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -40774,7 +40790,7 @@
           <t>B10 | 482呎 (2房)
 $1421万
 $29,485/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -40782,7 +40798,7 @@
           <t>B2 | 308呎 (1房)
 $807万
 $26,202/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -40798,7 +40814,7 @@
           <t>B5 | 307呎 (1房)
 $842万
 $27,417/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M22" s="25" t="inlineStr">
@@ -40967,7 +40983,7 @@
           <t>A2 | 450呎 (2房)
 $1658万
 $36,853/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40992,7 +41008,7 @@
           <t>B1 | 301呎 (1房)
 $810万
 $26,898/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -41008,7 +41024,7 @@
           <t>B2 | 308呎 (1房)
 $796万
 $25,839/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -41016,7 +41032,7 @@
           <t>B3 | 449呎 (2房)
 $1428万
 $31,794/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -41024,7 +41040,7 @@
           <t>B5 | 307呎 (1房)
 $826万
 $26,908/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M24" s="25" t="inlineStr">
@@ -41040,7 +41056,7 @@
           <t>B8 | 787呎 (3房)
 $2404万
 $30,544/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -41080,7 +41096,7 @@
           <t>A2 | 450呎 (2房)
 $1656万
 $36,804/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -41088,7 +41104,7 @@
           <t>A3 | 308呎 (1房)
 $1026万
 $33,320/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -41105,7 +41121,7 @@
           <t>B1 | 301呎 (1房)
 $805万
 $26,737/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -41113,7 +41129,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,605/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -41121,7 +41137,7 @@
           <t>B2 | 308呎 (1房)
 $790万
 $25,652/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -41129,7 +41145,7 @@
           <t>B3 | 449呎 (2房)
 $1391万
 $30,976/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L25" s="25" t="inlineStr">
@@ -41153,7 +41169,7 @@
           <t>B8 | 787呎 (3房)
 $2405万
 $30,564/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -41193,7 +41209,7 @@
           <t>A2 | 450呎 (2房)
 $1652万
 $36,700/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -41218,7 +41234,7 @@
           <t>B1 | 301呎 (1房)
 $770万
 $25,581/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -41234,7 +41250,7 @@
           <t>B2 | 308呎 (1房)
 $787万
 $25,550/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -41306,7 +41322,7 @@
           <t>A2 | 450呎 (2房)
 $1646万
 $36,578/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -41331,7 +41347,7 @@
           <t>B1 | 301呎 (1房)
 $766万
 $25,446/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -41339,7 +41355,7 @@
           <t>B10 | 482呎 (2房)
 $1337万
 $27,732/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -41347,7 +41363,7 @@
           <t>B2 | 308呎 (1房)
 $785万
 $25,480/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -41355,7 +41371,7 @@
           <t>B3 | 449呎 (2房)
 $1372万
 $30,557/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -41379,7 +41395,7 @@
           <t>B8 | 787呎 (3房)
 $2401万
 $30,508/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -41532,7 +41548,7 @@
           <t>A2 | 450呎 (2房)
 $1631万
 $36,238/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -41557,7 +41573,7 @@
           <t>B1 | 301呎 (1房)
 $762万
 $25,327/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -41565,7 +41581,7 @@
           <t>B10 | 482呎 (2房)
 $1310万
 $27,178/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -41573,7 +41589,7 @@
           <t>B2 | 308呎 (1房)
 $780万
 $25,328/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -41637,7 +41653,7 @@
           <t>A1 | 908呎 (4+房)
 $3459万
 $38,093/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -41645,7 +41661,7 @@
           <t>A2 | 450呎 (2房)
 $1595万
 $35,440/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -41653,7 +41669,7 @@
           <t>A3 | 308呎 (1房)
 $947万
 $30,732/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -41670,7 +41686,7 @@
           <t>B1 | 301呎 (1房)
 $761万
 $25,276/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -41678,7 +41694,7 @@
           <t>B10 | 482呎 (2房)
 $1282万
 $26,604/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -41686,7 +41702,7 @@
           <t>B2 | 308呎 (1房)
 $779万
 $25,277/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -41694,7 +41710,7 @@
           <t>B3 | 449呎 (2房)
 $1334万
 $29,711/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -41702,7 +41718,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,881/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -41718,7 +41734,7 @@
           <t>B8 | 787呎 (3房)
 $2312万
 $29,376/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -41783,7 +41799,7 @@
           <t>B1 | 301呎 (1房)
 $759万
 $25,226/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -41799,7 +41815,7 @@
           <t>B2 | 308呎 (1房)
 $777万
 $25,226/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -41815,7 +41831,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,860/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -41831,7 +41847,7 @@
           <t>B8 | 787呎 (3房)
 $2305万
 $29,288/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -41896,7 +41912,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,175/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -41904,7 +41920,7 @@
           <t>B10 | 482呎 (2房)
 $1278万
 $26,519/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -41912,7 +41928,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,144/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -41944,7 +41960,7 @@
           <t>B8 | 787呎 (3房)
 $2387万
 $30,326/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
@@ -41984,7 +42000,7 @@
           <t>A2 | 450呎 (2房)
 $1600万
 $35,556/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -42009,7 +42025,7 @@
           <t>B1 | 301呎 (1房)
 $756万
 $25,125/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -42017,7 +42033,7 @@
           <t>B10 | 482呎 (2房)
 $1256万
 $26,063/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -42025,7 +42041,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,126/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -42033,7 +42049,7 @@
           <t>B3 | 449呎 (2房)
 $1311万
 $29,190/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -42057,7 +42073,7 @@
           <t>B8 | 787呎 (3房)
 $2258万
 $28,689/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -42097,7 +42113,7 @@
           <t>A2 | 450呎 (2房)
 $1576万
 $35,026/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -42122,7 +42138,7 @@
           <t>B1 | 301呎 (1房)
 $753万
 $25,024/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -42138,7 +42154,7 @@
           <t>B2 | 308呎 (1房)
 $771万
 $25,025/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -42154,7 +42170,7 @@
           <t>B5 | 307呎 (1房)
 $823万
 $26,816/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -42210,7 +42226,7 @@
           <t>A2 | 450呎 (2房)
 $1526万
 $33,900/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -42235,7 +42251,7 @@
           <t>B1 | 301呎 (1房)
 $750万
 $24,924/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -42243,7 +42259,7 @@
           <t>B10 | 482呎 (2房)
 $1239万
 $25,705/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -42251,7 +42267,7 @@
           <t>B2 | 308呎 (1房)
 $768万
 $24,925/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -42259,7 +42275,7 @@
           <t>B3 | 449呎 (2房)
 $1305万
 $29,062/呎
-(26年-01月-28日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -42267,7 +42283,7 @@
           <t>B5 | 307呎 (1房)
 $820万
 $26,708/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -42283,7 +42299,7 @@
           <t>B8 | 787呎 (3房)
 $2296万
 $29,180/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -42461,7 +42477,7 @@
           <t>B1 | 301呎 (1房)
 $772万
 $25,635/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I37" s="25" t="inlineStr">
@@ -42477,7 +42493,7 @@
           <t>B2 | 308呎 (1房)
 $758万
 $24,626/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr">
@@ -42574,7 +42590,7 @@
           <t>B1 | 301呎 (1房)
 $765万
 $25,430/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -42582,7 +42598,7 @@
           <t>B10 | 482呎 (2房)
 $1220万
 $25,315/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -42590,7 +42606,7 @@
           <t>B2 | 308呎 (1房)
 $752万
 $24,429/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr">
@@ -42622,7 +42638,7 @@
           <t>B8 | 787呎 (3房)
 $2184万
 $27,750/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -42670,7 +42686,7 @@
           <t>A3 | 308呎 (1房)
 $899万
 $29,181/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -42687,7 +42703,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,193/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I39" s="23" t="inlineStr">
@@ -42695,7 +42711,7 @@
           <t>B10 | 482呎 (2房)
 $1212万
 $25,145/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
@@ -42703,7 +42719,7 @@
           <t>B2 | 308呎 (1房)
 $746万
 $24,233/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -42711,7 +42727,7 @@
           <t>B3 | 449呎 (2房)
 $1240万
 $27,627/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -42719,7 +42735,7 @@
           <t>B5 | 307呎 (1房)
 $793万
 $25,819/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M39" s="23" t="inlineStr">
@@ -42727,7 +42743,7 @@
           <t>B6 | 304呎 (1房)
 $785万
 $25,818/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
@@ -42735,7 +42751,7 @@
           <t>B8 | 787呎 (3房)
 $2169万
 $27,555/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -42767,7 +42783,7 @@
           <t>A1 | 908呎 (4+房)
 $3354万
 $36,941/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -42783,7 +42799,7 @@
           <t>A3 | 308呎 (1房)
 $861万
 $27,963/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -42800,7 +42816,7 @@
           <t>B1 | 301呎 (1房)
 $721万
 $23,946/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -42808,7 +42824,7 @@
           <t>B10 | 482呎 (2房)
 $1210万
 $25,104/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -42816,7 +42832,7 @@
           <t>B2 | 308呎 (1房)
 $738万
 $23,946/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -42824,7 +42840,7 @@
           <t>B3 | 449呎 (2房)
 $1260万
 $28,062/呎
-(26年-02月-02日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -42832,7 +42848,7 @@
           <t>B5 | 307呎 (1房)
 $785万
 $25,560/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M40" s="23" t="inlineStr">
@@ -42840,7 +42856,7 @@
           <t>B6 | 304呎 (1房)
 $776万
 $25,527/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N40" s="23" t="inlineStr">
@@ -42848,7 +42864,7 @@
           <t>B8 | 787呎 (3房)
 $2130万
 $27,062/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
@@ -42888,7 +42904,7 @@
           <t>A2 | 450呎 (2房)
 $1214万
 $26,979/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -42896,7 +42912,7 @@
           <t>A3 | 308呎 (1房)
 $845万
 $27,432/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -42913,7 +42929,7 @@
           <t>B1 | 301呎 (1房)
 $681万
 $22,617/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
@@ -42921,7 +42937,7 @@
           <t>B10 | 482呎 (2房)
 $1198万
 $24,861/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -42929,7 +42945,7 @@
           <t>B2 | 308呎 (1房)
 $697万
 $22,618/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K41" s="21" t="inlineStr">
@@ -42945,7 +42961,7 @@
           <t>B5 | 307呎 (1房)
 $777万
 $25,304/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M41" s="23" t="inlineStr">
@@ -42953,7 +42969,7 @@
           <t>B6 | 304呎 (1房)
 $769万
 $25,304/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
@@ -42961,7 +42977,7 @@
           <t>B8 | 787呎 (3房)
 $2157万
 $27,409/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -42969,7 +42985,7 @@
           <t>B9 | 296呎 (1房)
 $730万
 $24,675/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="P41" s="20" t="inlineStr"/>
@@ -43067,12 +43083,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -43082,12 +43098,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -43303,7 +43319,7 @@
           <t>C | 1227呎 (4+房)
 $5225万
 $42,586/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -43356,7 +43372,7 @@
           <t>C | 1227呎 (4+房)
 $4824万
 $39,314/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O8" s="22" t="inlineStr">
@@ -43436,7 +43452,7 @@
           <t>A | 1985呎 (4+房)
 $8348万
 $42,055/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -43462,7 +43478,7 @@
           <t>C | 1227呎 (4+房)
 $4330万
 $35,289/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -43470,7 +43486,7 @@
           <t>D | 1365呎 (4+房)
 $5191万
 $38,028/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr"/>
@@ -43568,7 +43584,7 @@
           <t>C | 1227呎 (4+房)
 $4668万
 $38,044/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O12" s="23" t="inlineStr">
@@ -43576,7 +43592,7 @@
           <t>D | 1365呎 (4+房)
 $5020万
 $36,777/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr"/>
@@ -43629,7 +43645,7 @@
           <t>D | 1365呎 (4+房)
 $4934万
 $36,147/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr"/>
@@ -43682,7 +43698,7 @@
           <t>D | 1365呎 (4+房)
 $4908万
 $35,956/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr"/>
@@ -43727,7 +43743,7 @@
           <t>C | 1227呎 (4+房)
 $4470万
 $36,430/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -43788,7 +43804,7 @@
           <t>D | 1365呎 (4+房)
 $4808万
 $35,223/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr"/>
@@ -43833,7 +43849,7 @@
           <t>C | 1227呎 (4+房)
 $4450万
 $36,267/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -43841,7 +43857,7 @@
           <t>D | 1365呎 (4+房)
 $4800万
 $35,165/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr"/>
@@ -43939,7 +43955,7 @@
           <t>C | 1227呎 (4+房)
 $4448万
 $36,251/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -43947,7 +43963,7 @@
           <t>D | 1365呎 (4+房)
 $4789万
 $35,084/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr"/>
@@ -44077,7 +44093,7 @@
           <t>B5 | 299呎 (1房)
 $828万
 $27,695/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -44085,7 +44101,7 @@
           <t>B6 | 297呎 (1房)
 $826万
 $27,810/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -44115,7 +44131,7 @@
           <t>A1 | 908呎 (4+房)
 $3710万
 $40,859/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -44146,8 +44162,8 @@
       <c r="H22" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1566万
-$32,761/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>
@@ -44172,7 +44188,7 @@
           <t>B5 | 299呎 (1房)
 $859万
 $28,723/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -44180,7 +44196,7 @@
           <t>B6 | 297呎 (1房)
 $824万
 $27,732/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44305,7 +44321,7 @@
           <t>A1 | 908呎 (4+房)
 $3657万
 $40,279/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -44313,7 +44329,7 @@
           <t>A2 | 446呎 (2房)
 $1818万
 $40,774/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -44329,16 +44345,16 @@
           <t>A5 | 545呎 (2房)
 $2071万
 $38,000/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -44362,7 +44378,7 @@
           <t>B5 | 299呎 (1房)
 $816万
 $27,280/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -44370,7 +44386,7 @@
           <t>B6 | 297呎 (1房)
 $814万
 $27,394/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -44400,7 +44416,7 @@
           <t>A1 | 908呎 (4+房)
 $3545万
 $39,040/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -44449,7 +44465,7 @@
           <t>B3 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -44457,7 +44473,7 @@
           <t>B5 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -44465,7 +44481,7 @@
           <t>B6 | 297呎 (1房)
 $810万
 $27,285/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -44495,7 +44511,7 @@
           <t>A1 | 908呎 (4+房)
 $3626万
 $39,932/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -44526,8 +44542,8 @@
       <c r="H26" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1537万
-$32,161/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>
@@ -44544,7 +44560,7 @@
           <t>B3 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -44552,7 +44568,7 @@
           <t>B5 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -44560,7 +44576,7 @@
           <t>B6 | 297呎 (1房)
 $798万
 $26,884/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -44590,7 +44606,7 @@
           <t>A1 | 908呎 (4+房)
 $3605万
 $39,705/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -44623,7 +44639,7 @@
           <t>B1 | 478呎 (2房)
 $1253万
 $26,218/呎
-(26年-07月-18日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -44647,7 +44663,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,428/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -44655,7 +44671,7 @@
           <t>B6 | 297呎 (1房)
 $818万
 $27,551/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -44780,7 +44796,7 @@
           <t>A1 | 908呎 (4+房)
 $3501万
 $38,558/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -44808,12 +44824,12 @@
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -44837,7 +44853,7 @@
           <t>B5 | 299呎 (1房)
 $768万
 $25,670/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -44845,7 +44861,7 @@
           <t>B6 | 297呎 (1房)
 $795万
 $26,760/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -44875,7 +44891,7 @@
           <t>A1 | 908呎 (4+房)
 $3335万
 $36,730/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -44903,12 +44919,12 @@
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -44932,7 +44948,7 @@
           <t>B5 | 299呎 (1房)
 $766万
 $25,618/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -44940,7 +44956,7 @@
           <t>B6 | 297呎 (1房)
 $793万
 $26,706/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -45027,7 +45043,7 @@
           <t>B5 | 299呎 (1房)
 $764万
 $25,567/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -45035,7 +45051,7 @@
           <t>B6 | 297呎 (1房)
 $791万
 $26,620/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -45065,7 +45081,7 @@
           <t>A1 | 908呎 (4+房)
 $3557万
 $39,172/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
@@ -45114,7 +45130,7 @@
           <t>B3 | 299呎 (1房)
 $792万
 $26,489/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -45122,7 +45138,7 @@
           <t>B5 | 299呎 (1房)
 $763万
 $25,516/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
@@ -45130,7 +45146,7 @@
           <t>B6 | 297呎 (1房)
 $789万
 $26,566/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -45201,7 +45217,7 @@
           <t>B2 | 302呎 (1房)
 $799万
 $26,470/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -45209,7 +45225,7 @@
           <t>B3 | 299呎 (1房)
 $789万
 $26,403/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -45217,7 +45233,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,436/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L33" s="23" t="inlineStr">
@@ -45225,7 +45241,7 @@
           <t>B6 | 297呎 (1房)
 $787万
 $26,513/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -45255,7 +45271,7 @@
           <t>A1 | 908呎 (4+房)
 $3610万
 $39,758/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -45274,12 +45290,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -45296,7 +45312,7 @@
           <t>B2 | 302呎 (1房)
 $796万
 $26,364/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -45304,7 +45320,7 @@
           <t>B3 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -45312,7 +45328,7 @@
           <t>B5 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">
@@ -45320,7 +45336,7 @@
           <t>B6 | 297呎 (1房)
 $785万
 $26,440/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -45350,7 +45366,7 @@
           <t>A1 | 908呎 (4+房)
 $3366万
 $37,070/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -45391,7 +45407,7 @@
           <t>B2 | 302呎 (1房)
 $792万
 $26,225/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -45399,7 +45415,7 @@
           <t>B3 | 299呎 (1房)
 $784万
 $26,225/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -45407,7 +45423,7 @@
           <t>B5 | 299呎 (1房)
 $783万
 $26,192/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -45415,7 +45431,7 @@
           <t>B6 | 297呎 (1房)
 $782万
 $26,334/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -45540,7 +45556,7 @@
           <t>A1 | 908呎 (4+房)
 $3136万
 $34,543/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -45581,7 +45597,7 @@
           <t>B2 | 302呎 (1房)
 $782万
 $25,878/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -45589,7 +45605,7 @@
           <t>B3 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -45597,7 +45613,7 @@
           <t>B5 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L37" s="23" t="inlineStr">
@@ -45605,7 +45621,7 @@
           <t>B6 | 297呎 (1房)
 $773万
 $26,019/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
@@ -45635,7 +45651,7 @@
           <t>A1 | 908呎 (4+房)
 $3033万
 $33,401/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
@@ -45676,7 +45692,7 @@
           <t>B2 | 302呎 (1房)
 $776万
 $25,704/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -45684,7 +45700,7 @@
           <t>B3 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
@@ -45692,7 +45708,7 @@
           <t>B5 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L38" s="23" t="inlineStr">
@@ -45700,7 +45716,7 @@
           <t>B6 | 297呎 (1房)
 $767万
 $25,810/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
@@ -45730,7 +45746,7 @@
           <t>A1 | 908呎 (4+房)
 $3064万
 $33,745/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
@@ -45779,7 +45795,7 @@
           <t>B3 | 299呎 (1房)
 $745万
 $24,902/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -45787,7 +45803,7 @@
           <t>B5 | 299呎 (1房)
 $718万
 $23,998/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -45795,7 +45811,7 @@
           <t>B6 | 297呎 (1房)
 $716万
 $24,098/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -45825,7 +45841,7 @@
           <t>A1 | 908呎 (4+房)
 $3012万
 $33,172/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -45833,7 +45849,7 @@
           <t>A2 | 446呎 (2房)
 $1423万
 $31,901/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -45849,7 +45865,7 @@
           <t>A5 | 545呎 (2房)
 $1660万
 $30,455/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -45858,7 +45874,7 @@
           <t>B1 | 478呎 (2房)
 $1178万
 $24,644/呎
-(26年-07月-18日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -45866,7 +45882,7 @@
           <t>B2 | 302呎 (1房)
 $746万
 $24,686/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -45874,7 +45890,7 @@
           <t>B3 | 299呎 (1房)
 $738万
 $24,685/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -45882,7 +45898,7 @@
           <t>B5 | 299呎 (1房)
 $710万
 $23,758/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -45890,7 +45906,7 @@
           <t>B6 | 297呎 (1房)
 $709万
 $23,857/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M40" s="21" t="inlineStr">
@@ -45920,7 +45936,7 @@
           <t>A1 | 874呎 (4+房)
 $2659万
 $30,427/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
@@ -45961,7 +45977,7 @@
           <t>B2 | 302呎 (1房)
 $719万
 $23,809/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -45969,7 +45985,7 @@
           <t>B3 | 299呎 (1房)
 $712万
 $23,808/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
@@ -45977,7 +45993,7 @@
           <t>B5 | 299呎 (1房)
 $685万
 $22,923/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="L41" s="23" t="inlineStr">
@@ -45985,7 +46001,7 @@
           <t>B6 | 297呎 (1房)
 $683万
 $22,985/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M41" s="21" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -39906,7 +39906,7 @@
           <t>B | 1808呎 (4+房)
 $8281万
 $45,803/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
@@ -39922,7 +39922,7 @@
           <t>C | 1511呎 (4+房)
 $5435万
 $35,970/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="Q8" s="20" t="inlineStr"/>
@@ -40020,7 +40020,7 @@
           <t>B | 1808呎 (4+房)
 $8112万
 $44,866/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -40036,7 +40036,7 @@
           <t>C | 1511呎 (4+房)
 $5230万
 $34,613/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="Q10" s="20" t="inlineStr"/>
@@ -40065,7 +40065,7 @@
           <t>A | 2230呎 (4+房)
 $10510万
 $47,132/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -40077,7 +40077,7 @@
           <t>B | 1808呎 (4+房)
 $8018万
 $44,345/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
@@ -40093,7 +40093,7 @@
           <t>C | 1511呎 (4+房)
 $5818万
 $38,504/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr"/>
@@ -40179,7 +40179,7 @@
           <t>A | 2230呎 (4+房)
 $9525万
 $42,713/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -40191,7 +40191,7 @@
           <t>B | 1808呎 (4+房)
 $7512万
 $41,550/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
@@ -40207,7 +40207,7 @@
           <t>C | 1511呎 (4+房)
 $5671万
 $37,530/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr"/>
@@ -40293,7 +40293,7 @@
           <t>A | 2230呎 (4+房)
 $9321万
 $41,797/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -40305,7 +40305,7 @@
           <t>B | 1808呎 (4+房)
 $7006万
 $38,750/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -40321,7 +40321,7 @@
           <t>C | 1511呎 (4+房)
 $6222万
 $41,176/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
@@ -40350,7 +40350,7 @@
           <t>A | 2230呎 (4+房)
 $9332万
 $41,850/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -40362,7 +40362,7 @@
           <t>B | 1808呎 (4+房)
 $7239万
 $40,040/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -40378,7 +40378,7 @@
           <t>C | 1511呎 (4+房)
 $5553万
 $36,749/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr"/>
@@ -40407,7 +40407,7 @@
           <t>A | 2230呎 (4+房)
 $9228万
 $41,381/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -40419,7 +40419,7 @@
           <t>B | 1808呎 (4+房)
 $7230万
 $39,989/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -40435,7 +40435,7 @@
           <t>C | 1511呎 (4+房)
 $5485万
 $36,299/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
@@ -40476,7 +40476,7 @@
           <t>B | 1808呎 (4+房)
 $7096万
 $39,246/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -40521,7 +40521,7 @@
           <t>A | 2230呎 (4+房)
 $8977万
 $40,257/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -40533,7 +40533,7 @@
           <t>B | 1808呎 (4+房)
 $7060万
 $39,050/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -40549,7 +40549,7 @@
           <t>C | 1511呎 (4+房)
 $5419万
 $35,863/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="Q19" s="20" t="inlineStr"/>
@@ -40578,7 +40578,7 @@
           <t>A | 2230呎 (4+房)
 $8807万
 $39,494/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -40590,7 +40590,7 @@
           <t>B | 1808呎 (4+房)
 $7380万
 $40,821/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -40606,7 +40606,7 @@
           <t>C | 1513呎 (4+房)
 $5473万
 $36,174/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="Q20" s="20" t="inlineStr"/>
@@ -40644,7 +40644,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -40652,7 +40652,7 @@
           <t>A3 | 308呎 (1房)
 $979万
 $31,783/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40669,7 +40669,7 @@
           <t>B1 | 301呎 (1房)
 $827万
 $27,461/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -40677,7 +40677,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,599/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -40685,7 +40685,7 @@
           <t>B2 | 308呎 (1房)
 $814万
 $26,412/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -40701,7 +40701,7 @@
           <t>B5 | 307呎 (1房)
 $852万
 $27,747/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="M21" s="25" t="inlineStr">
@@ -40757,7 +40757,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -40765,7 +40765,7 @@
           <t>A3 | 308呎 (1房)
 $978万
 $31,751/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40782,7 +40782,7 @@
           <t>B1 | 301呎 (1房)
 $821万
 $27,276/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -40790,7 +40790,7 @@
           <t>B10 | 482呎 (2房)
 $1421万
 $29,485/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -40798,7 +40798,7 @@
           <t>B2 | 308呎 (1房)
 $807万
 $26,202/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -40814,7 +40814,7 @@
           <t>B5 | 307呎 (1房)
 $842万
 $27,417/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M22" s="25" t="inlineStr">
@@ -40983,7 +40983,7 @@
           <t>A2 | 450呎 (2房)
 $1658万
 $36,853/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -41008,7 +41008,7 @@
           <t>B1 | 301呎 (1房)
 $810万
 $26,898/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -41024,7 +41024,7 @@
           <t>B2 | 308呎 (1房)
 $796万
 $25,839/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -41032,7 +41032,7 @@
           <t>B3 | 449呎 (2房)
 $1428万
 $31,794/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -41040,7 +41040,7 @@
           <t>B5 | 307呎 (1房)
 $826万
 $26,908/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="M24" s="25" t="inlineStr">
@@ -41056,7 +41056,7 @@
           <t>B8 | 787呎 (3房)
 $2404万
 $30,544/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -41096,7 +41096,7 @@
           <t>A2 | 450呎 (2房)
 $1656万
 $36,804/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -41104,7 +41104,7 @@
           <t>A3 | 308呎 (1房)
 $1026万
 $33,320/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -41121,7 +41121,7 @@
           <t>B1 | 301呎 (1房)
 $805万
 $26,737/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -41129,7 +41129,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,605/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -41137,7 +41137,7 @@
           <t>B2 | 308呎 (1房)
 $790万
 $25,652/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -41145,7 +41145,7 @@
           <t>B3 | 449呎 (2房)
 $1391万
 $30,976/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="L25" s="25" t="inlineStr">
@@ -41169,7 +41169,7 @@
           <t>B8 | 787呎 (3房)
 $2405万
 $30,564/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -41209,7 +41209,7 @@
           <t>A2 | 450呎 (2房)
 $1652万
 $36,700/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -41234,7 +41234,7 @@
           <t>B1 | 301呎 (1房)
 $770万
 $25,581/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>B2 | 308呎 (1房)
 $787万
 $25,550/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -41322,7 +41322,7 @@
           <t>A2 | 450呎 (2房)
 $1646万
 $36,578/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -41347,7 +41347,7 @@
           <t>B1 | 301呎 (1房)
 $766万
 $25,446/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -41355,7 +41355,7 @@
           <t>B10 | 482呎 (2房)
 $1337万
 $27,732/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -41363,7 +41363,7 @@
           <t>B2 | 308呎 (1房)
 $785万
 $25,480/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -41371,7 +41371,7 @@
           <t>B3 | 449呎 (2房)
 $1372万
 $30,557/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -41395,7 +41395,7 @@
           <t>B8 | 787呎 (3房)
 $2401万
 $30,508/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -41548,7 +41548,7 @@
           <t>A2 | 450呎 (2房)
 $1631万
 $36,238/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -41573,7 +41573,7 @@
           <t>B1 | 301呎 (1房)
 $762万
 $25,327/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -41581,7 +41581,7 @@
           <t>B10 | 482呎 (2房)
 $1310万
 $27,178/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -41589,7 +41589,7 @@
           <t>B2 | 308呎 (1房)
 $780万
 $25,328/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -41653,7 +41653,7 @@
           <t>A1 | 908呎 (4+房)
 $3459万
 $38,093/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -41661,7 +41661,7 @@
           <t>A2 | 450呎 (2房)
 $1595万
 $35,440/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -41669,7 +41669,7 @@
           <t>A3 | 308呎 (1房)
 $947万
 $30,732/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -41686,7 +41686,7 @@
           <t>B1 | 301呎 (1房)
 $761万
 $25,276/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -41694,7 +41694,7 @@
           <t>B10 | 482呎 (2房)
 $1282万
 $26,604/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -41702,7 +41702,7 @@
           <t>B2 | 308呎 (1房)
 $779万
 $25,277/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -41710,7 +41710,7 @@
           <t>B3 | 449呎 (2房)
 $1334万
 $29,711/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -41718,7 +41718,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,881/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -41734,7 +41734,7 @@
           <t>B8 | 787呎 (3房)
 $2312万
 $29,376/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -41799,7 +41799,7 @@
           <t>B1 | 301呎 (1房)
 $759万
 $25,226/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -41815,7 +41815,7 @@
           <t>B2 | 308呎 (1房)
 $777万
 $25,226/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -41831,7 +41831,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,860/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>B8 | 787呎 (3房)
 $2305万
 $29,288/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -41912,7 +41912,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,175/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -41920,7 +41920,7 @@
           <t>B10 | 482呎 (2房)
 $1278万
 $26,519/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -41928,7 +41928,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,144/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -41960,7 +41960,7 @@
           <t>B8 | 787呎 (3房)
 $2387万
 $30,326/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
@@ -42000,7 +42000,7 @@
           <t>A2 | 450呎 (2房)
 $1600万
 $35,556/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -42025,7 +42025,7 @@
           <t>B1 | 301呎 (1房)
 $756万
 $25,125/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -42033,7 +42033,7 @@
           <t>B10 | 482呎 (2房)
 $1256万
 $26,063/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -42041,7 +42041,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,126/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -42049,7 +42049,7 @@
           <t>B3 | 449呎 (2房)
 $1311万
 $29,190/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -42073,7 +42073,7 @@
           <t>B8 | 787呎 (3房)
 $2258万
 $28,689/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -42113,7 +42113,7 @@
           <t>A2 | 450呎 (2房)
 $1576万
 $35,026/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -42138,7 +42138,7 @@
           <t>B1 | 301呎 (1房)
 $753万
 $25,024/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -42154,7 +42154,7 @@
           <t>B2 | 308呎 (1房)
 $771万
 $25,025/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -42170,7 +42170,7 @@
           <t>B5 | 307呎 (1房)
 $823万
 $26,816/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -42226,7 +42226,7 @@
           <t>A2 | 450呎 (2房)
 $1526万
 $33,900/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -42251,7 +42251,7 @@
           <t>B1 | 301呎 (1房)
 $750万
 $24,924/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -42259,7 +42259,7 @@
           <t>B10 | 482呎 (2房)
 $1239万
 $25,705/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -42267,7 +42267,7 @@
           <t>B2 | 308呎 (1房)
 $768万
 $24,925/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -42275,7 +42275,7 @@
           <t>B3 | 449呎 (2房)
 $1305万
 $29,062/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -42283,7 +42283,7 @@
           <t>B5 | 307呎 (1房)
 $820万
 $26,708/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -42299,7 +42299,7 @@
           <t>B8 | 787呎 (3房)
 $2296万
 $29,180/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -42477,7 +42477,7 @@
           <t>B1 | 301呎 (1房)
 $772万
 $25,635/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="I37" s="25" t="inlineStr">
@@ -42493,7 +42493,7 @@
           <t>B2 | 308呎 (1房)
 $758万
 $24,626/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr">
@@ -42590,7 +42590,7 @@
           <t>B1 | 301呎 (1房)
 $765万
 $25,430/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -42598,7 +42598,7 @@
           <t>B10 | 482呎 (2房)
 $1220万
 $25,315/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -42606,7 +42606,7 @@
           <t>B2 | 308呎 (1房)
 $752万
 $24,429/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr">
@@ -42638,7 +42638,7 @@
           <t>B8 | 787呎 (3房)
 $2184万
 $27,750/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -42686,7 +42686,7 @@
           <t>A3 | 308呎 (1房)
 $899万
 $29,181/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -42703,7 +42703,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,193/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="I39" s="23" t="inlineStr">
@@ -42711,7 +42711,7 @@
           <t>B10 | 482呎 (2房)
 $1212万
 $25,145/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
@@ -42719,7 +42719,7 @@
           <t>B2 | 308呎 (1房)
 $746万
 $24,233/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -42727,7 +42727,7 @@
           <t>B3 | 449呎 (2房)
 $1240万
 $27,627/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -42735,7 +42735,7 @@
           <t>B5 | 307呎 (1房)
 $793万
 $25,819/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M39" s="23" t="inlineStr">
@@ -42743,7 +42743,7 @@
           <t>B6 | 304呎 (1房)
 $785万
 $25,818/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
@@ -42751,7 +42751,7 @@
           <t>B8 | 787呎 (3房)
 $2169万
 $27,555/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -42783,7 +42783,7 @@
           <t>A1 | 908呎 (4+房)
 $3354万
 $36,941/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -42799,7 +42799,7 @@
           <t>A3 | 308呎 (1房)
 $861万
 $27,963/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -42816,7 +42816,7 @@
           <t>B1 | 301呎 (1房)
 $721万
 $23,946/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -42824,7 +42824,7 @@
           <t>B10 | 482呎 (2房)
 $1210万
 $25,104/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -42832,7 +42832,7 @@
           <t>B2 | 308呎 (1房)
 $738万
 $23,946/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -42840,7 +42840,7 @@
           <t>B3 | 449呎 (2房)
 $1260万
 $28,062/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -42848,7 +42848,7 @@
           <t>B5 | 307呎 (1房)
 $785万
 $25,560/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="M40" s="23" t="inlineStr">
@@ -42856,7 +42856,7 @@
           <t>B6 | 304呎 (1房)
 $776万
 $25,527/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="N40" s="23" t="inlineStr">
@@ -42864,7 +42864,7 @@
           <t>B8 | 787呎 (3房)
 $2130万
 $27,062/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
@@ -42904,7 +42904,7 @@
           <t>A2 | 450呎 (2房)
 $1214万
 $26,979/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -42912,7 +42912,7 @@
           <t>A3 | 308呎 (1房)
 $845万
 $27,432/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -42929,7 +42929,7 @@
           <t>B1 | 301呎 (1房)
 $681万
 $22,617/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
@@ -42937,7 +42937,7 @@
           <t>B10 | 482呎 (2房)
 $1198万
 $24,861/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -42945,7 +42945,7 @@
           <t>B2 | 308呎 (1房)
 $697万
 $22,618/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="K41" s="21" t="inlineStr">
@@ -42961,7 +42961,7 @@
           <t>B5 | 307呎 (1房)
 $777万
 $25,304/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="M41" s="23" t="inlineStr">
@@ -42969,7 +42969,7 @@
           <t>B6 | 304呎 (1房)
 $769万
 $25,304/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
@@ -42977,7 +42977,7 @@
           <t>B8 | 787呎 (3房)
 $2157万
 $27,409/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -42985,7 +42985,7 @@
           <t>B9 | 296呎 (1房)
 $730万
 $24,675/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="P41" s="20" t="inlineStr"/>
@@ -43319,7 +43319,7 @@
           <t>C | 1227呎 (4+房)
 $5225万
 $42,586/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -43372,7 +43372,7 @@
           <t>C | 1227呎 (4+房)
 $4824万
 $39,314/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="O8" s="22" t="inlineStr">
@@ -43452,7 +43452,7 @@
           <t>A | 1985呎 (4+房)
 $8348万
 $42,055/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -43478,7 +43478,7 @@
           <t>C | 1227呎 (4+房)
 $4330万
 $35,289/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -43486,7 +43486,7 @@
           <t>D | 1365呎 (4+房)
 $5191万
 $38,028/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr"/>
@@ -43584,7 +43584,7 @@
           <t>C | 1227呎 (4+房)
 $4668万
 $38,044/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="O12" s="23" t="inlineStr">
@@ -43592,7 +43592,7 @@
           <t>D | 1365呎 (4+房)
 $5020万
 $36,777/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr"/>
@@ -43645,7 +43645,7 @@
           <t>D | 1365呎 (4+房)
 $4934万
 $36,147/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr"/>
@@ -43698,7 +43698,7 @@
           <t>D | 1365呎 (4+房)
 $4908万
 $35,956/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr"/>
@@ -43743,7 +43743,7 @@
           <t>C | 1227呎 (4+房)
 $4470万
 $36,430/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -43804,7 +43804,7 @@
           <t>D | 1365呎 (4+房)
 $4808万
 $35,223/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr"/>
@@ -43849,7 +43849,7 @@
           <t>C | 1227呎 (4+房)
 $4450万
 $36,267/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -43857,7 +43857,7 @@
           <t>D | 1365呎 (4+房)
 $4800万
 $35,165/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr"/>
@@ -43955,7 +43955,7 @@
           <t>C | 1227呎 (4+房)
 $4448万
 $36,251/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -43963,7 +43963,7 @@
           <t>D | 1365呎 (4+房)
 $4789万
 $35,084/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr"/>
@@ -44093,7 +44093,7 @@
           <t>B5 | 299呎 (1房)
 $828万
 $27,695/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -44101,7 +44101,7 @@
           <t>B6 | 297呎 (1房)
 $826万
 $27,810/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -44131,7 +44131,7 @@
           <t>A1 | 908呎 (4+房)
 $3710万
 $40,859/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -44188,7 +44188,7 @@
           <t>B5 | 299呎 (1房)
 $859万
 $28,723/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -44196,7 +44196,7 @@
           <t>B6 | 297呎 (1房)
 $824万
 $27,732/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44321,7 +44321,7 @@
           <t>A1 | 908呎 (4+房)
 $3657万
 $40,279/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -44329,7 +44329,7 @@
           <t>A2 | 446呎 (2房)
 $1818万
 $40,774/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -44345,7 +44345,7 @@
           <t>A5 | 545呎 (2房)
 $2071万
 $38,000/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
@@ -44378,7 +44378,7 @@
           <t>B5 | 299呎 (1房)
 $816万
 $27,280/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -44386,7 +44386,7 @@
           <t>B6 | 297呎 (1房)
 $814万
 $27,394/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -44416,7 +44416,7 @@
           <t>A1 | 908呎 (4+房)
 $3545万
 $39,040/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -44465,7 +44465,7 @@
           <t>B3 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -44473,7 +44473,7 @@
           <t>B5 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -44481,7 +44481,7 @@
           <t>B6 | 297呎 (1房)
 $810万
 $27,285/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -44511,7 +44511,7 @@
           <t>A1 | 908呎 (4+房)
 $3626万
 $39,932/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -44560,7 +44560,7 @@
           <t>B3 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -44568,7 +44568,7 @@
           <t>B5 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -44576,7 +44576,7 @@
           <t>B6 | 297呎 (1房)
 $798万
 $26,884/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -44606,7 +44606,7 @@
           <t>A1 | 908呎 (4+房)
 $3605万
 $39,705/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -44639,7 +44639,7 @@
           <t>B1 | 478呎 (2房)
 $1253万
 $26,218/呎
-(26年-07月)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -44663,7 +44663,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,428/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -44671,7 +44671,7 @@
           <t>B6 | 297呎 (1房)
 $818万
 $27,551/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -44796,7 +44796,7 @@
           <t>A1 | 908呎 (4+房)
 $3501万
 $38,558/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -44853,7 +44853,7 @@
           <t>B5 | 299呎 (1房)
 $768万
 $25,670/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -44861,7 +44861,7 @@
           <t>B6 | 297呎 (1房)
 $795万
 $26,760/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -44891,7 +44891,7 @@
           <t>A1 | 908呎 (4+房)
 $3335万
 $36,730/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -44948,7 +44948,7 @@
           <t>B5 | 299呎 (1房)
 $766万
 $25,618/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -44956,7 +44956,7 @@
           <t>B6 | 297呎 (1房)
 $793万
 $26,706/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -45043,7 +45043,7 @@
           <t>B5 | 299呎 (1房)
 $764万
 $25,567/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -45051,7 +45051,7 @@
           <t>B6 | 297呎 (1房)
 $791万
 $26,620/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -45081,7 +45081,7 @@
           <t>A1 | 908呎 (4+房)
 $3557万
 $39,172/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
@@ -45130,7 +45130,7 @@
           <t>B3 | 299呎 (1房)
 $792万
 $26,489/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -45138,7 +45138,7 @@
           <t>B5 | 299呎 (1房)
 $763万
 $25,516/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
@@ -45146,7 +45146,7 @@
           <t>B6 | 297呎 (1房)
 $789万
 $26,566/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -45217,7 +45217,7 @@
           <t>B2 | 302呎 (1房)
 $799万
 $26,470/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -45225,7 +45225,7 @@
           <t>B3 | 299呎 (1房)
 $789万
 $26,403/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -45233,7 +45233,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,436/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="L33" s="23" t="inlineStr">
@@ -45241,7 +45241,7 @@
           <t>B6 | 297呎 (1房)
 $787万
 $26,513/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -45271,7 +45271,7 @@
           <t>A1 | 908呎 (4+房)
 $3610万
 $39,758/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -45312,7 +45312,7 @@
           <t>B2 | 302呎 (1房)
 $796万
 $26,364/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -45320,7 +45320,7 @@
           <t>B3 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -45328,7 +45328,7 @@
           <t>B5 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">
@@ -45336,7 +45336,7 @@
           <t>B6 | 297呎 (1房)
 $785万
 $26,440/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -45366,7 +45366,7 @@
           <t>A1 | 908呎 (4+房)
 $3366万
 $37,070/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -45407,7 +45407,7 @@
           <t>B2 | 302呎 (1房)
 $792万
 $26,225/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -45415,7 +45415,7 @@
           <t>B3 | 299呎 (1房)
 $784万
 $26,225/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -45423,7 +45423,7 @@
           <t>B5 | 299呎 (1房)
 $783万
 $26,192/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -45431,7 +45431,7 @@
           <t>B6 | 297呎 (1房)
 $782万
 $26,334/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -45556,7 +45556,7 @@
           <t>A1 | 908呎 (4+房)
 $3136万
 $34,543/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -45597,7 +45597,7 @@
           <t>B2 | 302呎 (1房)
 $782万
 $25,878/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -45605,7 +45605,7 @@
           <t>B3 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -45613,7 +45613,7 @@
           <t>B5 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="L37" s="23" t="inlineStr">
@@ -45621,7 +45621,7 @@
           <t>B6 | 297呎 (1房)
 $773万
 $26,019/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
@@ -45651,7 +45651,7 @@
           <t>A1 | 908呎 (4+房)
 $3033万
 $33,401/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
@@ -45692,7 +45692,7 @@
           <t>B2 | 302呎 (1房)
 $776万
 $25,704/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -45700,7 +45700,7 @@
           <t>B3 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
@@ -45708,7 +45708,7 @@
           <t>B5 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="L38" s="23" t="inlineStr">
@@ -45716,7 +45716,7 @@
           <t>B6 | 297呎 (1房)
 $767万
 $25,810/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
@@ -45746,7 +45746,7 @@
           <t>A1 | 908呎 (4+房)
 $3064万
 $33,745/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
@@ -45795,7 +45795,7 @@
           <t>B3 | 299呎 (1房)
 $745万
 $24,902/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -45803,7 +45803,7 @@
           <t>B5 | 299呎 (1房)
 $718万
 $23,998/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -45811,7 +45811,7 @@
           <t>B6 | 297呎 (1房)
 $716万
 $24,098/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -45841,7 +45841,7 @@
           <t>A1 | 908呎 (4+房)
 $3012万
 $33,172/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -45849,7 +45849,7 @@
           <t>A2 | 446呎 (2房)
 $1423万
 $31,901/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -45865,7 +45865,7 @@
           <t>A5 | 545呎 (2房)
 $1660万
 $30,455/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -45874,7 +45874,7 @@
           <t>B1 | 478呎 (2房)
 $1178万
 $24,644/呎
-(26年-07月)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -45882,7 +45882,7 @@
           <t>B2 | 302呎 (1房)
 $746万
 $24,686/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -45890,7 +45890,7 @@
           <t>B3 | 299呎 (1房)
 $738万
 $24,685/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -45898,7 +45898,7 @@
           <t>B5 | 299呎 (1房)
 $710万
 $23,758/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -45906,7 +45906,7 @@
           <t>B6 | 297呎 (1房)
 $709万
 $23,857/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="M40" s="21" t="inlineStr">
@@ -45936,7 +45936,7 @@
           <t>A1 | 874呎 (4+房)
 $2659万
 $30,427/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
@@ -45977,7 +45977,7 @@
           <t>B2 | 302呎 (1房)
 $719万
 $23,809/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -45985,7 +45985,7 @@
           <t>B3 | 299呎 (1房)
 $712万
 $23,808/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
@@ -45993,7 +45993,7 @@
           <t>B5 | 299呎 (1房)
 $685万
 $22,923/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="L41" s="23" t="inlineStr">
@@ -46001,7 +46001,7 @@
           <t>B6 | 297呎 (1房)
 $683万
 $22,985/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M41" s="21" t="inlineStr">

--- a/files/九龙-启德-天玺．天第2期.xlsx
+++ b/files/九龙-启德-天玺．天第2期.xlsx
@@ -133,13 +133,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -290,10 +290,10 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -21455,7 +21455,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -22885,7 +22885,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -22895,12 +22895,12 @@
       </c>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
@@ -22910,12 +22910,12 @@
       </c>
       <c r="K337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M337" s="3" t="inlineStr">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -23773,12 +23773,12 @@
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J350" s="3" t="inlineStr">
@@ -23788,12 +23788,12 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M350" s="3" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="N350" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24175,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -24185,12 +24185,12 @@
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -24200,12 +24200,12 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M356" s="3" t="inlineStr">
@@ -24215,7 +24215,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26583,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -29199,7 +29199,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -31227,7 +31227,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
@@ -35235,7 +35235,7 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
@@ -36105,7 +36105,7 @@
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
@@ -36563,7 +36563,7 @@
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
@@ -37293,7 +37293,7 @@
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
@@ -37433,7 +37433,7 @@
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="F562" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G562" s="3" t="inlineStr">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
@@ -39585,12 +39585,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39600,12 +39600,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -39974,12 +39974,12 @@
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="21" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t>C | 1511呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="Q9" s="20" t="inlineStr"/>
@@ -40003,7 +40003,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>A | 2230呎 (4+房)
 招标单位
@@ -40129,7 +40129,7 @@
       <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>B | 1808呎 (4+房)
 招标单位
@@ -40145,7 +40145,7 @@
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="24" t="inlineStr">
+      <c r="P12" s="25" t="inlineStr">
         <is>
           <t>C | 1511呎 (4+房)
 招标单位
@@ -40704,7 +40704,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="M21" s="25" t="inlineStr">
+      <c r="M21" s="24" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $938万
@@ -40817,7 +40817,7 @@
 (25年-12月-09日)</t>
         </is>
       </c>
-      <c r="M22" s="25" t="inlineStr">
+      <c r="M22" s="24" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $927万
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $869万
@@ -40898,7 +40898,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1651万
@@ -40906,7 +40906,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $890万
@@ -40922,7 +40922,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $927万
@@ -40930,7 +40930,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M23" s="25" t="inlineStr">
+      <c r="M23" s="24" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $918万
@@ -41011,7 +41011,7 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1568万
@@ -41043,7 +41043,7 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="M24" s="25" t="inlineStr">
+      <c r="M24" s="24" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $909万
@@ -41148,7 +41148,7 @@
 (25年-12月-22日)</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
+      <c r="L25" s="24" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $909万
@@ -41156,7 +41156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M25" s="25" t="inlineStr">
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $900万
@@ -41196,12 +41196,12 @@
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr"/>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -41261,7 +41261,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="24" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $889万
@@ -41325,7 +41325,7 @@
 (26年-01月-25日)</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1105万
@@ -41438,7 +41438,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1088万
@@ -41455,7 +41455,7 @@
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $849万
@@ -41471,7 +41471,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="J28" s="24" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $869万
@@ -41761,12 +41761,12 @@
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -41777,7 +41777,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1043万
@@ -41890,7 +41890,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1035万
@@ -42326,12 +42326,12 @@
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -42359,7 +42359,7 @@
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="25" t="inlineStr">
+      <c r="H36" s="24" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $829万
@@ -42375,7 +42375,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J36" s="25" t="inlineStr">
+      <c r="J36" s="24" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $848万
@@ -42455,7 +42455,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1011万
@@ -42480,7 +42480,7 @@
 (25年-12月-09日)</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I37" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1417万
@@ -42568,7 +42568,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1003万
@@ -42665,7 +42665,7 @@
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
@@ -42891,12 +42891,12 @@
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -43083,7 +43083,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43098,12 +43098,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -43232,7 +43232,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>PSH B | 3553呎 (4+房)
 招标单位
@@ -43273,7 +43273,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>PSV B | 2765呎 (4+房)
 招标单位
@@ -43341,7 +43341,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
@@ -43534,12 +43534,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="O11" s="21" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>D | 1365呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr"/>
@@ -43553,7 +43553,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
@@ -43632,7 +43632,7 @@
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
       <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="24" t="inlineStr">
+      <c r="N13" s="25" t="inlineStr">
         <is>
           <t>C | 1227呎 (4+房)
 招标单位
@@ -43685,12 +43685,12 @@
       <c r="K14" s="20" t="inlineStr"/>
       <c r="L14" s="20" t="inlineStr"/>
       <c r="M14" s="20" t="inlineStr"/>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N14" s="24" t="inlineStr">
         <is>
           <t>C | 1227呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="O14" s="23" t="inlineStr">
@@ -43712,12 +43712,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -44064,7 +44064,7 @@
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 $1572万
@@ -44072,7 +44072,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $930万
@@ -44080,7 +44080,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J21" s="25" t="inlineStr">
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $958万
@@ -44164,10 +44164,10 @@
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $927万
@@ -44175,7 +44175,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="J22" s="24" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $954万
@@ -44254,7 +44254,7 @@
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 $1560万
@@ -44262,7 +44262,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $919万
@@ -44270,7 +44270,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J23" s="25" t="inlineStr">
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $910万
@@ -44278,7 +44278,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K23" s="25" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $910万
@@ -44286,7 +44286,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $908万
@@ -44357,7 +44357,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $915万
@@ -44365,7 +44365,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J24" s="25" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $906万
@@ -44419,7 +44419,7 @@
 (25年-11月-18日)</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -44435,7 +44435,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
@@ -44444,7 +44444,7 @@
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 $1540万
@@ -44452,7 +44452,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $913万
@@ -44544,10 +44544,10 @@
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $899万
@@ -44753,7 +44753,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K28" s="25" t="inlineStr">
+      <c r="K28" s="24" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $868万
@@ -44761,7 +44761,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="24" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $898万
@@ -44799,7 +44799,7 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -44815,12 +44815,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -44829,7 +44829,7 @@
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -45084,7 +45084,7 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -45117,7 +45117,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I32" s="25" t="inlineStr">
+      <c r="I32" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $890万
@@ -45195,12 +45195,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr"/>
@@ -45394,12 +45394,12 @@
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="24" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -45464,12 +45464,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -45497,7 +45497,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I36" s="25" t="inlineStr">
+      <c r="I36" s="24" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $875万
@@ -45505,7 +45505,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J36" s="25" t="inlineStr">
+      <c r="J36" s="24" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $866万
@@ -45513,7 +45513,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K36" s="25" t="inlineStr">
+      <c r="K36" s="24" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $866万
@@ -45521,7 +45521,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
+      <c r="L36" s="24" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $864万
@@ -45584,12 +45584,12 @@
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="24" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -45654,12 +45654,12 @@
 (25年-11月-05日)</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -45670,16 +45670,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
@@ -45749,12 +45749,12 @@
 (25年-11月-13日)</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -45765,21 +45765,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -45939,7 +45939,7 @@
 (25年-12月-17日)</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -45955,7 +45955,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
@@ -45964,7 +45964,7 @@
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="24" t="inlineStr">
+      <c r="H41" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
